--- a/paper/data/merapi_cpx_raw.xlsx
+++ b/paper/data/merapi_cpx_raw.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C12EB87B-3264-4BCD-B904-DC064743EC9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52E3AD39-EFD3-46F3-A5A8-DFF653E9B54C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3420" yWindow="3370" windowWidth="33020" windowHeight="18230" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3800" yWindow="3800" windowWidth="28800" windowHeight="16760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -456,9 +456,6 @@
     <t>core</t>
   </si>
   <si>
-    <t>LI thesis</t>
-  </si>
-  <si>
     <t>Rim/core</t>
   </si>
   <si>
@@ -1687,13 +1684,16 @@
   </si>
   <si>
     <t>Eruption</t>
+  </si>
+  <si>
+    <t>Costa et al., 2013</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1834,6 +1834,10 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="33">
@@ -2177,10 +2181,13 @@
     <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="17" builtinId="30" customBuiltin="1"/>
@@ -2545,75 +2552,75 @@
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>546</v>
+      </c>
+      <c r="B1" t="s">
+        <v>549</v>
+      </c>
+      <c r="C1" t="s">
         <v>547</v>
       </c>
-      <c r="B1" t="s">
-        <v>550</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E1" t="s">
+        <v>141</v>
+      </c>
+      <c r="F1" t="s">
+        <v>142</v>
+      </c>
+      <c r="G1" t="s">
+        <v>143</v>
+      </c>
+      <c r="H1" t="s">
+        <v>144</v>
+      </c>
+      <c r="I1" t="s">
+        <v>145</v>
+      </c>
+      <c r="J1" t="s">
+        <v>146</v>
+      </c>
+      <c r="K1" t="s">
+        <v>147</v>
+      </c>
+      <c r="L1" t="s">
+        <v>148</v>
+      </c>
+      <c r="M1" t="s">
+        <v>149</v>
+      </c>
+      <c r="N1" t="s">
+        <v>150</v>
+      </c>
+      <c r="O1" t="s">
+        <v>151</v>
+      </c>
+      <c r="P1" t="s">
+        <v>543</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>544</v>
+      </c>
+      <c r="R1" t="s">
+        <v>0</v>
+      </c>
+      <c r="S1" t="s">
+        <v>545</v>
+      </c>
+      <c r="T1" t="s">
         <v>548</v>
-      </c>
-      <c r="D1" t="s">
-        <v>141</v>
-      </c>
-      <c r="E1" t="s">
-        <v>142</v>
-      </c>
-      <c r="F1" t="s">
-        <v>143</v>
-      </c>
-      <c r="G1" t="s">
-        <v>144</v>
-      </c>
-      <c r="H1" t="s">
-        <v>145</v>
-      </c>
-      <c r="I1" t="s">
-        <v>146</v>
-      </c>
-      <c r="J1" t="s">
-        <v>147</v>
-      </c>
-      <c r="K1" t="s">
-        <v>148</v>
-      </c>
-      <c r="L1" t="s">
-        <v>149</v>
-      </c>
-      <c r="M1" t="s">
-        <v>150</v>
-      </c>
-      <c r="N1" t="s">
-        <v>151</v>
-      </c>
-      <c r="O1" t="s">
-        <v>152</v>
-      </c>
-      <c r="P1" t="s">
-        <v>544</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>545</v>
-      </c>
-      <c r="R1" t="s">
-        <v>0</v>
-      </c>
-      <c r="S1" t="s">
-        <v>546</v>
-      </c>
-      <c r="T1" t="s">
-        <v>549</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B2">
         <v>2006</v>
       </c>
       <c r="C2" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D2" t="s">
         <v>96</v>
@@ -2657,13 +2664,13 @@
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B3">
         <v>2006</v>
       </c>
       <c r="C3" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D3" t="s">
         <v>96</v>
@@ -2707,13 +2714,13 @@
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B4">
         <v>2006</v>
       </c>
       <c r="C4" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D4" t="s">
         <v>96</v>
@@ -2757,13 +2764,13 @@
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B5">
         <v>2006</v>
       </c>
       <c r="C5" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D5" t="s">
         <v>96</v>
@@ -2807,13 +2814,13 @@
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B6">
         <v>2006</v>
       </c>
       <c r="C6" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D6" t="s">
         <v>96</v>
@@ -2857,13 +2864,13 @@
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B7">
         <v>2006</v>
       </c>
       <c r="C7" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D7" t="s">
         <v>139</v>
@@ -2907,13 +2914,13 @@
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B8">
         <v>2006</v>
       </c>
       <c r="C8" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D8" t="s">
         <v>139</v>
@@ -2957,13 +2964,13 @@
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B9">
         <v>2006</v>
       </c>
       <c r="C9" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D9" t="s">
         <v>139</v>
@@ -3007,13 +3014,13 @@
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B10">
         <v>2006</v>
       </c>
       <c r="C10" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D10" t="s">
         <v>139</v>
@@ -3057,13 +3064,13 @@
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B11">
         <v>2006</v>
       </c>
       <c r="C11" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D11" t="s">
         <v>139</v>
@@ -3107,13 +3114,13 @@
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B12">
         <v>2006</v>
       </c>
       <c r="C12" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D12" t="s">
         <v>139</v>
@@ -3157,13 +3164,13 @@
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B13">
         <v>2006</v>
       </c>
       <c r="C13" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D13" t="s">
         <v>139</v>
@@ -3207,13 +3214,13 @@
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B14">
         <v>2006</v>
       </c>
       <c r="C14" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D14" t="s">
         <v>139</v>
@@ -3257,13 +3264,13 @@
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B15">
         <v>2006</v>
       </c>
       <c r="C15" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D15" t="s">
         <v>139</v>
@@ -3307,13 +3314,13 @@
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B16">
         <v>2006</v>
       </c>
       <c r="C16" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D16" t="s">
         <v>139</v>
@@ -3357,13 +3364,13 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B17">
         <v>2006</v>
       </c>
       <c r="C17" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D17" t="s">
         <v>139</v>
@@ -3407,13 +3414,13 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B18">
         <v>2006</v>
       </c>
       <c r="C18" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D18" t="s">
         <v>139</v>
@@ -3457,13 +3464,13 @@
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B19">
         <v>2006</v>
       </c>
       <c r="C19" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D19" t="s">
         <v>139</v>
@@ -3507,13 +3514,13 @@
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B20">
         <v>2006</v>
       </c>
       <c r="C20" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D20" t="s">
         <v>139</v>
@@ -3557,13 +3564,13 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B21">
         <v>2006</v>
       </c>
       <c r="C21" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D21" t="s">
         <v>139</v>
@@ -3607,13 +3614,13 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B22">
         <v>2006</v>
       </c>
       <c r="C22" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E22">
         <v>50.832092274785353</v>
@@ -3654,13 +3661,13 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B23">
         <v>2006</v>
       </c>
       <c r="C23" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E23">
         <v>51.69649533875068</v>
@@ -3701,13 +3708,13 @@
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B24">
         <v>2006</v>
       </c>
       <c r="C24" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E24">
         <v>52.425718314648321</v>
@@ -3748,13 +3755,13 @@
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B25">
         <v>2006</v>
       </c>
       <c r="C25" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E25">
         <v>52.374514281136079</v>
@@ -3795,13 +3802,13 @@
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B26">
         <v>2006</v>
       </c>
       <c r="C26" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E26">
         <v>51.941465951828448</v>
@@ -3842,13 +3849,13 @@
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B27">
         <v>2006</v>
       </c>
       <c r="C27" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E27">
         <v>52.191933684042723</v>
@@ -3889,13 +3896,13 @@
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B28">
         <v>2006</v>
       </c>
       <c r="C28" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E28">
         <v>52.15653271617925</v>
@@ -3936,13 +3943,13 @@
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B29">
         <v>2006</v>
       </c>
       <c r="C29" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E29">
         <v>51.039212554406419</v>
@@ -3983,13 +3990,13 @@
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B30">
         <v>2006</v>
       </c>
       <c r="C30" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E30">
         <v>51.420972417296724</v>
@@ -4030,13 +4037,13 @@
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B31">
         <v>2006</v>
       </c>
       <c r="C31" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E31">
         <v>50.917734849852557</v>
@@ -4077,13 +4084,13 @@
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B32">
         <v>2006</v>
       </c>
       <c r="C32" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E32">
         <v>51.689185795368921</v>
@@ -4124,13 +4131,13 @@
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B33">
         <v>2006</v>
       </c>
       <c r="C33" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E33">
         <v>51.646051569305598</v>
@@ -4171,13 +4178,13 @@
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B34">
         <v>2006</v>
       </c>
       <c r="C34" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E34">
         <v>51.206969144094472</v>
@@ -4218,13 +4225,13 @@
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B35">
         <v>2006</v>
       </c>
       <c r="C35" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E35">
         <v>50.514464956445295</v>
@@ -4265,13 +4272,13 @@
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B36">
         <v>2006</v>
       </c>
       <c r="C36" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E36">
         <v>50.843847946636664</v>
@@ -4312,13 +4319,13 @@
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B37">
         <v>2006</v>
       </c>
       <c r="C37" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E37">
         <v>49.121400146349771</v>
@@ -4359,13 +4366,13 @@
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B38">
         <v>2006</v>
       </c>
       <c r="C38" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E38">
         <v>49.407146290658545</v>
@@ -4406,13 +4413,13 @@
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B39">
         <v>2006</v>
       </c>
       <c r="C39" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E39">
         <v>49.325278360497009</v>
@@ -4453,13 +4460,13 @@
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B40">
         <v>2006</v>
       </c>
       <c r="C40" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E40">
         <v>48.880742375962683</v>
@@ -4500,13 +4507,13 @@
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B41">
         <v>2006</v>
       </c>
       <c r="C41" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E41">
         <v>48.922136422136418</v>
@@ -4547,13 +4554,13 @@
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B42">
         <v>2006</v>
       </c>
       <c r="C42" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E42">
         <v>49.159052843775378</v>
@@ -4594,13 +4601,13 @@
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B43">
         <v>2006</v>
       </c>
       <c r="C43" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E43">
         <v>48.948466848611332</v>
@@ -4641,13 +4648,13 @@
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B44">
         <v>2006</v>
       </c>
       <c r="C44" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E44">
         <v>48.468192467111194</v>
@@ -4688,13 +4695,13 @@
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B45">
         <v>2006</v>
       </c>
       <c r="C45" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E45">
         <v>48.635238219344231</v>
@@ -4735,13 +4742,13 @@
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B46">
         <v>2006</v>
       </c>
       <c r="C46" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E46">
         <v>50.557825581861145</v>
@@ -4782,13 +4789,13 @@
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B47">
         <v>2006</v>
       </c>
       <c r="C47" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E47">
         <v>52.337328167082163</v>
@@ -4829,13 +4836,13 @@
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B48">
         <v>2006</v>
       </c>
       <c r="C48" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E48">
         <v>51.681506437251834</v>
@@ -4876,13 +4883,13 @@
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B49">
         <v>2006</v>
       </c>
       <c r="C49" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E49">
         <v>51.817179512879626</v>
@@ -4923,13 +4930,13 @@
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B50">
         <v>2006</v>
       </c>
       <c r="C50" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E50">
         <v>52.34928856402923</v>
@@ -4970,13 +4977,13 @@
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B51">
         <v>2006</v>
       </c>
       <c r="C51" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E51">
         <v>51.861569464674076</v>
@@ -5017,13 +5024,13 @@
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B52">
         <v>2006</v>
       </c>
       <c r="C52" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E52">
         <v>52.132393380330988</v>
@@ -5064,13 +5071,13 @@
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B53">
         <v>2006</v>
       </c>
       <c r="C53" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E53">
         <v>52.056101038090084</v>
@@ -5111,13 +5118,13 @@
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B54">
         <v>2006</v>
       </c>
       <c r="C54" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E54">
         <v>51.87481900881739</v>
@@ -5158,13 +5165,13 @@
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B55">
         <v>2006</v>
       </c>
       <c r="C55" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E55">
         <v>51.992500698073322</v>
@@ -5205,13 +5212,13 @@
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B56">
         <v>2006</v>
       </c>
       <c r="C56" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E56">
         <v>51.802781491310334</v>
@@ -5252,13 +5259,13 @@
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B57">
         <v>2006</v>
       </c>
       <c r="C57" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E57">
         <v>50.470533940646497</v>
@@ -5299,13 +5306,13 @@
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B58">
         <v>2006</v>
       </c>
       <c r="C58" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E58">
         <v>51.967853689977439</v>
@@ -5346,13 +5353,13 @@
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B59">
         <v>2006</v>
       </c>
       <c r="C59" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E59">
         <v>52.445988578730876</v>
@@ -5393,13 +5400,13 @@
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B60">
         <v>2006</v>
       </c>
       <c r="C60" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E60">
         <v>48.775082359988012</v>
@@ -5440,13 +5447,13 @@
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B61">
         <v>2006</v>
       </c>
       <c r="C61" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E61">
         <v>49.991037820397921</v>
@@ -5487,13 +5494,13 @@
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B62">
         <v>2006</v>
       </c>
       <c r="C62" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E62">
         <v>50.292101341281665</v>
@@ -5534,13 +5541,13 @@
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B63">
         <v>2006</v>
       </c>
       <c r="C63" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E63">
         <v>50.628394877161512</v>
@@ -5581,13 +5588,13 @@
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B64">
         <v>2006</v>
       </c>
       <c r="C64" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E64">
         <v>50.530355896720167</v>
@@ -5628,13 +5635,13 @@
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B65">
         <v>2006</v>
       </c>
       <c r="C65" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E65">
         <v>50.463018281754103</v>
@@ -5675,13 +5682,13 @@
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B66">
         <v>2006</v>
       </c>
       <c r="C66" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E66">
         <v>50.154290264782006</v>
@@ -5722,13 +5729,13 @@
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B67">
         <v>2006</v>
       </c>
       <c r="C67" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E67">
         <v>50.413979778680044</v>
@@ -5769,13 +5776,13 @@
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B68">
         <v>2006</v>
       </c>
       <c r="C68" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E68">
         <v>50.351108185209561</v>
@@ -5816,13 +5823,13 @@
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B69">
         <v>2006</v>
       </c>
       <c r="C69" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E69">
         <v>50.386918379120338</v>
@@ -5863,13 +5870,13 @@
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B70">
         <v>2006</v>
       </c>
       <c r="C70" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E70">
         <v>50.313659966582954</v>
@@ -5910,13 +5917,13 @@
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B71">
         <v>2006</v>
       </c>
       <c r="C71" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E71">
         <v>50.483637993724152</v>
@@ -5957,13 +5964,13 @@
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B72">
         <v>2006</v>
       </c>
       <c r="C72" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E72">
         <v>50.392527079399784</v>
@@ -6004,13 +6011,13 @@
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B73">
         <v>2006</v>
       </c>
       <c r="C73" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E73">
         <v>50.374725931831776</v>
@@ -6051,13 +6058,13 @@
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B74">
         <v>2006</v>
       </c>
       <c r="C74" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E74">
         <v>50.118064342575884</v>
@@ -6098,13 +6105,13 @@
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B75">
         <v>2006</v>
       </c>
       <c r="C75" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E75">
         <v>49.750235721307199</v>
@@ -6145,13 +6152,13 @@
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B76">
         <v>2006</v>
       </c>
       <c r="C76" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E76">
         <v>49.505059173368984</v>
@@ -6192,13 +6199,13 @@
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B77">
         <v>2006</v>
       </c>
       <c r="C77" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E77">
         <v>49.874889903114742</v>
@@ -6239,13 +6246,13 @@
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B78">
         <v>2006</v>
       </c>
       <c r="C78" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E78">
         <v>49.937505624493795</v>
@@ -6286,13 +6293,13 @@
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B79">
         <v>2006</v>
       </c>
       <c r="C79" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E79">
         <v>49.902506824522277</v>
@@ -6333,13 +6340,13 @@
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B80">
         <v>2006</v>
       </c>
       <c r="C80" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E80">
         <v>50.02933426142296</v>
@@ -6380,13 +6387,13 @@
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B81">
         <v>2006</v>
       </c>
       <c r="C81" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E81">
         <v>50.026379971131348</v>
@@ -6427,13 +6434,13 @@
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B82">
         <v>2006</v>
       </c>
       <c r="C82" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E82">
         <v>49.550062991181235</v>
@@ -6474,13 +6481,13 @@
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B83">
         <v>2006</v>
       </c>
       <c r="C83" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E83">
         <v>49.412960711224507</v>
@@ -6521,13 +6528,13 @@
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B84">
         <v>2006</v>
       </c>
       <c r="C84" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E84">
         <v>49.355769134804433</v>
@@ -6568,13 +6575,13 @@
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B85">
         <v>2006</v>
       </c>
       <c r="C85" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E85">
         <v>49.797389460269414</v>
@@ -6615,13 +6622,13 @@
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B86">
         <v>2006</v>
       </c>
       <c r="C86" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E86">
         <v>50.030460705689656</v>
@@ -6662,13 +6669,13 @@
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B87">
         <v>2006</v>
       </c>
       <c r="C87" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E87">
         <v>49.763654936206869</v>
@@ -6709,13 +6716,13 @@
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B88">
         <v>2006</v>
       </c>
       <c r="C88" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E88">
         <v>49.387791849228748</v>
@@ -6756,13 +6763,13 @@
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B89">
         <v>2006</v>
       </c>
       <c r="C89" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E89">
         <v>49.339052875769944</v>
@@ -6803,13 +6810,13 @@
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B90">
         <v>2006</v>
       </c>
       <c r="C90" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E90">
         <v>49.534394713127064</v>
@@ -6850,13 +6857,13 @@
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B91">
         <v>2006</v>
       </c>
       <c r="C91" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E91">
         <v>49.514669975583402</v>
@@ -6897,13 +6904,13 @@
     </row>
     <row r="92" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B92">
         <v>2006</v>
       </c>
       <c r="C92" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E92">
         <v>49.053747920049716</v>
@@ -6944,13 +6951,13 @@
     </row>
     <row r="93" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B93">
         <v>2006</v>
       </c>
       <c r="C93" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E93">
         <v>49.715795771838849</v>
@@ -6991,13 +6998,13 @@
     </row>
     <row r="94" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B94">
         <v>2006</v>
       </c>
       <c r="C94" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E94">
         <v>50.995307976440053</v>
@@ -7038,13 +7045,13 @@
     </row>
     <row r="95" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B95">
         <v>2006</v>
       </c>
       <c r="C95" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E95">
         <v>51.678473355354804</v>
@@ -7085,13 +7092,13 @@
     </row>
     <row r="96" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B96">
         <v>2006</v>
       </c>
       <c r="C96" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E96">
         <v>52.205889670684009</v>
@@ -7132,13 +7139,13 @@
     </row>
     <row r="97" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B97">
         <v>2006</v>
       </c>
       <c r="C97" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E97">
         <v>52.079900124843945</v>
@@ -7179,13 +7186,13 @@
     </row>
     <row r="98" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B98">
         <v>2006</v>
       </c>
       <c r="C98" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E98">
         <v>52.28020875150542</v>
@@ -7226,13 +7233,13 @@
     </row>
     <row r="99" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B99">
         <v>2006</v>
       </c>
       <c r="C99" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E99">
         <v>52.250935804792121</v>
@@ -7273,13 +7280,13 @@
     </row>
     <row r="100" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B100">
         <v>2006</v>
       </c>
       <c r="C100" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E100">
         <v>51.905041323135983</v>
@@ -7320,13 +7327,13 @@
     </row>
     <row r="101" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B101">
         <v>2006</v>
       </c>
       <c r="C101" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E101">
         <v>52.132317658349329</v>
@@ -7367,13 +7374,13 @@
     </row>
     <row r="102" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B102">
         <v>2006</v>
       </c>
       <c r="C102" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E102">
         <v>52.007692001115942</v>
@@ -7414,13 +7421,13 @@
     </row>
     <row r="103" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B103">
         <v>2006</v>
       </c>
       <c r="C103" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E103">
         <v>52.085587210001201</v>
@@ -7461,13 +7468,13 @@
     </row>
     <row r="104" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B104">
         <v>2006</v>
       </c>
       <c r="C104" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E104">
         <v>52.493341446626836</v>
@@ -7508,13 +7515,13 @@
     </row>
     <row r="105" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B105">
         <v>2006</v>
       </c>
       <c r="C105" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E105">
         <v>52.678428227746586</v>
@@ -7555,13 +7562,13 @@
     </row>
     <row r="106" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B106">
         <v>2006</v>
       </c>
       <c r="C106" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E106">
         <v>52.778862032727822</v>
@@ -7602,13 +7609,13 @@
     </row>
     <row r="107" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B107">
         <v>2006</v>
       </c>
       <c r="C107" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E107">
         <v>52.699280258666427</v>
@@ -7649,13 +7656,13 @@
     </row>
     <row r="108" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B108">
         <v>2006</v>
       </c>
       <c r="C108" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E108">
         <v>51.850777326477115</v>
@@ -7696,13 +7703,13 @@
     </row>
     <row r="109" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B109">
         <v>2006</v>
       </c>
       <c r="C109" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E109">
         <v>50.371890485009267</v>
@@ -7743,13 +7750,13 @@
     </row>
     <row r="110" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B110">
         <v>2006</v>
       </c>
       <c r="C110" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D110" t="s">
         <v>96</v>
@@ -7793,13 +7800,13 @@
     </row>
     <row r="111" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B111">
         <v>2006</v>
       </c>
       <c r="C111" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D111" t="s">
         <v>96</v>
@@ -7843,13 +7850,13 @@
     </row>
     <row r="112" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B112">
         <v>2006</v>
       </c>
       <c r="C112" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D112" t="s">
         <v>96</v>
@@ -7893,13 +7900,13 @@
     </row>
     <row r="113" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B113">
         <v>2006</v>
       </c>
       <c r="C113" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D113" t="s">
         <v>96</v>
@@ -7943,13 +7950,13 @@
     </row>
     <row r="114" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B114">
         <v>2006</v>
       </c>
       <c r="C114" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D114" t="s">
         <v>96</v>
@@ -7993,13 +8000,13 @@
     </row>
     <row r="115" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B115">
         <v>2006</v>
       </c>
       <c r="C115" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D115" t="s">
         <v>96</v>
@@ -8043,13 +8050,13 @@
     </row>
     <row r="116" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B116">
         <v>2006</v>
       </c>
       <c r="C116" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D116" t="s">
         <v>96</v>
@@ -8093,13 +8100,13 @@
     </row>
     <row r="117" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B117">
         <v>2006</v>
       </c>
       <c r="C117" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D117" t="s">
         <v>96</v>
@@ -8143,13 +8150,13 @@
     </row>
     <row r="118" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B118">
         <v>2006</v>
       </c>
       <c r="C118" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D118" t="s">
         <v>96</v>
@@ -8193,13 +8200,13 @@
     </row>
     <row r="119" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B119">
         <v>2006</v>
       </c>
       <c r="C119" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D119" t="s">
         <v>96</v>
@@ -8243,13 +8250,13 @@
     </row>
     <row r="120" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B120">
         <v>2006</v>
       </c>
       <c r="C120" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D120" t="s">
         <v>96</v>
@@ -8293,13 +8300,13 @@
     </row>
     <row r="121" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B121">
         <v>2006</v>
       </c>
       <c r="C121" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D121" t="s">
         <v>139</v>
@@ -8343,13 +8350,13 @@
     </row>
     <row r="122" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B122">
         <v>2006</v>
       </c>
       <c r="C122" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D122" t="s">
         <v>139</v>
@@ -8393,13 +8400,13 @@
     </row>
     <row r="123" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B123">
         <v>2006</v>
       </c>
       <c r="C123" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D123" t="s">
         <v>139</v>
@@ -8443,13 +8450,13 @@
     </row>
     <row r="124" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B124">
         <v>2006</v>
       </c>
       <c r="C124" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D124" t="s">
         <v>139</v>
@@ -8493,13 +8500,13 @@
     </row>
     <row r="125" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B125">
         <v>2006</v>
       </c>
       <c r="C125" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D125" t="s">
         <v>139</v>
@@ -8543,13 +8550,13 @@
     </row>
     <row r="126" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B126">
         <v>2006</v>
       </c>
       <c r="C126" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D126" t="s">
         <v>139</v>
@@ -8593,13 +8600,13 @@
     </row>
     <row r="127" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B127">
         <v>2006</v>
       </c>
       <c r="C127" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D127" t="s">
         <v>139</v>
@@ -8643,13 +8650,13 @@
     </row>
     <row r="128" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B128">
         <v>2006</v>
       </c>
       <c r="C128" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D128" t="s">
         <v>139</v>
@@ -8693,13 +8700,13 @@
     </row>
     <row r="129" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B129">
         <v>2006</v>
       </c>
       <c r="C129" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D129" t="s">
         <v>139</v>
@@ -8743,13 +8750,13 @@
     </row>
     <row r="130" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B130">
         <v>2006</v>
       </c>
       <c r="C130" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D130" t="s">
         <v>139</v>
@@ -8793,13 +8800,13 @@
     </row>
     <row r="131" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B131">
         <v>2006</v>
       </c>
       <c r="C131" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D131" t="s">
         <v>139</v>
@@ -8843,13 +8850,13 @@
     </row>
     <row r="132" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B132">
         <v>2006</v>
       </c>
       <c r="C132" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D132" t="s">
         <v>139</v>
@@ -8893,13 +8900,13 @@
     </row>
     <row r="133" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B133">
         <v>2006</v>
       </c>
       <c r="C133" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D133" t="s">
         <v>139</v>
@@ -8943,13 +8950,13 @@
     </row>
     <row r="134" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B134">
         <v>2006</v>
       </c>
       <c r="C134" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D134" t="s">
         <v>139</v>
@@ -8993,13 +9000,13 @@
     </row>
     <row r="135" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B135">
         <v>2006</v>
       </c>
       <c r="C135" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D135" t="s">
         <v>139</v>
@@ -9043,13 +9050,13 @@
     </row>
     <row r="136" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B136">
         <v>2006</v>
       </c>
       <c r="C136" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D136" t="s">
         <v>139</v>
@@ -9093,13 +9100,13 @@
     </row>
     <row r="137" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B137">
         <v>2010</v>
       </c>
       <c r="C137" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D137" t="s">
         <v>96</v>
@@ -9143,13 +9150,13 @@
     </row>
     <row r="138" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B138">
         <v>2010</v>
       </c>
       <c r="C138" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D138" t="s">
         <v>96</v>
@@ -9193,13 +9200,13 @@
     </row>
     <row r="139" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B139">
         <v>2010</v>
       </c>
       <c r="C139" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D139" t="s">
         <v>96</v>
@@ -9243,13 +9250,13 @@
     </row>
     <row r="140" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B140">
         <v>2010</v>
       </c>
       <c r="C140" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D140" t="s">
         <v>96</v>
@@ -9293,13 +9300,13 @@
     </row>
     <row r="141" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B141">
         <v>2010</v>
       </c>
       <c r="C141" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D141" t="s">
         <v>96</v>
@@ -9343,13 +9350,13 @@
     </row>
     <row r="142" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B142">
         <v>2010</v>
       </c>
       <c r="C142" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D142" t="s">
         <v>96</v>
@@ -9393,13 +9400,13 @@
     </row>
     <row r="143" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B143">
         <v>2010</v>
       </c>
       <c r="C143" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D143" t="s">
         <v>96</v>
@@ -9443,13 +9450,13 @@
     </row>
     <row r="144" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B144">
         <v>2010</v>
       </c>
       <c r="C144" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D144" t="s">
         <v>96</v>
@@ -9493,13 +9500,13 @@
     </row>
     <row r="145" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B145">
         <v>2010</v>
       </c>
       <c r="C145" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D145" t="s">
         <v>96</v>
@@ -9543,13 +9550,13 @@
     </row>
     <row r="146" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B146">
         <v>2010</v>
       </c>
       <c r="C146" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D146" t="s">
         <v>96</v>
@@ -9593,13 +9600,13 @@
     </row>
     <row r="147" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B147">
         <v>2010</v>
       </c>
       <c r="C147" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D147" t="s">
         <v>96</v>
@@ -9643,13 +9650,13 @@
     </row>
     <row r="148" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B148">
         <v>2010</v>
       </c>
       <c r="C148" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D148" t="s">
         <v>96</v>
@@ -9693,13 +9700,13 @@
     </row>
     <row r="149" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B149">
         <v>2010</v>
       </c>
       <c r="C149" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D149" t="s">
         <v>96</v>
@@ -9743,13 +9750,13 @@
     </row>
     <row r="150" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B150">
         <v>2010</v>
       </c>
       <c r="C150" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D150" t="s">
         <v>96</v>
@@ -9793,13 +9800,13 @@
     </row>
     <row r="151" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B151">
         <v>2010</v>
       </c>
       <c r="C151" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D151" t="s">
         <v>96</v>
@@ -9843,13 +9850,13 @@
     </row>
     <row r="152" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B152">
         <v>2010</v>
       </c>
       <c r="C152" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D152" t="s">
         <v>96</v>
@@ -9893,13 +9900,13 @@
     </row>
     <row r="153" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B153">
         <v>2010</v>
       </c>
       <c r="C153" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D153" t="s">
         <v>96</v>
@@ -9943,13 +9950,13 @@
     </row>
     <row r="154" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B154">
         <v>2010</v>
       </c>
       <c r="C154" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D154" t="s">
         <v>139</v>
@@ -9993,13 +10000,13 @@
     </row>
     <row r="155" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B155">
         <v>2010</v>
       </c>
       <c r="C155" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D155" t="s">
         <v>139</v>
@@ -10043,13 +10050,13 @@
     </row>
     <row r="156" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B156">
         <v>2010</v>
       </c>
       <c r="C156" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D156" t="s">
         <v>139</v>
@@ -10093,13 +10100,13 @@
     </row>
     <row r="157" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B157">
         <v>2010</v>
       </c>
       <c r="C157" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D157" t="s">
         <v>139</v>
@@ -10143,13 +10150,13 @@
     </row>
     <row r="158" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B158">
         <v>2010</v>
       </c>
       <c r="C158" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D158" t="s">
         <v>139</v>
@@ -10193,13 +10200,13 @@
     </row>
     <row r="159" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B159">
         <v>2010</v>
       </c>
       <c r="C159" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D159" t="s">
         <v>139</v>
@@ -10243,13 +10250,13 @@
     </row>
     <row r="160" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B160">
         <v>2010</v>
       </c>
       <c r="C160" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D160" t="s">
         <v>139</v>
@@ -10293,13 +10300,13 @@
     </row>
     <row r="161" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B161">
         <v>2010</v>
       </c>
       <c r="C161" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D161" t="s">
         <v>139</v>
@@ -10343,13 +10350,13 @@
     </row>
     <row r="162" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B162">
         <v>2010</v>
       </c>
       <c r="C162" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D162" t="s">
         <v>139</v>
@@ -10393,13 +10400,13 @@
     </row>
     <row r="163" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B163">
         <v>2010</v>
       </c>
       <c r="C163" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D163" t="s">
         <v>139</v>
@@ -10443,13 +10450,13 @@
     </row>
     <row r="164" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B164">
         <v>2010</v>
       </c>
       <c r="C164" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D164" t="s">
         <v>139</v>
@@ -10493,13 +10500,13 @@
     </row>
     <row r="165" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B165">
         <v>2010</v>
       </c>
       <c r="C165" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D165" t="s">
         <v>139</v>
@@ -10543,13 +10550,13 @@
     </row>
     <row r="166" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B166">
         <v>2010</v>
       </c>
       <c r="C166" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D166" t="s">
         <v>139</v>
@@ -10593,13 +10600,13 @@
     </row>
     <row r="167" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B167">
         <v>2010</v>
       </c>
       <c r="C167" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D167" t="s">
         <v>139</v>
@@ -10643,13 +10650,13 @@
     </row>
     <row r="168" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B168">
         <v>2010</v>
       </c>
       <c r="C168" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D168" t="s">
         <v>139</v>
@@ -10693,13 +10700,13 @@
     </row>
     <row r="169" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B169">
         <v>2010</v>
       </c>
       <c r="C169" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D169" t="s">
         <v>139</v>
@@ -10743,13 +10750,13 @@
     </row>
     <row r="170" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B170">
         <v>2010</v>
       </c>
       <c r="C170" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D170" t="s">
         <v>139</v>
@@ -10793,13 +10800,13 @@
     </row>
     <row r="171" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B171">
         <v>2010</v>
       </c>
       <c r="C171" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D171" t="s">
         <v>139</v>
@@ -10843,13 +10850,13 @@
     </row>
     <row r="172" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B172">
         <v>2010</v>
       </c>
       <c r="C172" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D172" t="s">
         <v>139</v>
@@ -10893,13 +10900,13 @@
     </row>
     <row r="173" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B173">
         <v>2010</v>
       </c>
       <c r="C173" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D173" t="s">
         <v>139</v>
@@ -10943,13 +10950,13 @@
     </row>
     <row r="174" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B174">
         <v>2010</v>
       </c>
       <c r="C174" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D174" t="s">
         <v>139</v>
@@ -10993,13 +11000,13 @@
     </row>
     <row r="175" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B175">
         <v>2010</v>
       </c>
       <c r="C175" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D175" t="s">
         <v>139</v>
@@ -11043,13 +11050,13 @@
     </row>
     <row r="176" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B176">
         <v>2010</v>
       </c>
       <c r="C176" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D176" t="s">
         <v>139</v>
@@ -11093,13 +11100,13 @@
     </row>
     <row r="177" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B177">
         <v>2010</v>
       </c>
       <c r="C177" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D177" t="s">
         <v>139</v>
@@ -11143,13 +11150,13 @@
     </row>
     <row r="178" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B178">
         <v>2010</v>
       </c>
       <c r="C178" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D178" t="s">
         <v>139</v>
@@ -11193,13 +11200,13 @@
     </row>
     <row r="179" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B179">
         <v>2010</v>
       </c>
       <c r="C179" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D179" t="s">
         <v>139</v>
@@ -11243,13 +11250,13 @@
     </row>
     <row r="180" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B180">
         <v>2010</v>
       </c>
       <c r="C180" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D180" t="s">
         <v>139</v>
@@ -11293,13 +11300,13 @@
     </row>
     <row r="181" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B181">
         <v>2010</v>
       </c>
       <c r="C181" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D181" t="s">
         <v>139</v>
@@ -11343,13 +11350,13 @@
     </row>
     <row r="182" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B182">
         <v>2010</v>
       </c>
       <c r="C182" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D182" t="s">
         <v>139</v>
@@ -11393,13 +11400,13 @@
     </row>
     <row r="183" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B183">
         <v>2010</v>
       </c>
       <c r="C183" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D183" t="s">
         <v>139</v>
@@ -11443,13 +11450,13 @@
     </row>
     <row r="184" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B184">
         <v>2010</v>
       </c>
       <c r="C184" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D184" t="s">
         <v>139</v>
@@ -11493,13 +11500,13 @@
     </row>
     <row r="185" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B185">
         <v>2010</v>
       </c>
       <c r="C185" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D185" t="s">
         <v>139</v>
@@ -11543,13 +11550,13 @@
     </row>
     <row r="186" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B186">
         <v>2010</v>
       </c>
       <c r="C186" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D186" t="s">
         <v>139</v>
@@ -11593,13 +11600,13 @@
     </row>
     <row r="187" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B187">
         <v>2010</v>
       </c>
       <c r="C187" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D187" t="s">
         <v>139</v>
@@ -11643,13 +11650,13 @@
     </row>
     <row r="188" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B188">
         <v>2010</v>
       </c>
       <c r="C188" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D188" t="s">
         <v>139</v>
@@ -11693,13 +11700,13 @@
     </row>
     <row r="189" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B189">
         <v>2010</v>
       </c>
       <c r="C189" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D189" t="s">
         <v>139</v>
@@ -11743,13 +11750,13 @@
     </row>
     <row r="190" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B190">
         <v>2010</v>
       </c>
       <c r="C190" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D190" t="s">
         <v>139</v>
@@ -11793,13 +11800,13 @@
     </row>
     <row r="191" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B191">
         <v>2010</v>
       </c>
       <c r="C191" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D191" t="s">
         <v>139</v>
@@ -11843,13 +11850,13 @@
     </row>
     <row r="192" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B192">
         <v>2010</v>
       </c>
       <c r="C192" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D192" t="s">
         <v>139</v>
@@ -11893,13 +11900,13 @@
     </row>
     <row r="193" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B193">
         <v>2010</v>
       </c>
       <c r="C193" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D193" t="s">
         <v>139</v>
@@ -11943,13 +11950,13 @@
     </row>
     <row r="194" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B194">
         <v>2010</v>
       </c>
       <c r="C194" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D194" t="s">
         <v>139</v>
@@ -11993,13 +12000,13 @@
     </row>
     <row r="195" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B195">
         <v>2010</v>
       </c>
       <c r="C195" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D195" t="s">
         <v>139</v>
@@ -12043,13 +12050,13 @@
     </row>
     <row r="196" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B196">
         <v>2010</v>
       </c>
       <c r="C196" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D196" t="s">
         <v>139</v>
@@ -12093,13 +12100,13 @@
     </row>
     <row r="197" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B197">
         <v>2010</v>
       </c>
       <c r="C197" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D197" t="s">
         <v>139</v>
@@ -12143,13 +12150,13 @@
     </row>
     <row r="198" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B198">
         <v>2010</v>
       </c>
       <c r="C198" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D198" t="s">
         <v>139</v>
@@ -12193,13 +12200,13 @@
     </row>
     <row r="199" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B199">
         <v>2010</v>
       </c>
       <c r="C199" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D199" t="s">
         <v>139</v>
@@ -12243,13 +12250,13 @@
     </row>
     <row r="200" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B200">
         <v>2010</v>
       </c>
       <c r="C200" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D200" t="s">
         <v>139</v>
@@ -12293,13 +12300,13 @@
     </row>
     <row r="201" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B201">
         <v>2010</v>
       </c>
       <c r="C201" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D201" t="s">
         <v>139</v>
@@ -12343,13 +12350,13 @@
     </row>
     <row r="202" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B202">
         <v>2010</v>
       </c>
       <c r="C202" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D202" t="s">
         <v>139</v>
@@ -12393,13 +12400,13 @@
     </row>
     <row r="203" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B203">
         <v>2010</v>
       </c>
       <c r="C203" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D203" t="s">
         <v>139</v>
@@ -12443,13 +12450,13 @@
     </row>
     <row r="204" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B204">
         <v>2010</v>
       </c>
       <c r="C204" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D204" t="s">
         <v>139</v>
@@ -12493,13 +12500,13 @@
     </row>
     <row r="205" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B205">
         <v>2010</v>
       </c>
       <c r="C205" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D205" t="s">
         <v>139</v>
@@ -12543,13 +12550,13 @@
     </row>
     <row r="206" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B206">
         <v>2010</v>
       </c>
       <c r="C206" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D206" t="s">
         <v>139</v>
@@ -12593,13 +12600,13 @@
     </row>
     <row r="207" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B207">
         <v>2010</v>
       </c>
       <c r="C207" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D207" t="s">
         <v>139</v>
@@ -12643,13 +12650,13 @@
     </row>
     <row r="208" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B208">
         <v>2010</v>
       </c>
       <c r="C208" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D208" t="s">
         <v>139</v>
@@ -12693,13 +12700,13 @@
     </row>
     <row r="209" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B209">
         <v>2010</v>
       </c>
       <c r="C209" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D209" t="s">
         <v>139</v>
@@ -12743,13 +12750,13 @@
     </row>
     <row r="210" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B210">
         <v>2010</v>
       </c>
       <c r="C210" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D210" t="s">
         <v>139</v>
@@ -12793,13 +12800,13 @@
     </row>
     <row r="211" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B211">
         <v>2010</v>
       </c>
       <c r="C211" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D211" t="s">
         <v>139</v>
@@ -12843,13 +12850,13 @@
     </row>
     <row r="212" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B212">
         <v>2010</v>
       </c>
       <c r="C212" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D212" t="s">
         <v>139</v>
@@ -12893,13 +12900,13 @@
     </row>
     <row r="213" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B213">
         <v>2010</v>
       </c>
       <c r="C213" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D213" t="s">
         <v>139</v>
@@ -12943,13 +12950,13 @@
     </row>
     <row r="214" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B214">
         <v>2010</v>
       </c>
       <c r="C214" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D214" t="s">
         <v>139</v>
@@ -12993,13 +13000,13 @@
     </row>
     <row r="215" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B215">
         <v>2010</v>
       </c>
       <c r="C215" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D215" t="s">
         <v>139</v>
@@ -13043,13 +13050,13 @@
     </row>
     <row r="216" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B216">
         <v>2010</v>
       </c>
       <c r="C216" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D216" t="s">
         <v>139</v>
@@ -13093,13 +13100,13 @@
     </row>
     <row r="217" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B217">
         <v>2010</v>
       </c>
       <c r="C217" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D217" t="s">
         <v>139</v>
@@ -13143,13 +13150,13 @@
     </row>
     <row r="218" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B218">
         <v>2010</v>
       </c>
       <c r="C218" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D218" t="s">
         <v>139</v>
@@ -13193,13 +13200,13 @@
     </row>
     <row r="219" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B219">
         <v>2010</v>
       </c>
       <c r="C219" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D219" t="s">
         <v>139</v>
@@ -13243,13 +13250,13 @@
     </row>
     <row r="220" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B220">
         <v>2010</v>
       </c>
       <c r="C220" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D220" t="s">
         <v>139</v>
@@ -13293,13 +13300,13 @@
     </row>
     <row r="221" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B221">
         <v>2010</v>
       </c>
       <c r="C221" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D221" t="s">
         <v>96</v>
@@ -13343,13 +13350,13 @@
     </row>
     <row r="222" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B222">
         <v>2010</v>
       </c>
       <c r="C222" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D222" t="s">
         <v>96</v>
@@ -13393,13 +13400,13 @@
     </row>
     <row r="223" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B223">
         <v>2010</v>
       </c>
       <c r="C223" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D223" t="s">
         <v>96</v>
@@ -13443,13 +13450,13 @@
     </row>
     <row r="224" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B224">
         <v>2010</v>
       </c>
       <c r="C224" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D224" t="s">
         <v>96</v>
@@ -13493,13 +13500,13 @@
     </row>
     <row r="225" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B225">
         <v>2010</v>
       </c>
       <c r="C225" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D225" t="s">
         <v>96</v>
@@ -13543,13 +13550,13 @@
     </row>
     <row r="226" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B226">
         <v>2010</v>
       </c>
       <c r="C226" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D226" t="s">
         <v>96</v>
@@ -13593,13 +13600,13 @@
     </row>
     <row r="227" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B227">
         <v>2010</v>
       </c>
       <c r="C227" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D227" t="s">
         <v>96</v>
@@ -13643,13 +13650,13 @@
     </row>
     <row r="228" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B228">
         <v>2010</v>
       </c>
       <c r="C228" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D228" t="s">
         <v>96</v>
@@ -13693,13 +13700,13 @@
     </row>
     <row r="229" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B229">
         <v>2010</v>
       </c>
       <c r="C229" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D229" t="s">
         <v>96</v>
@@ -13743,13 +13750,13 @@
     </row>
     <row r="230" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B230">
         <v>2010</v>
       </c>
       <c r="C230" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D230" t="s">
         <v>96</v>
@@ -13793,13 +13800,13 @@
     </row>
     <row r="231" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B231">
         <v>2010</v>
       </c>
       <c r="C231" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D231" t="s">
         <v>96</v>
@@ -13843,13 +13850,13 @@
     </row>
     <row r="232" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B232">
         <v>2010</v>
       </c>
       <c r="C232" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D232" t="s">
         <v>96</v>
@@ -13893,13 +13900,13 @@
     </row>
     <row r="233" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B233">
         <v>2010</v>
       </c>
       <c r="C233" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D233" t="s">
         <v>96</v>
@@ -13943,13 +13950,13 @@
     </row>
     <row r="234" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B234">
         <v>2010</v>
       </c>
       <c r="C234" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D234" t="s">
         <v>96</v>
@@ -13993,13 +14000,13 @@
     </row>
     <row r="235" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B235">
         <v>2010</v>
       </c>
       <c r="C235" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D235" t="s">
         <v>96</v>
@@ -14043,13 +14050,13 @@
     </row>
     <row r="236" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B236">
         <v>2010</v>
       </c>
       <c r="C236" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D236" t="s">
         <v>96</v>
@@ -14093,13 +14100,13 @@
     </row>
     <row r="237" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B237">
         <v>2010</v>
       </c>
       <c r="C237" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D237" t="s">
         <v>96</v>
@@ -14143,13 +14150,13 @@
     </row>
     <row r="238" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B238">
         <v>2010</v>
       </c>
       <c r="C238" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D238" t="s">
         <v>139</v>
@@ -14193,13 +14200,13 @@
     </row>
     <row r="239" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B239">
         <v>2010</v>
       </c>
       <c r="C239" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D239" t="s">
         <v>139</v>
@@ -14243,13 +14250,13 @@
     </row>
     <row r="240" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B240">
         <v>2010</v>
       </c>
       <c r="C240" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D240" t="s">
         <v>139</v>
@@ -14293,13 +14300,13 @@
     </row>
     <row r="241" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B241">
         <v>2010</v>
       </c>
       <c r="C241" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D241" t="s">
         <v>139</v>
@@ -14343,13 +14350,13 @@
     </row>
     <row r="242" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B242">
         <v>2010</v>
       </c>
       <c r="C242" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D242" t="s">
         <v>139</v>
@@ -14393,13 +14400,13 @@
     </row>
     <row r="243" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B243">
         <v>2010</v>
       </c>
       <c r="C243" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D243" t="s">
         <v>139</v>
@@ -14443,13 +14450,13 @@
     </row>
     <row r="244" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B244">
         <v>2010</v>
       </c>
       <c r="C244" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D244" t="s">
         <v>139</v>
@@ -14493,13 +14500,13 @@
     </row>
     <row r="245" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B245">
         <v>2010</v>
       </c>
       <c r="C245" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D245" t="s">
         <v>139</v>
@@ -14543,13 +14550,13 @@
     </row>
     <row r="246" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B246">
         <v>2010</v>
       </c>
       <c r="C246" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D246" t="s">
         <v>139</v>
@@ -14593,13 +14600,13 @@
     </row>
     <row r="247" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B247">
         <v>2010</v>
       </c>
       <c r="C247" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D247" t="s">
         <v>139</v>
@@ -14643,13 +14650,13 @@
     </row>
     <row r="248" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B248">
         <v>2010</v>
       </c>
       <c r="C248" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D248" t="s">
         <v>139</v>
@@ -14693,13 +14700,13 @@
     </row>
     <row r="249" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B249">
         <v>2010</v>
       </c>
       <c r="C249" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D249" t="s">
         <v>139</v>
@@ -14743,13 +14750,13 @@
     </row>
     <row r="250" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B250">
         <v>2010</v>
       </c>
       <c r="C250" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D250" t="s">
         <v>139</v>
@@ -14793,13 +14800,13 @@
     </row>
     <row r="251" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B251">
         <v>2010</v>
       </c>
       <c r="C251" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D251" t="s">
         <v>139</v>
@@ -14843,13 +14850,13 @@
     </row>
     <row r="252" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B252">
         <v>2010</v>
       </c>
       <c r="C252" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D252" t="s">
         <v>139</v>
@@ -14893,13 +14900,13 @@
     </row>
     <row r="253" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B253">
         <v>2010</v>
       </c>
       <c r="C253" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D253" t="s">
         <v>139</v>
@@ -14943,13 +14950,13 @@
     </row>
     <row r="254" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B254">
         <v>2010</v>
       </c>
       <c r="C254" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D254" t="s">
         <v>139</v>
@@ -14993,13 +15000,13 @@
     </row>
     <row r="255" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B255">
         <v>2010</v>
       </c>
       <c r="C255" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D255" t="s">
         <v>139</v>
@@ -15043,13 +15050,13 @@
     </row>
     <row r="256" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B256">
         <v>2010</v>
       </c>
       <c r="C256" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D256" t="s">
         <v>139</v>
@@ -15093,13 +15100,13 @@
     </row>
     <row r="257" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B257">
         <v>2010</v>
       </c>
       <c r="C257" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D257" t="s">
         <v>139</v>
@@ -15143,13 +15150,13 @@
     </row>
     <row r="258" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B258">
         <v>2010</v>
       </c>
       <c r="C258" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D258" t="s">
         <v>139</v>
@@ -15193,13 +15200,13 @@
     </row>
     <row r="259" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B259">
         <v>2010</v>
       </c>
       <c r="C259" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D259" t="s">
         <v>139</v>
@@ -15243,13 +15250,13 @@
     </row>
     <row r="260" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B260">
         <v>2010</v>
       </c>
       <c r="C260" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D260" t="s">
         <v>139</v>
@@ -15293,13 +15300,13 @@
     </row>
     <row r="261" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B261">
         <v>2010</v>
       </c>
       <c r="C261" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D261" t="s">
         <v>139</v>
@@ -15343,13 +15350,13 @@
     </row>
     <row r="262" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B262">
         <v>2010</v>
       </c>
       <c r="C262" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D262" t="s">
         <v>139</v>
@@ -15393,13 +15400,13 @@
     </row>
     <row r="263" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B263">
         <v>2010</v>
       </c>
       <c r="C263" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D263" t="s">
         <v>139</v>
@@ -15443,13 +15450,13 @@
     </row>
     <row r="264" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B264">
         <v>2010</v>
       </c>
       <c r="C264" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D264" t="s">
         <v>139</v>
@@ -15493,13 +15500,13 @@
     </row>
     <row r="265" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B265">
         <v>2010</v>
       </c>
       <c r="C265" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D265" t="s">
         <v>139</v>
@@ -15543,13 +15550,13 @@
     </row>
     <row r="266" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B266">
         <v>2010</v>
       </c>
       <c r="C266" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D266" t="s">
         <v>139</v>
@@ -15593,13 +15600,13 @@
     </row>
     <row r="267" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B267">
         <v>2010</v>
       </c>
       <c r="C267" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D267" t="s">
         <v>139</v>
@@ -15643,13 +15650,13 @@
     </row>
     <row r="268" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B268">
         <v>2010</v>
       </c>
       <c r="C268" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D268" t="s">
         <v>139</v>
@@ -15693,13 +15700,13 @@
     </row>
     <row r="269" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B269">
         <v>2010</v>
       </c>
       <c r="C269" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D269" t="s">
         <v>139</v>
@@ -15743,13 +15750,13 @@
     </row>
     <row r="270" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B270">
         <v>2010</v>
       </c>
       <c r="C270" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D270" t="s">
         <v>139</v>
@@ -15793,13 +15800,13 @@
     </row>
     <row r="271" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B271">
         <v>2010</v>
       </c>
       <c r="C271" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D271" t="s">
         <v>139</v>
@@ -15843,13 +15850,13 @@
     </row>
     <row r="272" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B272">
         <v>2010</v>
       </c>
       <c r="C272" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D272" t="s">
         <v>96</v>
@@ -15893,13 +15900,13 @@
     </row>
     <row r="273" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B273">
         <v>2010</v>
       </c>
       <c r="C273" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D273" t="s">
         <v>96</v>
@@ -15943,13 +15950,13 @@
     </row>
     <row r="274" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B274">
         <v>2010</v>
       </c>
       <c r="C274" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D274" t="s">
         <v>96</v>
@@ -15993,13 +16000,13 @@
     </row>
     <row r="275" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B275">
         <v>2010</v>
       </c>
       <c r="C275" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D275" t="s">
         <v>96</v>
@@ -16043,13 +16050,13 @@
     </row>
     <row r="276" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B276">
         <v>2010</v>
       </c>
       <c r="C276" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D276" t="s">
         <v>96</v>
@@ -16093,13 +16100,13 @@
     </row>
     <row r="277" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B277">
         <v>2010</v>
       </c>
       <c r="C277" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D277" t="s">
         <v>96</v>
@@ -16143,13 +16150,13 @@
     </row>
     <row r="278" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B278">
         <v>2010</v>
       </c>
       <c r="C278" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D278" t="s">
         <v>96</v>
@@ -16193,13 +16200,13 @@
     </row>
     <row r="279" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B279">
         <v>2010</v>
       </c>
       <c r="C279" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D279" t="s">
         <v>96</v>
@@ -16243,13 +16250,13 @@
     </row>
     <row r="280" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B280">
         <v>2010</v>
       </c>
       <c r="C280" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D280" t="s">
         <v>139</v>
@@ -16293,13 +16300,13 @@
     </row>
     <row r="281" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B281">
         <v>2010</v>
       </c>
       <c r="C281" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D281" t="s">
         <v>139</v>
@@ -16343,13 +16350,13 @@
     </row>
     <row r="282" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B282">
         <v>2010</v>
       </c>
       <c r="C282" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D282" t="s">
         <v>139</v>
@@ -16393,13 +16400,13 @@
     </row>
     <row r="283" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B283">
         <v>2010</v>
       </c>
       <c r="C283" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D283" t="s">
         <v>139</v>
@@ -16443,13 +16450,13 @@
     </row>
     <row r="284" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B284">
         <v>2010</v>
       </c>
       <c r="C284" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D284" t="s">
         <v>139</v>
@@ -16493,13 +16500,13 @@
     </row>
     <row r="285" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B285">
         <v>2010</v>
       </c>
       <c r="C285" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D285" t="s">
         <v>139</v>
@@ -16543,13 +16550,13 @@
     </row>
     <row r="286" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B286">
         <v>2010</v>
       </c>
       <c r="C286" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D286" t="s">
         <v>139</v>
@@ -16593,13 +16600,13 @@
     </row>
     <row r="287" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B287">
         <v>2010</v>
       </c>
       <c r="C287" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D287" t="s">
         <v>139</v>
@@ -16643,13 +16650,13 @@
     </row>
     <row r="288" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B288">
         <v>2010</v>
       </c>
       <c r="C288" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D288" t="s">
         <v>139</v>
@@ -16693,13 +16700,13 @@
     </row>
     <row r="289" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B289">
         <v>2010</v>
       </c>
       <c r="C289" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D289" t="s">
         <v>139</v>
@@ -16743,13 +16750,13 @@
     </row>
     <row r="290" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B290">
         <v>2010</v>
       </c>
       <c r="C290" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D290" t="s">
         <v>139</v>
@@ -16793,13 +16800,13 @@
     </row>
     <row r="291" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B291">
         <v>2010</v>
       </c>
       <c r="C291" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D291" t="s">
         <v>139</v>
@@ -16843,13 +16850,13 @@
     </row>
     <row r="292" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B292">
         <v>2010</v>
       </c>
       <c r="C292" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D292" t="s">
         <v>139</v>
@@ -16893,13 +16900,13 @@
     </row>
     <row r="293" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B293">
         <v>2010</v>
       </c>
       <c r="C293" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D293" t="s">
         <v>139</v>
@@ -16943,13 +16950,13 @@
     </row>
     <row r="294" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B294">
         <v>2010</v>
       </c>
       <c r="C294" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D294" t="s">
         <v>139</v>
@@ -16993,13 +17000,13 @@
     </row>
     <row r="295" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B295">
         <v>2010</v>
       </c>
       <c r="C295" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D295" t="s">
         <v>139</v>
@@ -17043,13 +17050,13 @@
     </row>
     <row r="296" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B296">
         <v>2010</v>
       </c>
       <c r="C296" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D296" t="s">
         <v>139</v>
@@ -17093,13 +17100,13 @@
     </row>
     <row r="297" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B297">
         <v>2010</v>
       </c>
       <c r="C297" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D297" t="s">
         <v>139</v>
@@ -17143,13 +17150,13 @@
     </row>
     <row r="298" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B298">
         <v>2010</v>
       </c>
       <c r="C298" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D298" t="s">
         <v>139</v>
@@ -17193,13 +17200,13 @@
     </row>
     <row r="299" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B299">
         <v>2010</v>
       </c>
       <c r="C299" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D299" t="s">
         <v>139</v>
@@ -17243,13 +17250,13 @@
     </row>
     <row r="300" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B300">
         <v>2010</v>
       </c>
       <c r="C300" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D300" t="s">
         <v>139</v>
@@ -17293,13 +17300,13 @@
     </row>
     <row r="301" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B301">
         <v>2010</v>
       </c>
       <c r="C301" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D301" t="s">
         <v>139</v>
@@ -17343,13 +17350,13 @@
     </row>
     <row r="302" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B302">
         <v>2010</v>
       </c>
       <c r="C302" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D302" t="s">
         <v>139</v>
@@ -17393,13 +17400,13 @@
     </row>
     <row r="303" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B303">
         <v>2010</v>
       </c>
       <c r="C303" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D303" t="s">
         <v>139</v>
@@ -17443,13 +17450,13 @@
     </row>
     <row r="304" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B304">
         <v>2010</v>
       </c>
       <c r="C304" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D304" t="s">
         <v>139</v>
@@ -17493,13 +17500,13 @@
     </row>
     <row r="305" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B305">
         <v>2010</v>
       </c>
       <c r="C305" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D305" t="s">
         <v>139</v>
@@ -17543,13 +17550,13 @@
     </row>
     <row r="306" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B306">
         <v>2010</v>
       </c>
       <c r="C306" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D306" t="s">
         <v>139</v>
@@ -17593,13 +17600,13 @@
     </row>
     <row r="307" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B307">
         <v>2010</v>
       </c>
       <c r="C307" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D307" t="s">
         <v>96</v>
@@ -17643,13 +17650,13 @@
     </row>
     <row r="308" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B308">
         <v>2010</v>
       </c>
       <c r="C308" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D308" t="s">
         <v>96</v>
@@ -17693,13 +17700,13 @@
     </row>
     <row r="309" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B309">
         <v>2010</v>
       </c>
       <c r="C309" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D309" t="s">
         <v>96</v>
@@ -17743,13 +17750,13 @@
     </row>
     <row r="310" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B310">
         <v>2010</v>
       </c>
       <c r="C310" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D310" t="s">
         <v>96</v>
@@ -17793,13 +17800,13 @@
     </row>
     <row r="311" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B311">
         <v>2010</v>
       </c>
       <c r="C311" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D311" t="s">
         <v>96</v>
@@ -17843,13 +17850,13 @@
     </row>
     <row r="312" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B312">
         <v>2010</v>
       </c>
       <c r="C312" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D312" t="s">
         <v>96</v>
@@ -17893,13 +17900,13 @@
     </row>
     <row r="313" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B313">
         <v>2010</v>
       </c>
       <c r="C313" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D313" t="s">
         <v>96</v>
@@ -17943,13 +17950,13 @@
     </row>
     <row r="314" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B314">
         <v>2010</v>
       </c>
       <c r="C314" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D314" t="s">
         <v>96</v>
@@ -17993,13 +18000,13 @@
     </row>
     <row r="315" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B315">
         <v>2010</v>
       </c>
       <c r="C315" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D315" t="s">
         <v>96</v>
@@ -18043,13 +18050,13 @@
     </row>
     <row r="316" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B316">
         <v>2010</v>
       </c>
       <c r="C316" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D316" t="s">
         <v>96</v>
@@ -18093,13 +18100,13 @@
     </row>
     <row r="317" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B317">
         <v>2010</v>
       </c>
       <c r="C317" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D317" t="s">
         <v>96</v>
@@ -18143,13 +18150,13 @@
     </row>
     <row r="318" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B318">
         <v>2010</v>
       </c>
       <c r="C318" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D318" t="s">
         <v>96</v>
@@ -18193,13 +18200,13 @@
     </row>
     <row r="319" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B319">
         <v>2010</v>
       </c>
       <c r="C319" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D319" t="s">
         <v>96</v>
@@ -18243,13 +18250,13 @@
     </row>
     <row r="320" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B320">
         <v>2010</v>
       </c>
       <c r="C320" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D320" t="s">
         <v>96</v>
@@ -18293,13 +18300,13 @@
     </row>
     <row r="321" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B321">
         <v>2010</v>
       </c>
       <c r="C321" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D321" t="s">
         <v>96</v>
@@ -18343,13 +18350,13 @@
     </row>
     <row r="322" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B322">
         <v>2010</v>
       </c>
       <c r="C322" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D322" t="s">
         <v>139</v>
@@ -18393,13 +18400,13 @@
     </row>
     <row r="323" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B323">
         <v>2010</v>
       </c>
       <c r="C323" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D323" t="s">
         <v>139</v>
@@ -18443,13 +18450,13 @@
     </row>
     <row r="324" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B324">
         <v>2010</v>
       </c>
       <c r="C324" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D324" t="s">
         <v>139</v>
@@ -18493,13 +18500,13 @@
     </row>
     <row r="325" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B325">
         <v>2010</v>
       </c>
       <c r="C325" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D325" t="s">
         <v>139</v>
@@ -18543,13 +18550,13 @@
     </row>
     <row r="326" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B326">
         <v>2010</v>
       </c>
       <c r="C326" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D326" t="s">
         <v>139</v>
@@ -18593,13 +18600,13 @@
     </row>
     <row r="327" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B327">
         <v>2010</v>
       </c>
       <c r="C327" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D327" t="s">
         <v>139</v>
@@ -18643,13 +18650,13 @@
     </row>
     <row r="328" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B328">
         <v>2010</v>
       </c>
       <c r="C328" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D328" t="s">
         <v>139</v>
@@ -18693,13 +18700,13 @@
     </row>
     <row r="329" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B329">
         <v>2010</v>
       </c>
       <c r="C329" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D329" t="s">
         <v>139</v>
@@ -18743,13 +18750,13 @@
     </row>
     <row r="330" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B330">
         <v>2010</v>
       </c>
       <c r="C330" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D330" t="s">
         <v>139</v>
@@ -18793,13 +18800,13 @@
     </row>
     <row r="331" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B331">
         <v>2010</v>
       </c>
       <c r="C331" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D331" t="s">
         <v>139</v>
@@ -18843,13 +18850,13 @@
     </row>
     <row r="332" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B332">
         <v>2010</v>
       </c>
       <c r="C332" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D332" t="s">
         <v>139</v>
@@ -18893,13 +18900,13 @@
     </row>
     <row r="333" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B333">
         <v>2010</v>
       </c>
       <c r="C333" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D333" t="s">
         <v>139</v>
@@ -18943,13 +18950,13 @@
     </row>
     <row r="334" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B334">
         <v>2010</v>
       </c>
       <c r="C334" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D334" t="s">
         <v>139</v>
@@ -18993,13 +19000,13 @@
     </row>
     <row r="335" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B335">
         <v>2010</v>
       </c>
       <c r="C335" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D335" t="s">
         <v>139</v>
@@ -19043,13 +19050,13 @@
     </row>
     <row r="336" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B336">
         <v>2010</v>
       </c>
       <c r="C336" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D336" t="s">
         <v>139</v>
@@ -19093,13 +19100,13 @@
     </row>
     <row r="337" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B337">
         <v>2010</v>
       </c>
       <c r="C337" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D337" t="s">
         <v>139</v>
@@ -19143,13 +19150,13 @@
     </row>
     <row r="338" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B338">
         <v>2010</v>
       </c>
       <c r="C338" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D338" t="s">
         <v>139</v>
@@ -19193,13 +19200,13 @@
     </row>
     <row r="339" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B339">
         <v>2010</v>
       </c>
       <c r="C339" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D339" t="s">
         <v>139</v>
@@ -19243,13 +19250,13 @@
     </row>
     <row r="340" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B340">
         <v>2010</v>
       </c>
       <c r="C340" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D340" t="s">
         <v>139</v>
@@ -19293,13 +19300,13 @@
     </row>
     <row r="341" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B341">
         <v>2010</v>
       </c>
       <c r="C341" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D341" t="s">
         <v>139</v>
@@ -19343,13 +19350,13 @@
     </row>
     <row r="342" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B342">
         <v>2010</v>
       </c>
       <c r="C342" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D342" t="s">
         <v>139</v>
@@ -19393,13 +19400,13 @@
     </row>
     <row r="343" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B343">
         <v>2010</v>
       </c>
       <c r="C343" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D343" t="s">
         <v>96</v>
@@ -19443,13 +19450,13 @@
     </row>
     <row r="344" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B344">
         <v>2010</v>
       </c>
       <c r="C344" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D344" t="s">
         <v>96</v>
@@ -19493,13 +19500,13 @@
     </row>
     <row r="345" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B345">
         <v>2010</v>
       </c>
       <c r="C345" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D345" t="s">
         <v>96</v>
@@ -19543,13 +19550,13 @@
     </row>
     <row r="346" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B346">
         <v>2010</v>
       </c>
       <c r="C346" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D346" t="s">
         <v>96</v>
@@ -19593,13 +19600,13 @@
     </row>
     <row r="347" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B347">
         <v>2010</v>
       </c>
       <c r="C347" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D347" t="s">
         <v>96</v>
@@ -19643,13 +19650,13 @@
     </row>
     <row r="348" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B348">
         <v>2010</v>
       </c>
       <c r="C348" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D348" t="s">
         <v>96</v>
@@ -19693,13 +19700,13 @@
     </row>
     <row r="349" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B349">
         <v>2010</v>
       </c>
       <c r="C349" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D349" t="s">
         <v>96</v>
@@ -19743,13 +19750,13 @@
     </row>
     <row r="350" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B350">
         <v>2010</v>
       </c>
       <c r="C350" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D350" t="s">
         <v>96</v>
@@ -19793,13 +19800,13 @@
     </row>
     <row r="351" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B351">
         <v>2010</v>
       </c>
       <c r="C351" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D351" t="s">
         <v>96</v>
@@ -19843,13 +19850,13 @@
     </row>
     <row r="352" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B352">
         <v>2010</v>
       </c>
       <c r="C352" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D352" t="s">
         <v>96</v>
@@ -19893,13 +19900,13 @@
     </row>
     <row r="353" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B353">
         <v>2010</v>
       </c>
       <c r="C353" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D353" t="s">
         <v>96</v>
@@ -19943,13 +19950,13 @@
     </row>
     <row r="354" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B354">
         <v>2010</v>
       </c>
       <c r="C354" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D354" t="s">
         <v>96</v>
@@ -19993,13 +20000,13 @@
     </row>
     <row r="355" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B355">
         <v>2010</v>
       </c>
       <c r="C355" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D355" t="s">
         <v>96</v>
@@ -20043,13 +20050,13 @@
     </row>
     <row r="356" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B356">
         <v>2010</v>
       </c>
       <c r="C356" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D356" t="s">
         <v>96</v>
@@ -20093,13 +20100,13 @@
     </row>
     <row r="357" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B357">
         <v>2010</v>
       </c>
       <c r="C357" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D357" t="s">
         <v>96</v>
@@ -20143,13 +20150,13 @@
     </row>
     <row r="358" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B358">
         <v>2010</v>
       </c>
       <c r="C358" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D358" t="s">
         <v>96</v>
@@ -20193,13 +20200,13 @@
     </row>
     <row r="359" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B359">
         <v>2010</v>
       </c>
       <c r="C359" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D359" t="s">
         <v>96</v>
@@ -20243,13 +20250,13 @@
     </row>
     <row r="360" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B360">
         <v>2010</v>
       </c>
       <c r="C360" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D360" t="s">
         <v>96</v>
@@ -20293,13 +20300,13 @@
     </row>
     <row r="361" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B361">
         <v>2010</v>
       </c>
       <c r="C361" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D361" t="s">
         <v>96</v>
@@ -20343,13 +20350,13 @@
     </row>
     <row r="362" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B362">
         <v>2010</v>
       </c>
       <c r="C362" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D362" t="s">
         <v>96</v>
@@ -20393,13 +20400,13 @@
     </row>
     <row r="363" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B363">
         <v>2010</v>
       </c>
       <c r="C363" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D363" t="s">
         <v>139</v>
@@ -20443,13 +20450,13 @@
     </row>
     <row r="364" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B364">
         <v>2010</v>
       </c>
       <c r="C364" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D364" t="s">
         <v>139</v>
@@ -20493,13 +20500,13 @@
     </row>
     <row r="365" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B365">
         <v>2010</v>
       </c>
       <c r="C365" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D365" t="s">
         <v>139</v>
@@ -20543,13 +20550,13 @@
     </row>
     <row r="366" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B366">
         <v>2010</v>
       </c>
       <c r="C366" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D366" t="s">
         <v>96</v>
@@ -20593,13 +20600,13 @@
     </row>
     <row r="367" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B367">
         <v>2010</v>
       </c>
       <c r="C367" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D367" t="s">
         <v>96</v>
@@ -20643,13 +20650,13 @@
     </row>
     <row r="368" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B368">
         <v>2010</v>
       </c>
       <c r="C368" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D368" t="s">
         <v>96</v>
@@ -20693,13 +20700,13 @@
     </row>
     <row r="369" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B369">
         <v>2010</v>
       </c>
       <c r="C369" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D369" t="s">
         <v>96</v>
@@ -20743,13 +20750,13 @@
     </row>
     <row r="370" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B370">
         <v>2010</v>
       </c>
       <c r="C370" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D370" t="s">
         <v>96</v>
@@ -20793,13 +20800,13 @@
     </row>
     <row r="371" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B371">
         <v>2010</v>
       </c>
       <c r="C371" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D371" t="s">
         <v>96</v>
@@ -20843,13 +20850,13 @@
     </row>
     <row r="372" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B372">
         <v>2010</v>
       </c>
       <c r="C372" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D372" t="s">
         <v>96</v>
@@ -20893,13 +20900,13 @@
     </row>
     <row r="373" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B373">
         <v>2010</v>
       </c>
       <c r="C373" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D373" t="s">
         <v>96</v>
@@ -20943,13 +20950,13 @@
     </row>
     <row r="374" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B374">
         <v>2010</v>
       </c>
       <c r="C374" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D374" t="s">
         <v>96</v>
@@ -20993,13 +21000,13 @@
     </row>
     <row r="375" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B375">
         <v>2010</v>
       </c>
       <c r="C375" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D375" t="s">
         <v>96</v>
@@ -21043,13 +21050,13 @@
     </row>
     <row r="376" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B376">
         <v>2010</v>
       </c>
       <c r="C376" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D376" t="s">
         <v>96</v>
@@ -21093,13 +21100,13 @@
     </row>
     <row r="377" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B377">
         <v>2010</v>
       </c>
       <c r="C377" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D377" t="s">
         <v>96</v>
@@ -21143,13 +21150,13 @@
     </row>
     <row r="378" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B378">
         <v>2010</v>
       </c>
       <c r="C378" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D378" t="s">
         <v>139</v>
@@ -21193,13 +21200,13 @@
     </row>
     <row r="379" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B379">
         <v>2010</v>
       </c>
       <c r="C379" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D379" t="s">
         <v>139</v>
@@ -21243,13 +21250,13 @@
     </row>
     <row r="380" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B380">
         <v>2010</v>
       </c>
       <c r="C380" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D380" t="s">
         <v>139</v>
@@ -21293,13 +21300,13 @@
     </row>
     <row r="381" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B381">
         <v>2010</v>
       </c>
       <c r="C381" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D381" t="s">
         <v>139</v>
@@ -21343,13 +21350,13 @@
     </row>
     <row r="382" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B382">
         <v>2010</v>
       </c>
       <c r="C382" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D382" t="s">
         <v>139</v>
@@ -21393,13 +21400,13 @@
     </row>
     <row r="383" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B383">
         <v>2010</v>
       </c>
       <c r="C383" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D383" t="s">
         <v>139</v>
@@ -21443,13 +21450,13 @@
     </row>
     <row r="384" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B384">
         <v>2010</v>
       </c>
       <c r="C384" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E384">
         <v>47.354024785084292</v>
@@ -21490,13 +21497,13 @@
     </row>
     <row r="385" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B385">
         <v>2010</v>
       </c>
       <c r="C385" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D385" t="s">
         <v>139</v>
@@ -21540,13 +21547,13 @@
     </row>
     <row r="386" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B386">
         <v>2010</v>
       </c>
       <c r="C386" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D386" t="s">
         <v>139</v>
@@ -21590,13 +21597,13 @@
     </row>
     <row r="387" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B387">
         <v>2010</v>
       </c>
       <c r="C387" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D387" t="s">
         <v>139</v>
@@ -21640,13 +21647,13 @@
     </row>
     <row r="388" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B388">
         <v>2010</v>
       </c>
       <c r="C388" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D388" t="s">
         <v>139</v>
@@ -21690,13 +21697,13 @@
     </row>
     <row r="389" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B389">
         <v>2010</v>
       </c>
       <c r="C389" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D389" t="s">
         <v>139</v>
@@ -21740,13 +21747,13 @@
     </row>
     <row r="390" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B390">
         <v>2010</v>
       </c>
       <c r="C390" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D390" t="s">
         <v>139</v>
@@ -21790,13 +21797,13 @@
     </row>
     <row r="391" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B391">
         <v>2010</v>
       </c>
       <c r="C391" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D391" t="s">
         <v>139</v>
@@ -21845,8 +21852,8 @@
       <c r="B392">
         <v>2006</v>
       </c>
-      <c r="C392" t="s">
-        <v>140</v>
+      <c r="C392" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E392">
         <v>50.215499999999999</v>
@@ -21889,8 +21896,8 @@
       <c r="B393">
         <v>2006</v>
       </c>
-      <c r="C393" t="s">
-        <v>140</v>
+      <c r="C393" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E393">
         <v>53.144500000000001</v>
@@ -21933,8 +21940,8 @@
       <c r="B394">
         <v>2006</v>
       </c>
-      <c r="C394" t="s">
-        <v>140</v>
+      <c r="C394" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E394">
         <v>52.321399999999997</v>
@@ -21977,8 +21984,8 @@
       <c r="B395">
         <v>2006</v>
       </c>
-      <c r="C395" t="s">
-        <v>140</v>
+      <c r="C395" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E395">
         <v>52.1509</v>
@@ -22021,8 +22028,8 @@
       <c r="B396">
         <v>2006</v>
       </c>
-      <c r="C396" t="s">
-        <v>140</v>
+      <c r="C396" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E396">
         <v>50.286900000000003</v>
@@ -22065,8 +22072,8 @@
       <c r="B397">
         <v>2006</v>
       </c>
-      <c r="C397" t="s">
-        <v>140</v>
+      <c r="C397" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E397">
         <v>50.713700000000003</v>
@@ -22109,8 +22116,8 @@
       <c r="B398">
         <v>2006</v>
       </c>
-      <c r="C398" t="s">
-        <v>140</v>
+      <c r="C398" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E398">
         <v>52.264400000000002</v>
@@ -22153,8 +22160,8 @@
       <c r="B399">
         <v>2006</v>
       </c>
-      <c r="C399" t="s">
-        <v>140</v>
+      <c r="C399" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E399">
         <v>51.719200000000001</v>
@@ -22197,8 +22204,8 @@
       <c r="B400">
         <v>2006</v>
       </c>
-      <c r="C400" t="s">
-        <v>140</v>
+      <c r="C400" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E400">
         <v>51.775300000000001</v>
@@ -22241,8 +22248,8 @@
       <c r="B401">
         <v>2006</v>
       </c>
-      <c r="C401" t="s">
-        <v>140</v>
+      <c r="C401" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E401">
         <v>51.429099999999998</v>
@@ -22285,8 +22292,8 @@
       <c r="B402">
         <v>2006</v>
       </c>
-      <c r="C402" t="s">
-        <v>140</v>
+      <c r="C402" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E402">
         <v>51.997500000000002</v>
@@ -22329,8 +22336,8 @@
       <c r="B403">
         <v>2006</v>
       </c>
-      <c r="C403" t="s">
-        <v>140</v>
+      <c r="C403" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E403">
         <v>51.853000000000002</v>
@@ -22373,8 +22380,8 @@
       <c r="B404">
         <v>2006</v>
       </c>
-      <c r="C404" t="s">
-        <v>140</v>
+      <c r="C404" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E404">
         <v>52.081499999999998</v>
@@ -22417,8 +22424,8 @@
       <c r="B405">
         <v>2006</v>
       </c>
-      <c r="C405" t="s">
-        <v>140</v>
+      <c r="C405" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E405">
         <v>50.387599999999999</v>
@@ -22461,8 +22468,8 @@
       <c r="B406">
         <v>2006</v>
       </c>
-      <c r="C406" t="s">
-        <v>140</v>
+      <c r="C406" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E406">
         <v>51.983800000000002</v>
@@ -22505,8 +22512,8 @@
       <c r="B407">
         <v>2006</v>
       </c>
-      <c r="C407" t="s">
-        <v>140</v>
+      <c r="C407" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D407" t="s">
         <v>96</v>
@@ -22552,8 +22559,8 @@
       <c r="B408">
         <v>2006</v>
       </c>
-      <c r="C408" t="s">
-        <v>140</v>
+      <c r="C408" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D408" t="s">
         <v>96</v>
@@ -22599,8 +22606,8 @@
       <c r="B409">
         <v>2006</v>
       </c>
-      <c r="C409" t="s">
-        <v>140</v>
+      <c r="C409" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E409">
         <v>50.154499999999999</v>
@@ -22643,8 +22650,8 @@
       <c r="B410">
         <v>2006</v>
       </c>
-      <c r="C410" t="s">
-        <v>140</v>
+      <c r="C410" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E410">
         <v>49.400399999999998</v>
@@ -22687,8 +22694,8 @@
       <c r="B411">
         <v>2006</v>
       </c>
-      <c r="C411" t="s">
-        <v>140</v>
+      <c r="C411" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E411">
         <v>49.943600000000004</v>
@@ -22731,8 +22738,8 @@
       <c r="B412">
         <v>2006</v>
       </c>
-      <c r="C412" t="s">
-        <v>140</v>
+      <c r="C412" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E412">
         <v>49.940100000000001</v>
@@ -22775,8 +22782,8 @@
       <c r="B413">
         <v>2006</v>
       </c>
-      <c r="C413" t="s">
-        <v>140</v>
+      <c r="C413" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E413">
         <v>49.908900000000003</v>
@@ -22819,8 +22826,8 @@
       <c r="B414">
         <v>2006</v>
       </c>
-      <c r="C414" t="s">
-        <v>140</v>
+      <c r="C414" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E414">
         <v>37.328299999999999</v>
@@ -22863,8 +22870,8 @@
       <c r="B415">
         <v>2006</v>
       </c>
-      <c r="C415" t="s">
-        <v>140</v>
+      <c r="C415" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E415">
         <v>50.110500000000002</v>
@@ -22907,8 +22914,8 @@
       <c r="B416">
         <v>2006</v>
       </c>
-      <c r="C416" t="s">
-        <v>140</v>
+      <c r="C416" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D416" t="s">
         <v>96</v>
@@ -22954,8 +22961,8 @@
       <c r="B417">
         <v>2006</v>
       </c>
-      <c r="C417" t="s">
-        <v>140</v>
+      <c r="C417" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E417">
         <v>50.231400000000001</v>
@@ -22998,8 +23005,8 @@
       <c r="B418">
         <v>2006</v>
       </c>
-      <c r="C418" t="s">
-        <v>140</v>
+      <c r="C418" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E418">
         <v>50.688099999999999</v>
@@ -23042,8 +23049,8 @@
       <c r="B419">
         <v>2006</v>
       </c>
-      <c r="C419" t="s">
-        <v>140</v>
+      <c r="C419" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E419">
         <v>50.491900000000001</v>
@@ -23086,8 +23093,8 @@
       <c r="B420">
         <v>2006</v>
       </c>
-      <c r="C420" t="s">
-        <v>140</v>
+      <c r="C420" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E420">
         <v>50.802100000000003</v>
@@ -23130,8 +23137,8 @@
       <c r="B421">
         <v>2006</v>
       </c>
-      <c r="C421" t="s">
-        <v>140</v>
+      <c r="C421" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E421">
         <v>50.7361</v>
@@ -23174,8 +23181,8 @@
       <c r="B422">
         <v>2006</v>
       </c>
-      <c r="C422" t="s">
-        <v>140</v>
+      <c r="C422" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E422">
         <v>50.875900000000001</v>
@@ -23218,8 +23225,8 @@
       <c r="B423">
         <v>2006</v>
       </c>
-      <c r="C423" t="s">
-        <v>140</v>
+      <c r="C423" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E423">
         <v>50.5473</v>
@@ -23262,8 +23269,8 @@
       <c r="B424">
         <v>2006</v>
       </c>
-      <c r="C424" t="s">
-        <v>140</v>
+      <c r="C424" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E424">
         <v>51.2224</v>
@@ -23306,8 +23313,8 @@
       <c r="B425">
         <v>2006</v>
       </c>
-      <c r="C425" t="s">
-        <v>140</v>
+      <c r="C425" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E425">
         <v>47.170299999999997</v>
@@ -23350,8 +23357,8 @@
       <c r="B426">
         <v>2006</v>
       </c>
-      <c r="C426" t="s">
-        <v>140</v>
+      <c r="C426" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E426">
         <v>50.954300000000003</v>
@@ -23394,8 +23401,8 @@
       <c r="B427">
         <v>2006</v>
       </c>
-      <c r="C427" t="s">
-        <v>140</v>
+      <c r="C427" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E427">
         <v>50.542400000000001</v>
@@ -23438,8 +23445,8 @@
       <c r="B428">
         <v>2006</v>
       </c>
-      <c r="C428" t="s">
-        <v>140</v>
+      <c r="C428" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E428">
         <v>46.140500000000003</v>
@@ -23482,8 +23489,8 @@
       <c r="B429">
         <v>2006</v>
       </c>
-      <c r="C429" t="s">
-        <v>140</v>
+      <c r="C429" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E429">
         <v>51.566000000000003</v>
@@ -23526,8 +23533,8 @@
       <c r="B430">
         <v>2006</v>
       </c>
-      <c r="C430" t="s">
-        <v>140</v>
+      <c r="C430" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E430">
         <v>50.564700000000002</v>
@@ -23570,8 +23577,8 @@
       <c r="B431">
         <v>2006</v>
       </c>
-      <c r="C431" t="s">
-        <v>140</v>
+      <c r="C431" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E431">
         <v>22.904800000000002</v>
@@ -23614,8 +23621,8 @@
       <c r="B432">
         <v>2006</v>
       </c>
-      <c r="C432" t="s">
-        <v>140</v>
+      <c r="C432" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E432">
         <v>51.479599999999998</v>
@@ -23658,8 +23665,8 @@
       <c r="B433">
         <v>2006</v>
       </c>
-      <c r="C433" t="s">
-        <v>140</v>
+      <c r="C433" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E433">
         <v>51.427300000000002</v>
@@ -23702,8 +23709,8 @@
       <c r="B434">
         <v>2006</v>
       </c>
-      <c r="C434" t="s">
-        <v>140</v>
+      <c r="C434" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E434">
         <v>50.897300000000001</v>
@@ -23746,8 +23753,8 @@
       <c r="B435">
         <v>2006</v>
       </c>
-      <c r="C435" t="s">
-        <v>140</v>
+      <c r="C435" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E435">
         <v>51.141500000000001</v>
@@ -23790,8 +23797,8 @@
       <c r="B436">
         <v>2006</v>
       </c>
-      <c r="C436" t="s">
-        <v>140</v>
+      <c r="C436" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E436">
         <v>51.336100000000002</v>
@@ -23834,8 +23841,8 @@
       <c r="B437">
         <v>2006</v>
       </c>
-      <c r="C437" t="s">
-        <v>140</v>
+      <c r="C437" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E437">
         <v>51.109099999999998</v>
@@ -23878,8 +23885,8 @@
       <c r="B438">
         <v>2006</v>
       </c>
-      <c r="C438" t="s">
-        <v>140</v>
+      <c r="C438" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E438">
         <v>51.477499999999999</v>
@@ -23922,8 +23929,8 @@
       <c r="B439">
         <v>2006</v>
       </c>
-      <c r="C439" t="s">
-        <v>140</v>
+      <c r="C439" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E439">
         <v>51.2316</v>
@@ -23966,8 +23973,8 @@
       <c r="B440">
         <v>2006</v>
       </c>
-      <c r="C440" t="s">
-        <v>140</v>
+      <c r="C440" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E440">
         <v>51.453499999999998</v>
@@ -24010,8 +24017,8 @@
       <c r="B441">
         <v>2006</v>
       </c>
-      <c r="C441" t="s">
-        <v>140</v>
+      <c r="C441" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E441">
         <v>51.800699999999999</v>
@@ -24054,8 +24061,8 @@
       <c r="B442">
         <v>2006</v>
       </c>
-      <c r="C442" t="s">
-        <v>140</v>
+      <c r="C442" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E442">
         <v>50.796799999999998</v>
@@ -24098,8 +24105,8 @@
       <c r="B443">
         <v>2006</v>
       </c>
-      <c r="C443" t="s">
-        <v>140</v>
+      <c r="C443" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E443">
         <v>51.637700000000002</v>
@@ -24142,8 +24149,8 @@
       <c r="B444">
         <v>2006</v>
       </c>
-      <c r="C444" t="s">
-        <v>140</v>
+      <c r="C444" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E444">
         <v>51.4377</v>
@@ -24186,8 +24193,8 @@
       <c r="B445">
         <v>2006</v>
       </c>
-      <c r="C445" t="s">
-        <v>140</v>
+      <c r="C445" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E445">
         <v>51.680399999999999</v>
@@ -24230,8 +24237,8 @@
       <c r="B446">
         <v>2006</v>
       </c>
-      <c r="C446" t="s">
-        <v>140</v>
+      <c r="C446" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E446">
         <v>50.500500000000002</v>
@@ -24274,8 +24281,8 @@
       <c r="B447">
         <v>2006</v>
       </c>
-      <c r="C447" t="s">
-        <v>140</v>
+      <c r="C447" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E447">
         <v>51.210299999999997</v>
@@ -24318,8 +24325,8 @@
       <c r="B448">
         <v>2006</v>
       </c>
-      <c r="C448" t="s">
-        <v>140</v>
+      <c r="C448" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E448">
         <v>50.904800000000002</v>
@@ -24362,8 +24369,8 @@
       <c r="B449">
         <v>2010</v>
       </c>
-      <c r="C449" t="s">
-        <v>140</v>
+      <c r="C449" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E449">
         <v>52.600099999999998</v>
@@ -24406,8 +24413,8 @@
       <c r="B450">
         <v>2010</v>
       </c>
-      <c r="C450" t="s">
-        <v>140</v>
+      <c r="C450" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E450">
         <v>52.598500000000001</v>
@@ -24450,8 +24457,8 @@
       <c r="B451">
         <v>2010</v>
       </c>
-      <c r="C451" t="s">
-        <v>140</v>
+      <c r="C451" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E451">
         <v>52.634</v>
@@ -24494,8 +24501,8 @@
       <c r="B452">
         <v>2010</v>
       </c>
-      <c r="C452" t="s">
-        <v>140</v>
+      <c r="C452" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E452">
         <v>51.039400000000001</v>
@@ -24538,8 +24545,8 @@
       <c r="B453">
         <v>2010</v>
       </c>
-      <c r="C453" t="s">
-        <v>140</v>
+      <c r="C453" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E453">
         <v>51.640700000000002</v>
@@ -24582,8 +24589,8 @@
       <c r="B454">
         <v>2010</v>
       </c>
-      <c r="C454" t="s">
-        <v>140</v>
+      <c r="C454" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E454">
         <v>51.764699999999998</v>
@@ -24626,8 +24633,8 @@
       <c r="B455">
         <v>2010</v>
       </c>
-      <c r="C455" t="s">
-        <v>140</v>
+      <c r="C455" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E455">
         <v>50.794600000000003</v>
@@ -24670,8 +24677,8 @@
       <c r="B456">
         <v>2010</v>
       </c>
-      <c r="C456" t="s">
-        <v>140</v>
+      <c r="C456" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E456">
         <v>52.499000000000002</v>
@@ -24714,8 +24721,8 @@
       <c r="B457">
         <v>2010</v>
       </c>
-      <c r="C457" t="s">
-        <v>140</v>
+      <c r="C457" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E457">
         <v>52.428400000000003</v>
@@ -24758,8 +24765,8 @@
       <c r="B458">
         <v>2010</v>
       </c>
-      <c r="C458" t="s">
-        <v>140</v>
+      <c r="C458" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E458">
         <v>51.035499999999999</v>
@@ -24802,8 +24809,8 @@
       <c r="B459">
         <v>2010</v>
       </c>
-      <c r="C459" t="s">
-        <v>140</v>
+      <c r="C459" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E459">
         <v>51.6295</v>
@@ -24846,8 +24853,8 @@
       <c r="B460">
         <v>2010</v>
       </c>
-      <c r="C460" t="s">
-        <v>140</v>
+      <c r="C460" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E460">
         <v>51.912100000000002</v>
@@ -24890,8 +24897,8 @@
       <c r="B461">
         <v>2010</v>
       </c>
-      <c r="C461" t="s">
-        <v>140</v>
+      <c r="C461" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E461">
         <v>51.941600000000001</v>
@@ -24934,8 +24941,8 @@
       <c r="B462">
         <v>2010</v>
       </c>
-      <c r="C462" t="s">
-        <v>140</v>
+      <c r="C462" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E462">
         <v>51.648200000000003</v>
@@ -24978,8 +24985,8 @@
       <c r="B463">
         <v>2010</v>
       </c>
-      <c r="C463" t="s">
-        <v>140</v>
+      <c r="C463" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E463">
         <v>48.392299999999999</v>
@@ -25022,8 +25029,8 @@
       <c r="B464">
         <v>2010</v>
       </c>
-      <c r="C464" t="s">
-        <v>140</v>
+      <c r="C464" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E464">
         <v>46.825200000000002</v>
@@ -25066,8 +25073,8 @@
       <c r="B465">
         <v>2010</v>
       </c>
-      <c r="C465" t="s">
-        <v>140</v>
+      <c r="C465" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E465">
         <v>47.657699999999998</v>
@@ -25110,8 +25117,8 @@
       <c r="B466">
         <v>2010</v>
       </c>
-      <c r="C466" t="s">
-        <v>140</v>
+      <c r="C466" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E466">
         <v>47.0366</v>
@@ -25154,8 +25161,8 @@
       <c r="B467">
         <v>2010</v>
       </c>
-      <c r="C467" t="s">
-        <v>140</v>
+      <c r="C467" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E467">
         <v>46.766100000000002</v>
@@ -25198,8 +25205,8 @@
       <c r="B468">
         <v>2010</v>
       </c>
-      <c r="C468" t="s">
-        <v>140</v>
+      <c r="C468" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E468">
         <v>47.607999999999997</v>
@@ -25242,8 +25249,8 @@
       <c r="B469">
         <v>2010</v>
       </c>
-      <c r="C469" t="s">
-        <v>140</v>
+      <c r="C469" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E469">
         <v>47.965600000000002</v>
@@ -25286,8 +25293,8 @@
       <c r="B470">
         <v>2010</v>
       </c>
-      <c r="C470" t="s">
-        <v>140</v>
+      <c r="C470" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E470">
         <v>46.962499999999999</v>
@@ -25330,8 +25337,8 @@
       <c r="B471">
         <v>2010</v>
       </c>
-      <c r="C471" t="s">
-        <v>140</v>
+      <c r="C471" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E471">
         <v>46.741100000000003</v>
@@ -25374,8 +25381,8 @@
       <c r="B472">
         <v>2010</v>
       </c>
-      <c r="C472" t="s">
-        <v>140</v>
+      <c r="C472" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E472">
         <v>44.834899999999998</v>
@@ -25418,8 +25425,8 @@
       <c r="B473">
         <v>2010</v>
       </c>
-      <c r="C473" t="s">
-        <v>140</v>
+      <c r="C473" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E473">
         <v>45.429000000000002</v>
@@ -25462,8 +25469,8 @@
       <c r="B474">
         <v>2010</v>
       </c>
-      <c r="C474" t="s">
-        <v>140</v>
+      <c r="C474" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E474">
         <v>44.906100000000002</v>
@@ -25506,8 +25513,8 @@
       <c r="B475">
         <v>2010</v>
       </c>
-      <c r="C475" t="s">
-        <v>140</v>
+      <c r="C475" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E475">
         <v>43.943600000000004</v>
@@ -25550,8 +25557,8 @@
       <c r="B476">
         <v>2010</v>
       </c>
-      <c r="C476" t="s">
-        <v>140</v>
+      <c r="C476" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E476">
         <v>44.674999999999997</v>
@@ -25594,8 +25601,8 @@
       <c r="B477">
         <v>2010</v>
       </c>
-      <c r="C477" t="s">
-        <v>140</v>
+      <c r="C477" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E477">
         <v>46.465699999999998</v>
@@ -25638,8 +25645,8 @@
       <c r="B478">
         <v>2010</v>
       </c>
-      <c r="C478" t="s">
-        <v>140</v>
+      <c r="C478" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E478">
         <v>46.298400000000001</v>
@@ -25682,8 +25689,8 @@
       <c r="B479">
         <v>2010</v>
       </c>
-      <c r="C479" t="s">
-        <v>140</v>
+      <c r="C479" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E479">
         <v>44.919600000000003</v>
@@ -25726,8 +25733,8 @@
       <c r="B480">
         <v>2010</v>
       </c>
-      <c r="C480" t="s">
-        <v>140</v>
+      <c r="C480" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E480">
         <v>48.535899999999998</v>
@@ -25770,8 +25777,8 @@
       <c r="B481">
         <v>2010</v>
       </c>
-      <c r="C481" t="s">
-        <v>140</v>
+      <c r="C481" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E481">
         <v>47.724800000000002</v>
@@ -25814,8 +25821,8 @@
       <c r="B482">
         <v>2010</v>
       </c>
-      <c r="C482" t="s">
-        <v>140</v>
+      <c r="C482" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E482">
         <v>48.907800000000002</v>
@@ -25858,8 +25865,8 @@
       <c r="B483">
         <v>2010</v>
       </c>
-      <c r="C483" t="s">
-        <v>140</v>
+      <c r="C483" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E483">
         <v>50.492100000000001</v>
@@ -25902,8 +25909,8 @@
       <c r="B484">
         <v>2010</v>
       </c>
-      <c r="C484" t="s">
-        <v>140</v>
+      <c r="C484" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E484">
         <v>50.122900000000001</v>
@@ -25946,8 +25953,8 @@
       <c r="B485">
         <v>2010</v>
       </c>
-      <c r="C485" t="s">
-        <v>140</v>
+      <c r="C485" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E485">
         <v>49.796900000000001</v>
@@ -25990,8 +25997,8 @@
       <c r="B486">
         <v>2010</v>
       </c>
-      <c r="C486" t="s">
-        <v>140</v>
+      <c r="C486" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E486">
         <v>50.411200000000001</v>
@@ -26034,8 +26041,8 @@
       <c r="B487">
         <v>2010</v>
       </c>
-      <c r="C487" t="s">
-        <v>140</v>
+      <c r="C487" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E487">
         <v>49.868099999999998</v>
@@ -26078,8 +26085,8 @@
       <c r="B488">
         <v>2010</v>
       </c>
-      <c r="C488" t="s">
-        <v>140</v>
+      <c r="C488" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E488">
         <v>50.271000000000001</v>
@@ -26122,8 +26129,8 @@
       <c r="B489">
         <v>2010</v>
       </c>
-      <c r="C489" t="s">
-        <v>140</v>
+      <c r="C489" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E489">
         <v>49.133200000000002</v>
@@ -26166,8 +26173,8 @@
       <c r="B490">
         <v>2010</v>
       </c>
-      <c r="C490" t="s">
-        <v>140</v>
+      <c r="C490" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E490">
         <v>48.313499999999998</v>
@@ -26210,8 +26217,8 @@
       <c r="B491">
         <v>2010</v>
       </c>
-      <c r="C491" t="s">
-        <v>140</v>
+      <c r="C491" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E491">
         <v>50.280700000000003</v>
@@ -26254,8 +26261,8 @@
       <c r="B492">
         <v>2010</v>
       </c>
-      <c r="C492" t="s">
-        <v>140</v>
+      <c r="C492" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E492">
         <v>49.145699999999998</v>
@@ -26298,8 +26305,8 @@
       <c r="B493">
         <v>2010</v>
       </c>
-      <c r="C493" t="s">
-        <v>140</v>
+      <c r="C493" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E493">
         <v>45.384399999999999</v>
@@ -26342,8 +26349,8 @@
       <c r="B494">
         <v>2010</v>
       </c>
-      <c r="C494" t="s">
-        <v>140</v>
+      <c r="C494" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E494">
         <v>48.354999999999997</v>
@@ -26386,8 +26393,8 @@
       <c r="B495">
         <v>2010</v>
       </c>
-      <c r="C495" t="s">
-        <v>140</v>
+      <c r="C495" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E495">
         <v>50.6494</v>
@@ -26430,8 +26437,8 @@
       <c r="B496">
         <v>2010</v>
       </c>
-      <c r="C496" t="s">
-        <v>140</v>
+      <c r="C496" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E496">
         <v>51.224600000000002</v>
@@ -26474,8 +26481,8 @@
       <c r="B497">
         <v>2010</v>
       </c>
-      <c r="C497" t="s">
-        <v>140</v>
+      <c r="C497" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E497">
         <v>50.347200000000001</v>
@@ -26518,8 +26525,8 @@
       <c r="B498">
         <v>2010</v>
       </c>
-      <c r="C498" t="s">
-        <v>140</v>
+      <c r="C498" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E498">
         <v>53.985500000000002</v>
@@ -26562,8 +26569,8 @@
       <c r="B499">
         <v>2010</v>
       </c>
-      <c r="C499" t="s">
-        <v>140</v>
+      <c r="C499" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E499">
         <v>53.191699999999997</v>
@@ -26606,8 +26613,8 @@
       <c r="B500">
         <v>2010</v>
       </c>
-      <c r="C500" t="s">
-        <v>140</v>
+      <c r="C500" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E500">
         <v>53.131300000000003</v>
@@ -26650,8 +26657,8 @@
       <c r="B501">
         <v>2010</v>
       </c>
-      <c r="C501" t="s">
-        <v>140</v>
+      <c r="C501" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E501">
         <v>52.441699999999997</v>
@@ -26694,8 +26701,8 @@
       <c r="B502">
         <v>2010</v>
       </c>
-      <c r="C502" t="s">
-        <v>140</v>
+      <c r="C502" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E502">
         <v>47.673200000000001</v>
@@ -26738,8 +26745,8 @@
       <c r="B503">
         <v>2010</v>
       </c>
-      <c r="C503" t="s">
-        <v>140</v>
+      <c r="C503" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E503">
         <v>52.6267</v>
@@ -26782,8 +26789,8 @@
       <c r="B504">
         <v>2010</v>
       </c>
-      <c r="C504" t="s">
-        <v>140</v>
+      <c r="C504" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E504">
         <v>51.896599999999999</v>
@@ -26826,8 +26833,8 @@
       <c r="B505">
         <v>2010</v>
       </c>
-      <c r="C505" t="s">
-        <v>140</v>
+      <c r="C505" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E505">
         <v>50.389299999999999</v>
@@ -26870,8 +26877,8 @@
       <c r="B506">
         <v>2010</v>
       </c>
-      <c r="C506" t="s">
-        <v>140</v>
+      <c r="C506" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E506">
         <v>52.139200000000002</v>
@@ -26914,8 +26921,8 @@
       <c r="B507">
         <v>2010</v>
       </c>
-      <c r="C507" t="s">
-        <v>140</v>
+      <c r="C507" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E507">
         <v>51.399799999999999</v>
@@ -26958,8 +26965,8 @@
       <c r="B508">
         <v>2010</v>
       </c>
-      <c r="C508" t="s">
-        <v>140</v>
+      <c r="C508" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E508">
         <v>49.427</v>
@@ -27002,8 +27009,8 @@
       <c r="B509">
         <v>2010</v>
       </c>
-      <c r="C509" t="s">
-        <v>140</v>
+      <c r="C509" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E509">
         <v>51.782400000000003</v>
@@ -27046,8 +27053,8 @@
       <c r="B510">
         <v>2010</v>
       </c>
-      <c r="C510" t="s">
-        <v>140</v>
+      <c r="C510" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D510" t="s">
         <v>96</v>
@@ -27093,8 +27100,8 @@
       <c r="B511">
         <v>2010</v>
       </c>
-      <c r="C511" t="s">
-        <v>140</v>
+      <c r="C511" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E511">
         <v>50.922699999999999</v>
@@ -27137,8 +27144,8 @@
       <c r="B512">
         <v>2010</v>
       </c>
-      <c r="C512" t="s">
-        <v>140</v>
+      <c r="C512" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E512">
         <v>52.1447</v>
@@ -27181,8 +27188,8 @@
       <c r="B513">
         <v>2010</v>
       </c>
-      <c r="C513" t="s">
-        <v>140</v>
+      <c r="C513" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E513">
         <v>51.215699999999998</v>
@@ -27225,8 +27232,8 @@
       <c r="B514">
         <v>2010</v>
       </c>
-      <c r="C514" t="s">
-        <v>140</v>
+      <c r="C514" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E514">
         <v>51.811599999999999</v>
@@ -27269,8 +27276,8 @@
       <c r="B515">
         <v>2010</v>
       </c>
-      <c r="C515" t="s">
-        <v>140</v>
+      <c r="C515" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E515">
         <v>49.096299999999999</v>
@@ -27313,8 +27320,8 @@
       <c r="B516">
         <v>2010</v>
       </c>
-      <c r="C516" t="s">
-        <v>140</v>
+      <c r="C516" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D516" t="s">
         <v>96</v>
@@ -27360,8 +27367,8 @@
       <c r="B517">
         <v>2010</v>
       </c>
-      <c r="C517" t="s">
-        <v>140</v>
+      <c r="C517" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E517">
         <v>51.855899999999998</v>
@@ -27404,8 +27411,8 @@
       <c r="B518">
         <v>2010</v>
       </c>
-      <c r="C518" t="s">
-        <v>140</v>
+      <c r="C518" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D518" t="s">
         <v>96</v>
@@ -27451,8 +27458,8 @@
       <c r="B519">
         <v>2010</v>
       </c>
-      <c r="C519" t="s">
-        <v>140</v>
+      <c r="C519" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D519" t="s">
         <v>96</v>
@@ -27498,8 +27505,8 @@
       <c r="B520">
         <v>2010</v>
       </c>
-      <c r="C520" t="s">
-        <v>140</v>
+      <c r="C520" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E520">
         <v>51.496000000000002</v>
@@ -27542,8 +27549,8 @@
       <c r="B521">
         <v>2010</v>
       </c>
-      <c r="C521" t="s">
-        <v>140</v>
+      <c r="C521" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E521">
         <v>51.464300000000001</v>
@@ -27586,8 +27593,8 @@
       <c r="B522">
         <v>2010</v>
       </c>
-      <c r="C522" t="s">
-        <v>140</v>
+      <c r="C522" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E522">
         <v>50.908999999999999</v>
@@ -27630,8 +27637,8 @@
       <c r="B523">
         <v>2010</v>
       </c>
-      <c r="C523" t="s">
-        <v>140</v>
+      <c r="C523" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E523">
         <v>52.254800000000003</v>
@@ -27674,8 +27681,8 @@
       <c r="B524">
         <v>2010</v>
       </c>
-      <c r="C524" t="s">
-        <v>140</v>
+      <c r="C524" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E524">
         <v>51.493499999999997</v>
@@ -27718,8 +27725,8 @@
       <c r="B525">
         <v>2010</v>
       </c>
-      <c r="C525" t="s">
-        <v>140</v>
+      <c r="C525" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E525">
         <v>51.538699999999999</v>
@@ -27762,8 +27769,8 @@
       <c r="B526">
         <v>2010</v>
       </c>
-      <c r="C526" t="s">
-        <v>140</v>
+      <c r="C526" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D526" t="s">
         <v>96</v>
@@ -27809,8 +27816,8 @@
       <c r="B527">
         <v>2010</v>
       </c>
-      <c r="C527" t="s">
-        <v>140</v>
+      <c r="C527" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E527">
         <v>51.953299999999999</v>
@@ -27853,8 +27860,8 @@
       <c r="B528">
         <v>2010</v>
       </c>
-      <c r="C528" t="s">
-        <v>140</v>
+      <c r="C528" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E528">
         <v>51.316299999999998</v>
@@ -27897,8 +27904,8 @@
       <c r="B529">
         <v>2010</v>
       </c>
-      <c r="C529" t="s">
-        <v>140</v>
+      <c r="C529" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D529" t="s">
         <v>96</v>
@@ -27944,8 +27951,8 @@
       <c r="B530">
         <v>2010</v>
       </c>
-      <c r="C530" t="s">
-        <v>140</v>
+      <c r="C530" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D530" t="s">
         <v>96</v>
@@ -27991,8 +27998,8 @@
       <c r="B531">
         <v>2010</v>
       </c>
-      <c r="C531" t="s">
-        <v>140</v>
+      <c r="C531" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E531">
         <v>52.109699999999997</v>

--- a/paper/data/merapi_cpx_raw.xlsx
+++ b/paper/data/merapi_cpx_raw.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52E3AD39-EFD3-46F3-A5A8-DFF653E9B54C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE62AF97-F3CD-4F1F-A837-94D80EE0BC59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3800" yWindow="3800" windowWidth="28800" windowHeight="16760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2240" yWindow="2240" windowWidth="28800" windowHeight="15080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2619,8 +2619,8 @@
       <c r="B2">
         <v>2006</v>
       </c>
-      <c r="C2" t="s">
-        <v>542</v>
+      <c r="C2" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D2" t="s">
         <v>96</v>
@@ -2669,8 +2669,8 @@
       <c r="B3">
         <v>2006</v>
       </c>
-      <c r="C3" t="s">
-        <v>542</v>
+      <c r="C3" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D3" t="s">
         <v>96</v>
@@ -2719,8 +2719,8 @@
       <c r="B4">
         <v>2006</v>
       </c>
-      <c r="C4" t="s">
-        <v>542</v>
+      <c r="C4" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D4" t="s">
         <v>96</v>
@@ -2769,8 +2769,8 @@
       <c r="B5">
         <v>2006</v>
       </c>
-      <c r="C5" t="s">
-        <v>542</v>
+      <c r="C5" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D5" t="s">
         <v>96</v>
@@ -2819,8 +2819,8 @@
       <c r="B6">
         <v>2006</v>
       </c>
-      <c r="C6" t="s">
-        <v>542</v>
+      <c r="C6" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D6" t="s">
         <v>96</v>
@@ -2869,8 +2869,8 @@
       <c r="B7">
         <v>2006</v>
       </c>
-      <c r="C7" t="s">
-        <v>542</v>
+      <c r="C7" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D7" t="s">
         <v>139</v>
@@ -2919,8 +2919,8 @@
       <c r="B8">
         <v>2006</v>
       </c>
-      <c r="C8" t="s">
-        <v>542</v>
+      <c r="C8" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D8" t="s">
         <v>139</v>
@@ -2969,8 +2969,8 @@
       <c r="B9">
         <v>2006</v>
       </c>
-      <c r="C9" t="s">
-        <v>542</v>
+      <c r="C9" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D9" t="s">
         <v>139</v>
@@ -3019,8 +3019,8 @@
       <c r="B10">
         <v>2006</v>
       </c>
-      <c r="C10" t="s">
-        <v>542</v>
+      <c r="C10" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D10" t="s">
         <v>139</v>
@@ -3069,8 +3069,8 @@
       <c r="B11">
         <v>2006</v>
       </c>
-      <c r="C11" t="s">
-        <v>542</v>
+      <c r="C11" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D11" t="s">
         <v>139</v>
@@ -3119,8 +3119,8 @@
       <c r="B12">
         <v>2006</v>
       </c>
-      <c r="C12" t="s">
-        <v>542</v>
+      <c r="C12" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D12" t="s">
         <v>139</v>
@@ -3169,8 +3169,8 @@
       <c r="B13">
         <v>2006</v>
       </c>
-      <c r="C13" t="s">
-        <v>542</v>
+      <c r="C13" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D13" t="s">
         <v>139</v>
@@ -3219,8 +3219,8 @@
       <c r="B14">
         <v>2006</v>
       </c>
-      <c r="C14" t="s">
-        <v>542</v>
+      <c r="C14" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D14" t="s">
         <v>139</v>
@@ -3269,8 +3269,8 @@
       <c r="B15">
         <v>2006</v>
       </c>
-      <c r="C15" t="s">
-        <v>542</v>
+      <c r="C15" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D15" t="s">
         <v>139</v>
@@ -3319,8 +3319,8 @@
       <c r="B16">
         <v>2006</v>
       </c>
-      <c r="C16" t="s">
-        <v>542</v>
+      <c r="C16" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D16" t="s">
         <v>139</v>
@@ -3369,8 +3369,8 @@
       <c r="B17">
         <v>2006</v>
       </c>
-      <c r="C17" t="s">
-        <v>542</v>
+      <c r="C17" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D17" t="s">
         <v>139</v>
@@ -3419,8 +3419,8 @@
       <c r="B18">
         <v>2006</v>
       </c>
-      <c r="C18" t="s">
-        <v>542</v>
+      <c r="C18" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D18" t="s">
         <v>139</v>
@@ -3469,8 +3469,8 @@
       <c r="B19">
         <v>2006</v>
       </c>
-      <c r="C19" t="s">
-        <v>542</v>
+      <c r="C19" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D19" t="s">
         <v>139</v>
@@ -3519,8 +3519,8 @@
       <c r="B20">
         <v>2006</v>
       </c>
-      <c r="C20" t="s">
-        <v>542</v>
+      <c r="C20" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D20" t="s">
         <v>139</v>
@@ -3569,8 +3569,8 @@
       <c r="B21">
         <v>2006</v>
       </c>
-      <c r="C21" t="s">
-        <v>542</v>
+      <c r="C21" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D21" t="s">
         <v>139</v>
@@ -3619,8 +3619,8 @@
       <c r="B22">
         <v>2006</v>
       </c>
-      <c r="C22" t="s">
-        <v>542</v>
+      <c r="C22" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E22">
         <v>50.832092274785353</v>
@@ -3666,8 +3666,8 @@
       <c r="B23">
         <v>2006</v>
       </c>
-      <c r="C23" t="s">
-        <v>542</v>
+      <c r="C23" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E23">
         <v>51.69649533875068</v>
@@ -3713,8 +3713,8 @@
       <c r="B24">
         <v>2006</v>
       </c>
-      <c r="C24" t="s">
-        <v>542</v>
+      <c r="C24" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E24">
         <v>52.425718314648321</v>
@@ -3760,8 +3760,8 @@
       <c r="B25">
         <v>2006</v>
       </c>
-      <c r="C25" t="s">
-        <v>542</v>
+      <c r="C25" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E25">
         <v>52.374514281136079</v>
@@ -3807,8 +3807,8 @@
       <c r="B26">
         <v>2006</v>
       </c>
-      <c r="C26" t="s">
-        <v>542</v>
+      <c r="C26" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E26">
         <v>51.941465951828448</v>
@@ -3854,8 +3854,8 @@
       <c r="B27">
         <v>2006</v>
       </c>
-      <c r="C27" t="s">
-        <v>542</v>
+      <c r="C27" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E27">
         <v>52.191933684042723</v>
@@ -3901,8 +3901,8 @@
       <c r="B28">
         <v>2006</v>
       </c>
-      <c r="C28" t="s">
-        <v>542</v>
+      <c r="C28" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E28">
         <v>52.15653271617925</v>
@@ -3948,8 +3948,8 @@
       <c r="B29">
         <v>2006</v>
       </c>
-      <c r="C29" t="s">
-        <v>542</v>
+      <c r="C29" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E29">
         <v>51.039212554406419</v>
@@ -3995,8 +3995,8 @@
       <c r="B30">
         <v>2006</v>
       </c>
-      <c r="C30" t="s">
-        <v>542</v>
+      <c r="C30" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E30">
         <v>51.420972417296724</v>
@@ -4042,8 +4042,8 @@
       <c r="B31">
         <v>2006</v>
       </c>
-      <c r="C31" t="s">
-        <v>542</v>
+      <c r="C31" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E31">
         <v>50.917734849852557</v>
@@ -4089,8 +4089,8 @@
       <c r="B32">
         <v>2006</v>
       </c>
-      <c r="C32" t="s">
-        <v>542</v>
+      <c r="C32" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E32">
         <v>51.689185795368921</v>
@@ -4136,8 +4136,8 @@
       <c r="B33">
         <v>2006</v>
       </c>
-      <c r="C33" t="s">
-        <v>542</v>
+      <c r="C33" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E33">
         <v>51.646051569305598</v>
@@ -4183,8 +4183,8 @@
       <c r="B34">
         <v>2006</v>
       </c>
-      <c r="C34" t="s">
-        <v>542</v>
+      <c r="C34" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E34">
         <v>51.206969144094472</v>
@@ -4230,8 +4230,8 @@
       <c r="B35">
         <v>2006</v>
       </c>
-      <c r="C35" t="s">
-        <v>542</v>
+      <c r="C35" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E35">
         <v>50.514464956445295</v>
@@ -4277,8 +4277,8 @@
       <c r="B36">
         <v>2006</v>
       </c>
-      <c r="C36" t="s">
-        <v>542</v>
+      <c r="C36" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E36">
         <v>50.843847946636664</v>
@@ -4324,8 +4324,8 @@
       <c r="B37">
         <v>2006</v>
       </c>
-      <c r="C37" t="s">
-        <v>542</v>
+      <c r="C37" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E37">
         <v>49.121400146349771</v>
@@ -4371,8 +4371,8 @@
       <c r="B38">
         <v>2006</v>
       </c>
-      <c r="C38" t="s">
-        <v>542</v>
+      <c r="C38" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E38">
         <v>49.407146290658545</v>
@@ -4418,8 +4418,8 @@
       <c r="B39">
         <v>2006</v>
       </c>
-      <c r="C39" t="s">
-        <v>542</v>
+      <c r="C39" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E39">
         <v>49.325278360497009</v>
@@ -4465,8 +4465,8 @@
       <c r="B40">
         <v>2006</v>
       </c>
-      <c r="C40" t="s">
-        <v>542</v>
+      <c r="C40" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E40">
         <v>48.880742375962683</v>
@@ -4512,8 +4512,8 @@
       <c r="B41">
         <v>2006</v>
       </c>
-      <c r="C41" t="s">
-        <v>542</v>
+      <c r="C41" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E41">
         <v>48.922136422136418</v>
@@ -4559,8 +4559,8 @@
       <c r="B42">
         <v>2006</v>
       </c>
-      <c r="C42" t="s">
-        <v>542</v>
+      <c r="C42" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E42">
         <v>49.159052843775378</v>
@@ -4606,8 +4606,8 @@
       <c r="B43">
         <v>2006</v>
       </c>
-      <c r="C43" t="s">
-        <v>542</v>
+      <c r="C43" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E43">
         <v>48.948466848611332</v>
@@ -4653,8 +4653,8 @@
       <c r="B44">
         <v>2006</v>
       </c>
-      <c r="C44" t="s">
-        <v>542</v>
+      <c r="C44" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E44">
         <v>48.468192467111194</v>
@@ -4700,8 +4700,8 @@
       <c r="B45">
         <v>2006</v>
       </c>
-      <c r="C45" t="s">
-        <v>542</v>
+      <c r="C45" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E45">
         <v>48.635238219344231</v>
@@ -4747,8 +4747,8 @@
       <c r="B46">
         <v>2006</v>
       </c>
-      <c r="C46" t="s">
-        <v>542</v>
+      <c r="C46" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E46">
         <v>50.557825581861145</v>
@@ -4794,8 +4794,8 @@
       <c r="B47">
         <v>2006</v>
       </c>
-      <c r="C47" t="s">
-        <v>542</v>
+      <c r="C47" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E47">
         <v>52.337328167082163</v>
@@ -4841,8 +4841,8 @@
       <c r="B48">
         <v>2006</v>
       </c>
-      <c r="C48" t="s">
-        <v>542</v>
+      <c r="C48" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E48">
         <v>51.681506437251834</v>
@@ -4888,8 +4888,8 @@
       <c r="B49">
         <v>2006</v>
       </c>
-      <c r="C49" t="s">
-        <v>542</v>
+      <c r="C49" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E49">
         <v>51.817179512879626</v>
@@ -4935,8 +4935,8 @@
       <c r="B50">
         <v>2006</v>
       </c>
-      <c r="C50" t="s">
-        <v>542</v>
+      <c r="C50" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E50">
         <v>52.34928856402923</v>
@@ -4982,8 +4982,8 @@
       <c r="B51">
         <v>2006</v>
       </c>
-      <c r="C51" t="s">
-        <v>542</v>
+      <c r="C51" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E51">
         <v>51.861569464674076</v>
@@ -5029,8 +5029,8 @@
       <c r="B52">
         <v>2006</v>
       </c>
-      <c r="C52" t="s">
-        <v>542</v>
+      <c r="C52" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E52">
         <v>52.132393380330988</v>
@@ -5076,8 +5076,8 @@
       <c r="B53">
         <v>2006</v>
       </c>
-      <c r="C53" t="s">
-        <v>542</v>
+      <c r="C53" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E53">
         <v>52.056101038090084</v>
@@ -5123,8 +5123,8 @@
       <c r="B54">
         <v>2006</v>
       </c>
-      <c r="C54" t="s">
-        <v>542</v>
+      <c r="C54" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E54">
         <v>51.87481900881739</v>
@@ -5170,8 +5170,8 @@
       <c r="B55">
         <v>2006</v>
       </c>
-      <c r="C55" t="s">
-        <v>542</v>
+      <c r="C55" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E55">
         <v>51.992500698073322</v>
@@ -5217,8 +5217,8 @@
       <c r="B56">
         <v>2006</v>
       </c>
-      <c r="C56" t="s">
-        <v>542</v>
+      <c r="C56" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E56">
         <v>51.802781491310334</v>
@@ -5264,8 +5264,8 @@
       <c r="B57">
         <v>2006</v>
       </c>
-      <c r="C57" t="s">
-        <v>542</v>
+      <c r="C57" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E57">
         <v>50.470533940646497</v>
@@ -5311,8 +5311,8 @@
       <c r="B58">
         <v>2006</v>
       </c>
-      <c r="C58" t="s">
-        <v>542</v>
+      <c r="C58" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E58">
         <v>51.967853689977439</v>
@@ -5358,8 +5358,8 @@
       <c r="B59">
         <v>2006</v>
       </c>
-      <c r="C59" t="s">
-        <v>542</v>
+      <c r="C59" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E59">
         <v>52.445988578730876</v>
@@ -5405,8 +5405,8 @@
       <c r="B60">
         <v>2006</v>
       </c>
-      <c r="C60" t="s">
-        <v>542</v>
+      <c r="C60" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E60">
         <v>48.775082359988012</v>
@@ -5452,8 +5452,8 @@
       <c r="B61">
         <v>2006</v>
       </c>
-      <c r="C61" t="s">
-        <v>542</v>
+      <c r="C61" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E61">
         <v>49.991037820397921</v>
@@ -5499,8 +5499,8 @@
       <c r="B62">
         <v>2006</v>
       </c>
-      <c r="C62" t="s">
-        <v>542</v>
+      <c r="C62" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E62">
         <v>50.292101341281665</v>
@@ -5546,8 +5546,8 @@
       <c r="B63">
         <v>2006</v>
       </c>
-      <c r="C63" t="s">
-        <v>542</v>
+      <c r="C63" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E63">
         <v>50.628394877161512</v>
@@ -5593,8 +5593,8 @@
       <c r="B64">
         <v>2006</v>
       </c>
-      <c r="C64" t="s">
-        <v>542</v>
+      <c r="C64" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E64">
         <v>50.530355896720167</v>
@@ -5640,8 +5640,8 @@
       <c r="B65">
         <v>2006</v>
       </c>
-      <c r="C65" t="s">
-        <v>542</v>
+      <c r="C65" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E65">
         <v>50.463018281754103</v>
@@ -5687,8 +5687,8 @@
       <c r="B66">
         <v>2006</v>
       </c>
-      <c r="C66" t="s">
-        <v>542</v>
+      <c r="C66" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E66">
         <v>50.154290264782006</v>
@@ -5734,8 +5734,8 @@
       <c r="B67">
         <v>2006</v>
       </c>
-      <c r="C67" t="s">
-        <v>542</v>
+      <c r="C67" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E67">
         <v>50.413979778680044</v>
@@ -5781,8 +5781,8 @@
       <c r="B68">
         <v>2006</v>
       </c>
-      <c r="C68" t="s">
-        <v>542</v>
+      <c r="C68" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E68">
         <v>50.351108185209561</v>
@@ -5828,8 +5828,8 @@
       <c r="B69">
         <v>2006</v>
       </c>
-      <c r="C69" t="s">
-        <v>542</v>
+      <c r="C69" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E69">
         <v>50.386918379120338</v>
@@ -5875,8 +5875,8 @@
       <c r="B70">
         <v>2006</v>
       </c>
-      <c r="C70" t="s">
-        <v>542</v>
+      <c r="C70" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E70">
         <v>50.313659966582954</v>
@@ -5922,8 +5922,8 @@
       <c r="B71">
         <v>2006</v>
       </c>
-      <c r="C71" t="s">
-        <v>542</v>
+      <c r="C71" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E71">
         <v>50.483637993724152</v>
@@ -5969,8 +5969,8 @@
       <c r="B72">
         <v>2006</v>
       </c>
-      <c r="C72" t="s">
-        <v>542</v>
+      <c r="C72" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E72">
         <v>50.392527079399784</v>
@@ -6016,8 +6016,8 @@
       <c r="B73">
         <v>2006</v>
       </c>
-      <c r="C73" t="s">
-        <v>542</v>
+      <c r="C73" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E73">
         <v>50.374725931831776</v>
@@ -6063,8 +6063,8 @@
       <c r="B74">
         <v>2006</v>
       </c>
-      <c r="C74" t="s">
-        <v>542</v>
+      <c r="C74" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E74">
         <v>50.118064342575884</v>
@@ -6110,8 +6110,8 @@
       <c r="B75">
         <v>2006</v>
       </c>
-      <c r="C75" t="s">
-        <v>542</v>
+      <c r="C75" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E75">
         <v>49.750235721307199</v>
@@ -6157,8 +6157,8 @@
       <c r="B76">
         <v>2006</v>
       </c>
-      <c r="C76" t="s">
-        <v>542</v>
+      <c r="C76" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E76">
         <v>49.505059173368984</v>
@@ -6204,8 +6204,8 @@
       <c r="B77">
         <v>2006</v>
       </c>
-      <c r="C77" t="s">
-        <v>542</v>
+      <c r="C77" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E77">
         <v>49.874889903114742</v>
@@ -6251,8 +6251,8 @@
       <c r="B78">
         <v>2006</v>
       </c>
-      <c r="C78" t="s">
-        <v>542</v>
+      <c r="C78" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E78">
         <v>49.937505624493795</v>
@@ -6298,8 +6298,8 @@
       <c r="B79">
         <v>2006</v>
       </c>
-      <c r="C79" t="s">
-        <v>542</v>
+      <c r="C79" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E79">
         <v>49.902506824522277</v>
@@ -6345,8 +6345,8 @@
       <c r="B80">
         <v>2006</v>
       </c>
-      <c r="C80" t="s">
-        <v>542</v>
+      <c r="C80" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E80">
         <v>50.02933426142296</v>
@@ -6392,8 +6392,8 @@
       <c r="B81">
         <v>2006</v>
       </c>
-      <c r="C81" t="s">
-        <v>542</v>
+      <c r="C81" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E81">
         <v>50.026379971131348</v>
@@ -6439,8 +6439,8 @@
       <c r="B82">
         <v>2006</v>
       </c>
-      <c r="C82" t="s">
-        <v>542</v>
+      <c r="C82" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E82">
         <v>49.550062991181235</v>
@@ -6486,8 +6486,8 @@
       <c r="B83">
         <v>2006</v>
       </c>
-      <c r="C83" t="s">
-        <v>542</v>
+      <c r="C83" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E83">
         <v>49.412960711224507</v>
@@ -6533,8 +6533,8 @@
       <c r="B84">
         <v>2006</v>
       </c>
-      <c r="C84" t="s">
-        <v>542</v>
+      <c r="C84" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E84">
         <v>49.355769134804433</v>
@@ -6580,8 +6580,8 @@
       <c r="B85">
         <v>2006</v>
       </c>
-      <c r="C85" t="s">
-        <v>542</v>
+      <c r="C85" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E85">
         <v>49.797389460269414</v>
@@ -6627,8 +6627,8 @@
       <c r="B86">
         <v>2006</v>
       </c>
-      <c r="C86" t="s">
-        <v>542</v>
+      <c r="C86" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E86">
         <v>50.030460705689656</v>
@@ -6674,8 +6674,8 @@
       <c r="B87">
         <v>2006</v>
       </c>
-      <c r="C87" t="s">
-        <v>542</v>
+      <c r="C87" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E87">
         <v>49.763654936206869</v>
@@ -6721,8 +6721,8 @@
       <c r="B88">
         <v>2006</v>
       </c>
-      <c r="C88" t="s">
-        <v>542</v>
+      <c r="C88" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E88">
         <v>49.387791849228748</v>
@@ -6768,8 +6768,8 @@
       <c r="B89">
         <v>2006</v>
       </c>
-      <c r="C89" t="s">
-        <v>542</v>
+      <c r="C89" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E89">
         <v>49.339052875769944</v>
@@ -6815,8 +6815,8 @@
       <c r="B90">
         <v>2006</v>
       </c>
-      <c r="C90" t="s">
-        <v>542</v>
+      <c r="C90" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E90">
         <v>49.534394713127064</v>
@@ -6862,8 +6862,8 @@
       <c r="B91">
         <v>2006</v>
       </c>
-      <c r="C91" t="s">
-        <v>542</v>
+      <c r="C91" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E91">
         <v>49.514669975583402</v>
@@ -6909,8 +6909,8 @@
       <c r="B92">
         <v>2006</v>
       </c>
-      <c r="C92" t="s">
-        <v>542</v>
+      <c r="C92" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E92">
         <v>49.053747920049716</v>
@@ -6956,8 +6956,8 @@
       <c r="B93">
         <v>2006</v>
       </c>
-      <c r="C93" t="s">
-        <v>542</v>
+      <c r="C93" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E93">
         <v>49.715795771838849</v>
@@ -7003,8 +7003,8 @@
       <c r="B94">
         <v>2006</v>
       </c>
-      <c r="C94" t="s">
-        <v>542</v>
+      <c r="C94" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E94">
         <v>50.995307976440053</v>
@@ -7050,8 +7050,8 @@
       <c r="B95">
         <v>2006</v>
       </c>
-      <c r="C95" t="s">
-        <v>542</v>
+      <c r="C95" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E95">
         <v>51.678473355354804</v>
@@ -7097,8 +7097,8 @@
       <c r="B96">
         <v>2006</v>
       </c>
-      <c r="C96" t="s">
-        <v>542</v>
+      <c r="C96" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E96">
         <v>52.205889670684009</v>
@@ -7144,8 +7144,8 @@
       <c r="B97">
         <v>2006</v>
       </c>
-      <c r="C97" t="s">
-        <v>542</v>
+      <c r="C97" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E97">
         <v>52.079900124843945</v>
@@ -7191,8 +7191,8 @@
       <c r="B98">
         <v>2006</v>
       </c>
-      <c r="C98" t="s">
-        <v>542</v>
+      <c r="C98" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E98">
         <v>52.28020875150542</v>
@@ -7238,8 +7238,8 @@
       <c r="B99">
         <v>2006</v>
       </c>
-      <c r="C99" t="s">
-        <v>542</v>
+      <c r="C99" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E99">
         <v>52.250935804792121</v>
@@ -7285,8 +7285,8 @@
       <c r="B100">
         <v>2006</v>
       </c>
-      <c r="C100" t="s">
-        <v>542</v>
+      <c r="C100" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E100">
         <v>51.905041323135983</v>
@@ -7332,8 +7332,8 @@
       <c r="B101">
         <v>2006</v>
       </c>
-      <c r="C101" t="s">
-        <v>542</v>
+      <c r="C101" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E101">
         <v>52.132317658349329</v>
@@ -7379,8 +7379,8 @@
       <c r="B102">
         <v>2006</v>
       </c>
-      <c r="C102" t="s">
-        <v>542</v>
+      <c r="C102" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E102">
         <v>52.007692001115942</v>
@@ -7426,8 +7426,8 @@
       <c r="B103">
         <v>2006</v>
       </c>
-      <c r="C103" t="s">
-        <v>542</v>
+      <c r="C103" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E103">
         <v>52.085587210001201</v>
@@ -7473,8 +7473,8 @@
       <c r="B104">
         <v>2006</v>
       </c>
-      <c r="C104" t="s">
-        <v>542</v>
+      <c r="C104" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E104">
         <v>52.493341446626836</v>
@@ -7520,8 +7520,8 @@
       <c r="B105">
         <v>2006</v>
       </c>
-      <c r="C105" t="s">
-        <v>542</v>
+      <c r="C105" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E105">
         <v>52.678428227746586</v>
@@ -7567,8 +7567,8 @@
       <c r="B106">
         <v>2006</v>
       </c>
-      <c r="C106" t="s">
-        <v>542</v>
+      <c r="C106" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E106">
         <v>52.778862032727822</v>
@@ -7614,8 +7614,8 @@
       <c r="B107">
         <v>2006</v>
       </c>
-      <c r="C107" t="s">
-        <v>542</v>
+      <c r="C107" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E107">
         <v>52.699280258666427</v>
@@ -7661,8 +7661,8 @@
       <c r="B108">
         <v>2006</v>
       </c>
-      <c r="C108" t="s">
-        <v>542</v>
+      <c r="C108" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E108">
         <v>51.850777326477115</v>
@@ -7708,8 +7708,8 @@
       <c r="B109">
         <v>2006</v>
       </c>
-      <c r="C109" t="s">
-        <v>542</v>
+      <c r="C109" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E109">
         <v>50.371890485009267</v>
@@ -7755,8 +7755,8 @@
       <c r="B110">
         <v>2006</v>
       </c>
-      <c r="C110" t="s">
-        <v>542</v>
+      <c r="C110" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D110" t="s">
         <v>96</v>
@@ -7805,8 +7805,8 @@
       <c r="B111">
         <v>2006</v>
       </c>
-      <c r="C111" t="s">
-        <v>542</v>
+      <c r="C111" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D111" t="s">
         <v>96</v>
@@ -7855,8 +7855,8 @@
       <c r="B112">
         <v>2006</v>
       </c>
-      <c r="C112" t="s">
-        <v>542</v>
+      <c r="C112" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D112" t="s">
         <v>96</v>
@@ -7905,8 +7905,8 @@
       <c r="B113">
         <v>2006</v>
       </c>
-      <c r="C113" t="s">
-        <v>542</v>
+      <c r="C113" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D113" t="s">
         <v>96</v>
@@ -7955,8 +7955,8 @@
       <c r="B114">
         <v>2006</v>
       </c>
-      <c r="C114" t="s">
-        <v>542</v>
+      <c r="C114" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D114" t="s">
         <v>96</v>
@@ -8005,8 +8005,8 @@
       <c r="B115">
         <v>2006</v>
       </c>
-      <c r="C115" t="s">
-        <v>542</v>
+      <c r="C115" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D115" t="s">
         <v>96</v>
@@ -8055,8 +8055,8 @@
       <c r="B116">
         <v>2006</v>
       </c>
-      <c r="C116" t="s">
-        <v>542</v>
+      <c r="C116" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D116" t="s">
         <v>96</v>
@@ -8105,8 +8105,8 @@
       <c r="B117">
         <v>2006</v>
       </c>
-      <c r="C117" t="s">
-        <v>542</v>
+      <c r="C117" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D117" t="s">
         <v>96</v>
@@ -8155,8 +8155,8 @@
       <c r="B118">
         <v>2006</v>
       </c>
-      <c r="C118" t="s">
-        <v>542</v>
+      <c r="C118" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D118" t="s">
         <v>96</v>
@@ -8205,8 +8205,8 @@
       <c r="B119">
         <v>2006</v>
       </c>
-      <c r="C119" t="s">
-        <v>542</v>
+      <c r="C119" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D119" t="s">
         <v>96</v>
@@ -8255,8 +8255,8 @@
       <c r="B120">
         <v>2006</v>
       </c>
-      <c r="C120" t="s">
-        <v>542</v>
+      <c r="C120" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D120" t="s">
         <v>96</v>
@@ -8305,8 +8305,8 @@
       <c r="B121">
         <v>2006</v>
       </c>
-      <c r="C121" t="s">
-        <v>542</v>
+      <c r="C121" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D121" t="s">
         <v>139</v>
@@ -8355,8 +8355,8 @@
       <c r="B122">
         <v>2006</v>
       </c>
-      <c r="C122" t="s">
-        <v>542</v>
+      <c r="C122" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D122" t="s">
         <v>139</v>
@@ -8405,8 +8405,8 @@
       <c r="B123">
         <v>2006</v>
       </c>
-      <c r="C123" t="s">
-        <v>542</v>
+      <c r="C123" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D123" t="s">
         <v>139</v>
@@ -8455,8 +8455,8 @@
       <c r="B124">
         <v>2006</v>
       </c>
-      <c r="C124" t="s">
-        <v>542</v>
+      <c r="C124" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D124" t="s">
         <v>139</v>
@@ -8505,8 +8505,8 @@
       <c r="B125">
         <v>2006</v>
       </c>
-      <c r="C125" t="s">
-        <v>542</v>
+      <c r="C125" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D125" t="s">
         <v>139</v>
@@ -8555,8 +8555,8 @@
       <c r="B126">
         <v>2006</v>
       </c>
-      <c r="C126" t="s">
-        <v>542</v>
+      <c r="C126" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D126" t="s">
         <v>139</v>
@@ -8605,8 +8605,8 @@
       <c r="B127">
         <v>2006</v>
       </c>
-      <c r="C127" t="s">
-        <v>542</v>
+      <c r="C127" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D127" t="s">
         <v>139</v>
@@ -8655,8 +8655,8 @@
       <c r="B128">
         <v>2006</v>
       </c>
-      <c r="C128" t="s">
-        <v>542</v>
+      <c r="C128" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D128" t="s">
         <v>139</v>
@@ -8705,8 +8705,8 @@
       <c r="B129">
         <v>2006</v>
       </c>
-      <c r="C129" t="s">
-        <v>542</v>
+      <c r="C129" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D129" t="s">
         <v>139</v>
@@ -8755,8 +8755,8 @@
       <c r="B130">
         <v>2006</v>
       </c>
-      <c r="C130" t="s">
-        <v>542</v>
+      <c r="C130" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D130" t="s">
         <v>139</v>
@@ -8805,8 +8805,8 @@
       <c r="B131">
         <v>2006</v>
       </c>
-      <c r="C131" t="s">
-        <v>542</v>
+      <c r="C131" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D131" t="s">
         <v>139</v>
@@ -8855,8 +8855,8 @@
       <c r="B132">
         <v>2006</v>
       </c>
-      <c r="C132" t="s">
-        <v>542</v>
+      <c r="C132" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D132" t="s">
         <v>139</v>
@@ -8905,8 +8905,8 @@
       <c r="B133">
         <v>2006</v>
       </c>
-      <c r="C133" t="s">
-        <v>542</v>
+      <c r="C133" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D133" t="s">
         <v>139</v>
@@ -8955,8 +8955,8 @@
       <c r="B134">
         <v>2006</v>
       </c>
-      <c r="C134" t="s">
-        <v>542</v>
+      <c r="C134" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D134" t="s">
         <v>139</v>
@@ -9005,8 +9005,8 @@
       <c r="B135">
         <v>2006</v>
       </c>
-      <c r="C135" t="s">
-        <v>542</v>
+      <c r="C135" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D135" t="s">
         <v>139</v>
@@ -9055,8 +9055,8 @@
       <c r="B136">
         <v>2006</v>
       </c>
-      <c r="C136" t="s">
-        <v>542</v>
+      <c r="C136" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D136" t="s">
         <v>139</v>
@@ -9105,8 +9105,8 @@
       <c r="B137">
         <v>2010</v>
       </c>
-      <c r="C137" t="s">
-        <v>542</v>
+      <c r="C137" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D137" t="s">
         <v>96</v>
@@ -9155,8 +9155,8 @@
       <c r="B138">
         <v>2010</v>
       </c>
-      <c r="C138" t="s">
-        <v>542</v>
+      <c r="C138" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D138" t="s">
         <v>96</v>
@@ -9205,8 +9205,8 @@
       <c r="B139">
         <v>2010</v>
       </c>
-      <c r="C139" t="s">
-        <v>542</v>
+      <c r="C139" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D139" t="s">
         <v>96</v>
@@ -9255,8 +9255,8 @@
       <c r="B140">
         <v>2010</v>
       </c>
-      <c r="C140" t="s">
-        <v>542</v>
+      <c r="C140" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D140" t="s">
         <v>96</v>
@@ -9305,8 +9305,8 @@
       <c r="B141">
         <v>2010</v>
       </c>
-      <c r="C141" t="s">
-        <v>542</v>
+      <c r="C141" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D141" t="s">
         <v>96</v>
@@ -9355,8 +9355,8 @@
       <c r="B142">
         <v>2010</v>
       </c>
-      <c r="C142" t="s">
-        <v>542</v>
+      <c r="C142" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D142" t="s">
         <v>96</v>
@@ -9405,8 +9405,8 @@
       <c r="B143">
         <v>2010</v>
       </c>
-      <c r="C143" t="s">
-        <v>542</v>
+      <c r="C143" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D143" t="s">
         <v>96</v>
@@ -9455,8 +9455,8 @@
       <c r="B144">
         <v>2010</v>
       </c>
-      <c r="C144" t="s">
-        <v>542</v>
+      <c r="C144" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D144" t="s">
         <v>96</v>
@@ -9505,8 +9505,8 @@
       <c r="B145">
         <v>2010</v>
       </c>
-      <c r="C145" t="s">
-        <v>542</v>
+      <c r="C145" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D145" t="s">
         <v>96</v>
@@ -9555,8 +9555,8 @@
       <c r="B146">
         <v>2010</v>
       </c>
-      <c r="C146" t="s">
-        <v>542</v>
+      <c r="C146" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D146" t="s">
         <v>96</v>
@@ -9605,8 +9605,8 @@
       <c r="B147">
         <v>2010</v>
       </c>
-      <c r="C147" t="s">
-        <v>542</v>
+      <c r="C147" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D147" t="s">
         <v>96</v>
@@ -9655,8 +9655,8 @@
       <c r="B148">
         <v>2010</v>
       </c>
-      <c r="C148" t="s">
-        <v>542</v>
+      <c r="C148" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D148" t="s">
         <v>96</v>
@@ -9705,8 +9705,8 @@
       <c r="B149">
         <v>2010</v>
       </c>
-      <c r="C149" t="s">
-        <v>542</v>
+      <c r="C149" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D149" t="s">
         <v>96</v>
@@ -9755,8 +9755,8 @@
       <c r="B150">
         <v>2010</v>
       </c>
-      <c r="C150" t="s">
-        <v>542</v>
+      <c r="C150" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D150" t="s">
         <v>96</v>
@@ -9805,8 +9805,8 @@
       <c r="B151">
         <v>2010</v>
       </c>
-      <c r="C151" t="s">
-        <v>542</v>
+      <c r="C151" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D151" t="s">
         <v>96</v>
@@ -9855,8 +9855,8 @@
       <c r="B152">
         <v>2010</v>
       </c>
-      <c r="C152" t="s">
-        <v>542</v>
+      <c r="C152" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D152" t="s">
         <v>96</v>
@@ -9905,8 +9905,8 @@
       <c r="B153">
         <v>2010</v>
       </c>
-      <c r="C153" t="s">
-        <v>542</v>
+      <c r="C153" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D153" t="s">
         <v>96</v>
@@ -9955,8 +9955,8 @@
       <c r="B154">
         <v>2010</v>
       </c>
-      <c r="C154" t="s">
-        <v>542</v>
+      <c r="C154" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D154" t="s">
         <v>139</v>
@@ -10005,8 +10005,8 @@
       <c r="B155">
         <v>2010</v>
       </c>
-      <c r="C155" t="s">
-        <v>542</v>
+      <c r="C155" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D155" t="s">
         <v>139</v>
@@ -10055,8 +10055,8 @@
       <c r="B156">
         <v>2010</v>
       </c>
-      <c r="C156" t="s">
-        <v>542</v>
+      <c r="C156" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D156" t="s">
         <v>139</v>
@@ -10105,8 +10105,8 @@
       <c r="B157">
         <v>2010</v>
       </c>
-      <c r="C157" t="s">
-        <v>542</v>
+      <c r="C157" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D157" t="s">
         <v>139</v>
@@ -10155,8 +10155,8 @@
       <c r="B158">
         <v>2010</v>
       </c>
-      <c r="C158" t="s">
-        <v>542</v>
+      <c r="C158" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D158" t="s">
         <v>139</v>
@@ -10205,8 +10205,8 @@
       <c r="B159">
         <v>2010</v>
       </c>
-      <c r="C159" t="s">
-        <v>542</v>
+      <c r="C159" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D159" t="s">
         <v>139</v>
@@ -10255,8 +10255,8 @@
       <c r="B160">
         <v>2010</v>
       </c>
-      <c r="C160" t="s">
-        <v>542</v>
+      <c r="C160" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D160" t="s">
         <v>139</v>
@@ -10305,8 +10305,8 @@
       <c r="B161">
         <v>2010</v>
       </c>
-      <c r="C161" t="s">
-        <v>542</v>
+      <c r="C161" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D161" t="s">
         <v>139</v>
@@ -10355,8 +10355,8 @@
       <c r="B162">
         <v>2010</v>
       </c>
-      <c r="C162" t="s">
-        <v>542</v>
+      <c r="C162" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D162" t="s">
         <v>139</v>
@@ -10405,8 +10405,8 @@
       <c r="B163">
         <v>2010</v>
       </c>
-      <c r="C163" t="s">
-        <v>542</v>
+      <c r="C163" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D163" t="s">
         <v>139</v>
@@ -10455,8 +10455,8 @@
       <c r="B164">
         <v>2010</v>
       </c>
-      <c r="C164" t="s">
-        <v>542</v>
+      <c r="C164" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D164" t="s">
         <v>139</v>
@@ -10505,8 +10505,8 @@
       <c r="B165">
         <v>2010</v>
       </c>
-      <c r="C165" t="s">
-        <v>542</v>
+      <c r="C165" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D165" t="s">
         <v>139</v>
@@ -10555,8 +10555,8 @@
       <c r="B166">
         <v>2010</v>
       </c>
-      <c r="C166" t="s">
-        <v>542</v>
+      <c r="C166" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D166" t="s">
         <v>139</v>
@@ -10605,8 +10605,8 @@
       <c r="B167">
         <v>2010</v>
       </c>
-      <c r="C167" t="s">
-        <v>542</v>
+      <c r="C167" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D167" t="s">
         <v>139</v>
@@ -10655,8 +10655,8 @@
       <c r="B168">
         <v>2010</v>
       </c>
-      <c r="C168" t="s">
-        <v>542</v>
+      <c r="C168" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D168" t="s">
         <v>139</v>
@@ -10705,8 +10705,8 @@
       <c r="B169">
         <v>2010</v>
       </c>
-      <c r="C169" t="s">
-        <v>542</v>
+      <c r="C169" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D169" t="s">
         <v>139</v>
@@ -10755,8 +10755,8 @@
       <c r="B170">
         <v>2010</v>
       </c>
-      <c r="C170" t="s">
-        <v>542</v>
+      <c r="C170" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D170" t="s">
         <v>139</v>
@@ -10805,8 +10805,8 @@
       <c r="B171">
         <v>2010</v>
       </c>
-      <c r="C171" t="s">
-        <v>542</v>
+      <c r="C171" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D171" t="s">
         <v>139</v>
@@ -10855,8 +10855,8 @@
       <c r="B172">
         <v>2010</v>
       </c>
-      <c r="C172" t="s">
-        <v>542</v>
+      <c r="C172" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D172" t="s">
         <v>139</v>
@@ -10905,8 +10905,8 @@
       <c r="B173">
         <v>2010</v>
       </c>
-      <c r="C173" t="s">
-        <v>542</v>
+      <c r="C173" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D173" t="s">
         <v>139</v>
@@ -10955,8 +10955,8 @@
       <c r="B174">
         <v>2010</v>
       </c>
-      <c r="C174" t="s">
-        <v>542</v>
+      <c r="C174" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D174" t="s">
         <v>139</v>
@@ -11005,8 +11005,8 @@
       <c r="B175">
         <v>2010</v>
       </c>
-      <c r="C175" t="s">
-        <v>542</v>
+      <c r="C175" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D175" t="s">
         <v>139</v>
@@ -11055,8 +11055,8 @@
       <c r="B176">
         <v>2010</v>
       </c>
-      <c r="C176" t="s">
-        <v>542</v>
+      <c r="C176" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D176" t="s">
         <v>139</v>
@@ -11105,8 +11105,8 @@
       <c r="B177">
         <v>2010</v>
       </c>
-      <c r="C177" t="s">
-        <v>542</v>
+      <c r="C177" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D177" t="s">
         <v>139</v>
@@ -11155,8 +11155,8 @@
       <c r="B178">
         <v>2010</v>
       </c>
-      <c r="C178" t="s">
-        <v>542</v>
+      <c r="C178" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D178" t="s">
         <v>139</v>
@@ -11205,8 +11205,8 @@
       <c r="B179">
         <v>2010</v>
       </c>
-      <c r="C179" t="s">
-        <v>542</v>
+      <c r="C179" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D179" t="s">
         <v>139</v>
@@ -11255,8 +11255,8 @@
       <c r="B180">
         <v>2010</v>
       </c>
-      <c r="C180" t="s">
-        <v>542</v>
+      <c r="C180" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D180" t="s">
         <v>139</v>
@@ -11305,8 +11305,8 @@
       <c r="B181">
         <v>2010</v>
       </c>
-      <c r="C181" t="s">
-        <v>542</v>
+      <c r="C181" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D181" t="s">
         <v>139</v>
@@ -11355,8 +11355,8 @@
       <c r="B182">
         <v>2010</v>
       </c>
-      <c r="C182" t="s">
-        <v>542</v>
+      <c r="C182" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D182" t="s">
         <v>139</v>
@@ -11405,8 +11405,8 @@
       <c r="B183">
         <v>2010</v>
       </c>
-      <c r="C183" t="s">
-        <v>542</v>
+      <c r="C183" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D183" t="s">
         <v>139</v>
@@ -11455,8 +11455,8 @@
       <c r="B184">
         <v>2010</v>
       </c>
-      <c r="C184" t="s">
-        <v>542</v>
+      <c r="C184" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D184" t="s">
         <v>139</v>
@@ -11505,8 +11505,8 @@
       <c r="B185">
         <v>2010</v>
       </c>
-      <c r="C185" t="s">
-        <v>542</v>
+      <c r="C185" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D185" t="s">
         <v>139</v>
@@ -11555,8 +11555,8 @@
       <c r="B186">
         <v>2010</v>
       </c>
-      <c r="C186" t="s">
-        <v>542</v>
+      <c r="C186" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D186" t="s">
         <v>139</v>
@@ -11605,8 +11605,8 @@
       <c r="B187">
         <v>2010</v>
       </c>
-      <c r="C187" t="s">
-        <v>542</v>
+      <c r="C187" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D187" t="s">
         <v>139</v>
@@ -11655,8 +11655,8 @@
       <c r="B188">
         <v>2010</v>
       </c>
-      <c r="C188" t="s">
-        <v>542</v>
+      <c r="C188" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D188" t="s">
         <v>139</v>
@@ -11705,8 +11705,8 @@
       <c r="B189">
         <v>2010</v>
       </c>
-      <c r="C189" t="s">
-        <v>542</v>
+      <c r="C189" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D189" t="s">
         <v>139</v>
@@ -11755,8 +11755,8 @@
       <c r="B190">
         <v>2010</v>
       </c>
-      <c r="C190" t="s">
-        <v>542</v>
+      <c r="C190" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D190" t="s">
         <v>139</v>
@@ -11805,8 +11805,8 @@
       <c r="B191">
         <v>2010</v>
       </c>
-      <c r="C191" t="s">
-        <v>542</v>
+      <c r="C191" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D191" t="s">
         <v>139</v>
@@ -11855,8 +11855,8 @@
       <c r="B192">
         <v>2010</v>
       </c>
-      <c r="C192" t="s">
-        <v>542</v>
+      <c r="C192" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D192" t="s">
         <v>139</v>
@@ -11905,8 +11905,8 @@
       <c r="B193">
         <v>2010</v>
       </c>
-      <c r="C193" t="s">
-        <v>542</v>
+      <c r="C193" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D193" t="s">
         <v>139</v>
@@ -11955,8 +11955,8 @@
       <c r="B194">
         <v>2010</v>
       </c>
-      <c r="C194" t="s">
-        <v>542</v>
+      <c r="C194" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D194" t="s">
         <v>139</v>
@@ -12005,8 +12005,8 @@
       <c r="B195">
         <v>2010</v>
       </c>
-      <c r="C195" t="s">
-        <v>542</v>
+      <c r="C195" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D195" t="s">
         <v>139</v>
@@ -12055,8 +12055,8 @@
       <c r="B196">
         <v>2010</v>
       </c>
-      <c r="C196" t="s">
-        <v>542</v>
+      <c r="C196" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D196" t="s">
         <v>139</v>
@@ -12105,8 +12105,8 @@
       <c r="B197">
         <v>2010</v>
       </c>
-      <c r="C197" t="s">
-        <v>542</v>
+      <c r="C197" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D197" t="s">
         <v>139</v>
@@ -12155,8 +12155,8 @@
       <c r="B198">
         <v>2010</v>
       </c>
-      <c r="C198" t="s">
-        <v>542</v>
+      <c r="C198" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D198" t="s">
         <v>139</v>
@@ -12205,8 +12205,8 @@
       <c r="B199">
         <v>2010</v>
       </c>
-      <c r="C199" t="s">
-        <v>542</v>
+      <c r="C199" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D199" t="s">
         <v>139</v>
@@ -12255,8 +12255,8 @@
       <c r="B200">
         <v>2010</v>
       </c>
-      <c r="C200" t="s">
-        <v>542</v>
+      <c r="C200" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D200" t="s">
         <v>139</v>
@@ -12305,8 +12305,8 @@
       <c r="B201">
         <v>2010</v>
       </c>
-      <c r="C201" t="s">
-        <v>542</v>
+      <c r="C201" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D201" t="s">
         <v>139</v>
@@ -12355,8 +12355,8 @@
       <c r="B202">
         <v>2010</v>
       </c>
-      <c r="C202" t="s">
-        <v>542</v>
+      <c r="C202" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D202" t="s">
         <v>139</v>
@@ -12405,8 +12405,8 @@
       <c r="B203">
         <v>2010</v>
       </c>
-      <c r="C203" t="s">
-        <v>542</v>
+      <c r="C203" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D203" t="s">
         <v>139</v>
@@ -12455,8 +12455,8 @@
       <c r="B204">
         <v>2010</v>
       </c>
-      <c r="C204" t="s">
-        <v>542</v>
+      <c r="C204" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D204" t="s">
         <v>139</v>
@@ -12505,8 +12505,8 @@
       <c r="B205">
         <v>2010</v>
       </c>
-      <c r="C205" t="s">
-        <v>542</v>
+      <c r="C205" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D205" t="s">
         <v>139</v>
@@ -12555,8 +12555,8 @@
       <c r="B206">
         <v>2010</v>
       </c>
-      <c r="C206" t="s">
-        <v>542</v>
+      <c r="C206" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D206" t="s">
         <v>139</v>
@@ -12605,8 +12605,8 @@
       <c r="B207">
         <v>2010</v>
       </c>
-      <c r="C207" t="s">
-        <v>542</v>
+      <c r="C207" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D207" t="s">
         <v>139</v>
@@ -12655,8 +12655,8 @@
       <c r="B208">
         <v>2010</v>
       </c>
-      <c r="C208" t="s">
-        <v>542</v>
+      <c r="C208" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D208" t="s">
         <v>139</v>
@@ -12705,8 +12705,8 @@
       <c r="B209">
         <v>2010</v>
       </c>
-      <c r="C209" t="s">
-        <v>542</v>
+      <c r="C209" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D209" t="s">
         <v>139</v>
@@ -12755,8 +12755,8 @@
       <c r="B210">
         <v>2010</v>
       </c>
-      <c r="C210" t="s">
-        <v>542</v>
+      <c r="C210" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D210" t="s">
         <v>139</v>
@@ -12805,8 +12805,8 @@
       <c r="B211">
         <v>2010</v>
       </c>
-      <c r="C211" t="s">
-        <v>542</v>
+      <c r="C211" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D211" t="s">
         <v>139</v>
@@ -12855,8 +12855,8 @@
       <c r="B212">
         <v>2010</v>
       </c>
-      <c r="C212" t="s">
-        <v>542</v>
+      <c r="C212" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D212" t="s">
         <v>139</v>
@@ -12905,8 +12905,8 @@
       <c r="B213">
         <v>2010</v>
       </c>
-      <c r="C213" t="s">
-        <v>542</v>
+      <c r="C213" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D213" t="s">
         <v>139</v>
@@ -12955,8 +12955,8 @@
       <c r="B214">
         <v>2010</v>
       </c>
-      <c r="C214" t="s">
-        <v>542</v>
+      <c r="C214" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D214" t="s">
         <v>139</v>
@@ -13005,8 +13005,8 @@
       <c r="B215">
         <v>2010</v>
       </c>
-      <c r="C215" t="s">
-        <v>542</v>
+      <c r="C215" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D215" t="s">
         <v>139</v>
@@ -13055,8 +13055,8 @@
       <c r="B216">
         <v>2010</v>
       </c>
-      <c r="C216" t="s">
-        <v>542</v>
+      <c r="C216" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D216" t="s">
         <v>139</v>
@@ -13105,8 +13105,8 @@
       <c r="B217">
         <v>2010</v>
       </c>
-      <c r="C217" t="s">
-        <v>542</v>
+      <c r="C217" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D217" t="s">
         <v>139</v>
@@ -13155,8 +13155,8 @@
       <c r="B218">
         <v>2010</v>
       </c>
-      <c r="C218" t="s">
-        <v>542</v>
+      <c r="C218" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D218" t="s">
         <v>139</v>
@@ -13205,8 +13205,8 @@
       <c r="B219">
         <v>2010</v>
       </c>
-      <c r="C219" t="s">
-        <v>542</v>
+      <c r="C219" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D219" t="s">
         <v>139</v>
@@ -13255,8 +13255,8 @@
       <c r="B220">
         <v>2010</v>
       </c>
-      <c r="C220" t="s">
-        <v>542</v>
+      <c r="C220" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D220" t="s">
         <v>139</v>
@@ -13305,8 +13305,8 @@
       <c r="B221">
         <v>2010</v>
       </c>
-      <c r="C221" t="s">
-        <v>542</v>
+      <c r="C221" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D221" t="s">
         <v>96</v>
@@ -13355,8 +13355,8 @@
       <c r="B222">
         <v>2010</v>
       </c>
-      <c r="C222" t="s">
-        <v>542</v>
+      <c r="C222" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D222" t="s">
         <v>96</v>
@@ -13405,8 +13405,8 @@
       <c r="B223">
         <v>2010</v>
       </c>
-      <c r="C223" t="s">
-        <v>542</v>
+      <c r="C223" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D223" t="s">
         <v>96</v>
@@ -13455,8 +13455,8 @@
       <c r="B224">
         <v>2010</v>
       </c>
-      <c r="C224" t="s">
-        <v>542</v>
+      <c r="C224" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D224" t="s">
         <v>96</v>
@@ -13505,8 +13505,8 @@
       <c r="B225">
         <v>2010</v>
       </c>
-      <c r="C225" t="s">
-        <v>542</v>
+      <c r="C225" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D225" t="s">
         <v>96</v>
@@ -13555,8 +13555,8 @@
       <c r="B226">
         <v>2010</v>
       </c>
-      <c r="C226" t="s">
-        <v>542</v>
+      <c r="C226" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D226" t="s">
         <v>96</v>
@@ -13605,8 +13605,8 @@
       <c r="B227">
         <v>2010</v>
       </c>
-      <c r="C227" t="s">
-        <v>542</v>
+      <c r="C227" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D227" t="s">
         <v>96</v>
@@ -13655,8 +13655,8 @@
       <c r="B228">
         <v>2010</v>
       </c>
-      <c r="C228" t="s">
-        <v>542</v>
+      <c r="C228" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D228" t="s">
         <v>96</v>
@@ -13705,8 +13705,8 @@
       <c r="B229">
         <v>2010</v>
       </c>
-      <c r="C229" t="s">
-        <v>542</v>
+      <c r="C229" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D229" t="s">
         <v>96</v>
@@ -13755,8 +13755,8 @@
       <c r="B230">
         <v>2010</v>
       </c>
-      <c r="C230" t="s">
-        <v>542</v>
+      <c r="C230" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D230" t="s">
         <v>96</v>
@@ -13805,8 +13805,8 @@
       <c r="B231">
         <v>2010</v>
       </c>
-      <c r="C231" t="s">
-        <v>542</v>
+      <c r="C231" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D231" t="s">
         <v>96</v>
@@ -13855,8 +13855,8 @@
       <c r="B232">
         <v>2010</v>
       </c>
-      <c r="C232" t="s">
-        <v>542</v>
+      <c r="C232" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D232" t="s">
         <v>96</v>
@@ -13905,8 +13905,8 @@
       <c r="B233">
         <v>2010</v>
       </c>
-      <c r="C233" t="s">
-        <v>542</v>
+      <c r="C233" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D233" t="s">
         <v>96</v>
@@ -13955,8 +13955,8 @@
       <c r="B234">
         <v>2010</v>
       </c>
-      <c r="C234" t="s">
-        <v>542</v>
+      <c r="C234" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D234" t="s">
         <v>96</v>
@@ -14005,8 +14005,8 @@
       <c r="B235">
         <v>2010</v>
       </c>
-      <c r="C235" t="s">
-        <v>542</v>
+      <c r="C235" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D235" t="s">
         <v>96</v>
@@ -14055,8 +14055,8 @@
       <c r="B236">
         <v>2010</v>
       </c>
-      <c r="C236" t="s">
-        <v>542</v>
+      <c r="C236" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D236" t="s">
         <v>96</v>
@@ -14105,8 +14105,8 @@
       <c r="B237">
         <v>2010</v>
       </c>
-      <c r="C237" t="s">
-        <v>542</v>
+      <c r="C237" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D237" t="s">
         <v>96</v>
@@ -14155,8 +14155,8 @@
       <c r="B238">
         <v>2010</v>
       </c>
-      <c r="C238" t="s">
-        <v>542</v>
+      <c r="C238" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D238" t="s">
         <v>139</v>
@@ -14205,8 +14205,8 @@
       <c r="B239">
         <v>2010</v>
       </c>
-      <c r="C239" t="s">
-        <v>542</v>
+      <c r="C239" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D239" t="s">
         <v>139</v>
@@ -14255,8 +14255,8 @@
       <c r="B240">
         <v>2010</v>
       </c>
-      <c r="C240" t="s">
-        <v>542</v>
+      <c r="C240" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D240" t="s">
         <v>139</v>
@@ -14305,8 +14305,8 @@
       <c r="B241">
         <v>2010</v>
       </c>
-      <c r="C241" t="s">
-        <v>542</v>
+      <c r="C241" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D241" t="s">
         <v>139</v>
@@ -14355,8 +14355,8 @@
       <c r="B242">
         <v>2010</v>
       </c>
-      <c r="C242" t="s">
-        <v>542</v>
+      <c r="C242" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D242" t="s">
         <v>139</v>
@@ -14405,8 +14405,8 @@
       <c r="B243">
         <v>2010</v>
       </c>
-      <c r="C243" t="s">
-        <v>542</v>
+      <c r="C243" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D243" t="s">
         <v>139</v>
@@ -14455,8 +14455,8 @@
       <c r="B244">
         <v>2010</v>
       </c>
-      <c r="C244" t="s">
-        <v>542</v>
+      <c r="C244" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D244" t="s">
         <v>139</v>
@@ -14505,8 +14505,8 @@
       <c r="B245">
         <v>2010</v>
       </c>
-      <c r="C245" t="s">
-        <v>542</v>
+      <c r="C245" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D245" t="s">
         <v>139</v>
@@ -14555,8 +14555,8 @@
       <c r="B246">
         <v>2010</v>
       </c>
-      <c r="C246" t="s">
-        <v>542</v>
+      <c r="C246" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D246" t="s">
         <v>139</v>
@@ -14605,8 +14605,8 @@
       <c r="B247">
         <v>2010</v>
       </c>
-      <c r="C247" t="s">
-        <v>542</v>
+      <c r="C247" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D247" t="s">
         <v>139</v>
@@ -14655,8 +14655,8 @@
       <c r="B248">
         <v>2010</v>
       </c>
-      <c r="C248" t="s">
-        <v>542</v>
+      <c r="C248" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D248" t="s">
         <v>139</v>
@@ -14705,8 +14705,8 @@
       <c r="B249">
         <v>2010</v>
       </c>
-      <c r="C249" t="s">
-        <v>542</v>
+      <c r="C249" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D249" t="s">
         <v>139</v>
@@ -14755,8 +14755,8 @@
       <c r="B250">
         <v>2010</v>
       </c>
-      <c r="C250" t="s">
-        <v>542</v>
+      <c r="C250" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D250" t="s">
         <v>139</v>
@@ -14805,8 +14805,8 @@
       <c r="B251">
         <v>2010</v>
       </c>
-      <c r="C251" t="s">
-        <v>542</v>
+      <c r="C251" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D251" t="s">
         <v>139</v>
@@ -14855,8 +14855,8 @@
       <c r="B252">
         <v>2010</v>
       </c>
-      <c r="C252" t="s">
-        <v>542</v>
+      <c r="C252" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D252" t="s">
         <v>139</v>
@@ -14905,8 +14905,8 @@
       <c r="B253">
         <v>2010</v>
       </c>
-      <c r="C253" t="s">
-        <v>542</v>
+      <c r="C253" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D253" t="s">
         <v>139</v>
@@ -14955,8 +14955,8 @@
       <c r="B254">
         <v>2010</v>
       </c>
-      <c r="C254" t="s">
-        <v>542</v>
+      <c r="C254" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D254" t="s">
         <v>139</v>
@@ -15005,8 +15005,8 @@
       <c r="B255">
         <v>2010</v>
       </c>
-      <c r="C255" t="s">
-        <v>542</v>
+      <c r="C255" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D255" t="s">
         <v>139</v>
@@ -15055,8 +15055,8 @@
       <c r="B256">
         <v>2010</v>
       </c>
-      <c r="C256" t="s">
-        <v>542</v>
+      <c r="C256" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D256" t="s">
         <v>139</v>
@@ -15105,8 +15105,8 @@
       <c r="B257">
         <v>2010</v>
       </c>
-      <c r="C257" t="s">
-        <v>542</v>
+      <c r="C257" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D257" t="s">
         <v>139</v>
@@ -15155,8 +15155,8 @@
       <c r="B258">
         <v>2010</v>
       </c>
-      <c r="C258" t="s">
-        <v>542</v>
+      <c r="C258" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D258" t="s">
         <v>139</v>
@@ -15205,8 +15205,8 @@
       <c r="B259">
         <v>2010</v>
       </c>
-      <c r="C259" t="s">
-        <v>542</v>
+      <c r="C259" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D259" t="s">
         <v>139</v>
@@ -15255,8 +15255,8 @@
       <c r="B260">
         <v>2010</v>
       </c>
-      <c r="C260" t="s">
-        <v>542</v>
+      <c r="C260" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D260" t="s">
         <v>139</v>
@@ -15305,8 +15305,8 @@
       <c r="B261">
         <v>2010</v>
       </c>
-      <c r="C261" t="s">
-        <v>542</v>
+      <c r="C261" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D261" t="s">
         <v>139</v>
@@ -15355,8 +15355,8 @@
       <c r="B262">
         <v>2010</v>
       </c>
-      <c r="C262" t="s">
-        <v>542</v>
+      <c r="C262" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D262" t="s">
         <v>139</v>
@@ -15405,8 +15405,8 @@
       <c r="B263">
         <v>2010</v>
       </c>
-      <c r="C263" t="s">
-        <v>542</v>
+      <c r="C263" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D263" t="s">
         <v>139</v>
@@ -15455,8 +15455,8 @@
       <c r="B264">
         <v>2010</v>
       </c>
-      <c r="C264" t="s">
-        <v>542</v>
+      <c r="C264" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D264" t="s">
         <v>139</v>
@@ -15505,8 +15505,8 @@
       <c r="B265">
         <v>2010</v>
       </c>
-      <c r="C265" t="s">
-        <v>542</v>
+      <c r="C265" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D265" t="s">
         <v>139</v>
@@ -15555,8 +15555,8 @@
       <c r="B266">
         <v>2010</v>
       </c>
-      <c r="C266" t="s">
-        <v>542</v>
+      <c r="C266" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D266" t="s">
         <v>139</v>
@@ -15605,8 +15605,8 @@
       <c r="B267">
         <v>2010</v>
       </c>
-      <c r="C267" t="s">
-        <v>542</v>
+      <c r="C267" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D267" t="s">
         <v>139</v>
@@ -15655,8 +15655,8 @@
       <c r="B268">
         <v>2010</v>
       </c>
-      <c r="C268" t="s">
-        <v>542</v>
+      <c r="C268" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D268" t="s">
         <v>139</v>
@@ -15705,8 +15705,8 @@
       <c r="B269">
         <v>2010</v>
       </c>
-      <c r="C269" t="s">
-        <v>542</v>
+      <c r="C269" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D269" t="s">
         <v>139</v>
@@ -15755,8 +15755,8 @@
       <c r="B270">
         <v>2010</v>
       </c>
-      <c r="C270" t="s">
-        <v>542</v>
+      <c r="C270" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D270" t="s">
         <v>139</v>
@@ -15805,8 +15805,8 @@
       <c r="B271">
         <v>2010</v>
       </c>
-      <c r="C271" t="s">
-        <v>542</v>
+      <c r="C271" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D271" t="s">
         <v>139</v>
@@ -15855,8 +15855,8 @@
       <c r="B272">
         <v>2010</v>
       </c>
-      <c r="C272" t="s">
-        <v>542</v>
+      <c r="C272" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D272" t="s">
         <v>96</v>
@@ -15905,8 +15905,8 @@
       <c r="B273">
         <v>2010</v>
       </c>
-      <c r="C273" t="s">
-        <v>542</v>
+      <c r="C273" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D273" t="s">
         <v>96</v>
@@ -15955,8 +15955,8 @@
       <c r="B274">
         <v>2010</v>
       </c>
-      <c r="C274" t="s">
-        <v>542</v>
+      <c r="C274" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D274" t="s">
         <v>96</v>
@@ -16005,8 +16005,8 @@
       <c r="B275">
         <v>2010</v>
       </c>
-      <c r="C275" t="s">
-        <v>542</v>
+      <c r="C275" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D275" t="s">
         <v>96</v>
@@ -16055,8 +16055,8 @@
       <c r="B276">
         <v>2010</v>
       </c>
-      <c r="C276" t="s">
-        <v>542</v>
+      <c r="C276" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D276" t="s">
         <v>96</v>
@@ -16105,8 +16105,8 @@
       <c r="B277">
         <v>2010</v>
       </c>
-      <c r="C277" t="s">
-        <v>542</v>
+      <c r="C277" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D277" t="s">
         <v>96</v>
@@ -16155,8 +16155,8 @@
       <c r="B278">
         <v>2010</v>
       </c>
-      <c r="C278" t="s">
-        <v>542</v>
+      <c r="C278" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D278" t="s">
         <v>96</v>
@@ -16205,8 +16205,8 @@
       <c r="B279">
         <v>2010</v>
       </c>
-      <c r="C279" t="s">
-        <v>542</v>
+      <c r="C279" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D279" t="s">
         <v>96</v>
@@ -16255,8 +16255,8 @@
       <c r="B280">
         <v>2010</v>
       </c>
-      <c r="C280" t="s">
-        <v>542</v>
+      <c r="C280" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D280" t="s">
         <v>139</v>
@@ -16305,8 +16305,8 @@
       <c r="B281">
         <v>2010</v>
       </c>
-      <c r="C281" t="s">
-        <v>542</v>
+      <c r="C281" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D281" t="s">
         <v>139</v>
@@ -16355,8 +16355,8 @@
       <c r="B282">
         <v>2010</v>
       </c>
-      <c r="C282" t="s">
-        <v>542</v>
+      <c r="C282" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D282" t="s">
         <v>139</v>
@@ -16405,8 +16405,8 @@
       <c r="B283">
         <v>2010</v>
       </c>
-      <c r="C283" t="s">
-        <v>542</v>
+      <c r="C283" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D283" t="s">
         <v>139</v>
@@ -16455,8 +16455,8 @@
       <c r="B284">
         <v>2010</v>
       </c>
-      <c r="C284" t="s">
-        <v>542</v>
+      <c r="C284" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D284" t="s">
         <v>139</v>
@@ -16505,8 +16505,8 @@
       <c r="B285">
         <v>2010</v>
       </c>
-      <c r="C285" t="s">
-        <v>542</v>
+      <c r="C285" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D285" t="s">
         <v>139</v>
@@ -16555,8 +16555,8 @@
       <c r="B286">
         <v>2010</v>
       </c>
-      <c r="C286" t="s">
-        <v>542</v>
+      <c r="C286" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D286" t="s">
         <v>139</v>
@@ -16605,8 +16605,8 @@
       <c r="B287">
         <v>2010</v>
       </c>
-      <c r="C287" t="s">
-        <v>542</v>
+      <c r="C287" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D287" t="s">
         <v>139</v>
@@ -16655,8 +16655,8 @@
       <c r="B288">
         <v>2010</v>
       </c>
-      <c r="C288" t="s">
-        <v>542</v>
+      <c r="C288" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D288" t="s">
         <v>139</v>
@@ -16705,8 +16705,8 @@
       <c r="B289">
         <v>2010</v>
       </c>
-      <c r="C289" t="s">
-        <v>542</v>
+      <c r="C289" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D289" t="s">
         <v>139</v>
@@ -16755,8 +16755,8 @@
       <c r="B290">
         <v>2010</v>
       </c>
-      <c r="C290" t="s">
-        <v>542</v>
+      <c r="C290" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D290" t="s">
         <v>139</v>
@@ -16805,8 +16805,8 @@
       <c r="B291">
         <v>2010</v>
       </c>
-      <c r="C291" t="s">
-        <v>542</v>
+      <c r="C291" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D291" t="s">
         <v>139</v>
@@ -16855,8 +16855,8 @@
       <c r="B292">
         <v>2010</v>
       </c>
-      <c r="C292" t="s">
-        <v>542</v>
+      <c r="C292" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D292" t="s">
         <v>139</v>
@@ -16905,8 +16905,8 @@
       <c r="B293">
         <v>2010</v>
       </c>
-      <c r="C293" t="s">
-        <v>542</v>
+      <c r="C293" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D293" t="s">
         <v>139</v>
@@ -16955,8 +16955,8 @@
       <c r="B294">
         <v>2010</v>
       </c>
-      <c r="C294" t="s">
-        <v>542</v>
+      <c r="C294" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D294" t="s">
         <v>139</v>
@@ -17005,8 +17005,8 @@
       <c r="B295">
         <v>2010</v>
       </c>
-      <c r="C295" t="s">
-        <v>542</v>
+      <c r="C295" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D295" t="s">
         <v>139</v>
@@ -17055,8 +17055,8 @@
       <c r="B296">
         <v>2010</v>
       </c>
-      <c r="C296" t="s">
-        <v>542</v>
+      <c r="C296" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D296" t="s">
         <v>139</v>
@@ -17105,8 +17105,8 @@
       <c r="B297">
         <v>2010</v>
       </c>
-      <c r="C297" t="s">
-        <v>542</v>
+      <c r="C297" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D297" t="s">
         <v>139</v>
@@ -17155,8 +17155,8 @@
       <c r="B298">
         <v>2010</v>
       </c>
-      <c r="C298" t="s">
-        <v>542</v>
+      <c r="C298" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D298" t="s">
         <v>139</v>
@@ -17205,8 +17205,8 @@
       <c r="B299">
         <v>2010</v>
       </c>
-      <c r="C299" t="s">
-        <v>542</v>
+      <c r="C299" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D299" t="s">
         <v>139</v>
@@ -17255,8 +17255,8 @@
       <c r="B300">
         <v>2010</v>
       </c>
-      <c r="C300" t="s">
-        <v>542</v>
+      <c r="C300" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D300" t="s">
         <v>139</v>
@@ -17305,8 +17305,8 @@
       <c r="B301">
         <v>2010</v>
       </c>
-      <c r="C301" t="s">
-        <v>542</v>
+      <c r="C301" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D301" t="s">
         <v>139</v>
@@ -17355,8 +17355,8 @@
       <c r="B302">
         <v>2010</v>
       </c>
-      <c r="C302" t="s">
-        <v>542</v>
+      <c r="C302" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D302" t="s">
         <v>139</v>
@@ -17405,8 +17405,8 @@
       <c r="B303">
         <v>2010</v>
       </c>
-      <c r="C303" t="s">
-        <v>542</v>
+      <c r="C303" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D303" t="s">
         <v>139</v>
@@ -17455,8 +17455,8 @@
       <c r="B304">
         <v>2010</v>
       </c>
-      <c r="C304" t="s">
-        <v>542</v>
+      <c r="C304" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D304" t="s">
         <v>139</v>
@@ -17505,8 +17505,8 @@
       <c r="B305">
         <v>2010</v>
       </c>
-      <c r="C305" t="s">
-        <v>542</v>
+      <c r="C305" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D305" t="s">
         <v>139</v>
@@ -17555,8 +17555,8 @@
       <c r="B306">
         <v>2010</v>
       </c>
-      <c r="C306" t="s">
-        <v>542</v>
+      <c r="C306" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D306" t="s">
         <v>139</v>
@@ -17605,8 +17605,8 @@
       <c r="B307">
         <v>2010</v>
       </c>
-      <c r="C307" t="s">
-        <v>542</v>
+      <c r="C307" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D307" t="s">
         <v>96</v>
@@ -17655,8 +17655,8 @@
       <c r="B308">
         <v>2010</v>
       </c>
-      <c r="C308" t="s">
-        <v>542</v>
+      <c r="C308" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D308" t="s">
         <v>96</v>
@@ -17705,8 +17705,8 @@
       <c r="B309">
         <v>2010</v>
       </c>
-      <c r="C309" t="s">
-        <v>542</v>
+      <c r="C309" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D309" t="s">
         <v>96</v>
@@ -17755,8 +17755,8 @@
       <c r="B310">
         <v>2010</v>
       </c>
-      <c r="C310" t="s">
-        <v>542</v>
+      <c r="C310" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D310" t="s">
         <v>96</v>
@@ -17805,8 +17805,8 @@
       <c r="B311">
         <v>2010</v>
       </c>
-      <c r="C311" t="s">
-        <v>542</v>
+      <c r="C311" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D311" t="s">
         <v>96</v>
@@ -17855,8 +17855,8 @@
       <c r="B312">
         <v>2010</v>
       </c>
-      <c r="C312" t="s">
-        <v>542</v>
+      <c r="C312" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D312" t="s">
         <v>96</v>
@@ -17905,8 +17905,8 @@
       <c r="B313">
         <v>2010</v>
       </c>
-      <c r="C313" t="s">
-        <v>542</v>
+      <c r="C313" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D313" t="s">
         <v>96</v>
@@ -17955,8 +17955,8 @@
       <c r="B314">
         <v>2010</v>
       </c>
-      <c r="C314" t="s">
-        <v>542</v>
+      <c r="C314" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D314" t="s">
         <v>96</v>
@@ -18005,8 +18005,8 @@
       <c r="B315">
         <v>2010</v>
       </c>
-      <c r="C315" t="s">
-        <v>542</v>
+      <c r="C315" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D315" t="s">
         <v>96</v>
@@ -18055,8 +18055,8 @@
       <c r="B316">
         <v>2010</v>
       </c>
-      <c r="C316" t="s">
-        <v>542</v>
+      <c r="C316" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D316" t="s">
         <v>96</v>
@@ -18105,8 +18105,8 @@
       <c r="B317">
         <v>2010</v>
       </c>
-      <c r="C317" t="s">
-        <v>542</v>
+      <c r="C317" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D317" t="s">
         <v>96</v>
@@ -18155,8 +18155,8 @@
       <c r="B318">
         <v>2010</v>
       </c>
-      <c r="C318" t="s">
-        <v>542</v>
+      <c r="C318" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D318" t="s">
         <v>96</v>
@@ -18205,8 +18205,8 @@
       <c r="B319">
         <v>2010</v>
       </c>
-      <c r="C319" t="s">
-        <v>542</v>
+      <c r="C319" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D319" t="s">
         <v>96</v>
@@ -18255,8 +18255,8 @@
       <c r="B320">
         <v>2010</v>
       </c>
-      <c r="C320" t="s">
-        <v>542</v>
+      <c r="C320" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D320" t="s">
         <v>96</v>
@@ -18305,8 +18305,8 @@
       <c r="B321">
         <v>2010</v>
       </c>
-      <c r="C321" t="s">
-        <v>542</v>
+      <c r="C321" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D321" t="s">
         <v>96</v>
@@ -18355,8 +18355,8 @@
       <c r="B322">
         <v>2010</v>
       </c>
-      <c r="C322" t="s">
-        <v>542</v>
+      <c r="C322" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D322" t="s">
         <v>139</v>
@@ -18405,8 +18405,8 @@
       <c r="B323">
         <v>2010</v>
       </c>
-      <c r="C323" t="s">
-        <v>542</v>
+      <c r="C323" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D323" t="s">
         <v>139</v>
@@ -18455,8 +18455,8 @@
       <c r="B324">
         <v>2010</v>
       </c>
-      <c r="C324" t="s">
-        <v>542</v>
+      <c r="C324" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D324" t="s">
         <v>139</v>
@@ -18505,8 +18505,8 @@
       <c r="B325">
         <v>2010</v>
       </c>
-      <c r="C325" t="s">
-        <v>542</v>
+      <c r="C325" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D325" t="s">
         <v>139</v>
@@ -18555,8 +18555,8 @@
       <c r="B326">
         <v>2010</v>
       </c>
-      <c r="C326" t="s">
-        <v>542</v>
+      <c r="C326" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D326" t="s">
         <v>139</v>
@@ -18605,8 +18605,8 @@
       <c r="B327">
         <v>2010</v>
       </c>
-      <c r="C327" t="s">
-        <v>542</v>
+      <c r="C327" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D327" t="s">
         <v>139</v>
@@ -18655,8 +18655,8 @@
       <c r="B328">
         <v>2010</v>
       </c>
-      <c r="C328" t="s">
-        <v>542</v>
+      <c r="C328" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D328" t="s">
         <v>139</v>
@@ -18705,8 +18705,8 @@
       <c r="B329">
         <v>2010</v>
       </c>
-      <c r="C329" t="s">
-        <v>542</v>
+      <c r="C329" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D329" t="s">
         <v>139</v>
@@ -18755,8 +18755,8 @@
       <c r="B330">
         <v>2010</v>
       </c>
-      <c r="C330" t="s">
-        <v>542</v>
+      <c r="C330" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D330" t="s">
         <v>139</v>
@@ -18805,8 +18805,8 @@
       <c r="B331">
         <v>2010</v>
       </c>
-      <c r="C331" t="s">
-        <v>542</v>
+      <c r="C331" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D331" t="s">
         <v>139</v>
@@ -18855,8 +18855,8 @@
       <c r="B332">
         <v>2010</v>
       </c>
-      <c r="C332" t="s">
-        <v>542</v>
+      <c r="C332" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D332" t="s">
         <v>139</v>
@@ -18905,8 +18905,8 @@
       <c r="B333">
         <v>2010</v>
       </c>
-      <c r="C333" t="s">
-        <v>542</v>
+      <c r="C333" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D333" t="s">
         <v>139</v>
@@ -18955,8 +18955,8 @@
       <c r="B334">
         <v>2010</v>
       </c>
-      <c r="C334" t="s">
-        <v>542</v>
+      <c r="C334" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D334" t="s">
         <v>139</v>
@@ -19005,8 +19005,8 @@
       <c r="B335">
         <v>2010</v>
       </c>
-      <c r="C335" t="s">
-        <v>542</v>
+      <c r="C335" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D335" t="s">
         <v>139</v>
@@ -19055,8 +19055,8 @@
       <c r="B336">
         <v>2010</v>
       </c>
-      <c r="C336" t="s">
-        <v>542</v>
+      <c r="C336" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D336" t="s">
         <v>139</v>
@@ -19105,8 +19105,8 @@
       <c r="B337">
         <v>2010</v>
       </c>
-      <c r="C337" t="s">
-        <v>542</v>
+      <c r="C337" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D337" t="s">
         <v>139</v>
@@ -19155,8 +19155,8 @@
       <c r="B338">
         <v>2010</v>
       </c>
-      <c r="C338" t="s">
-        <v>542</v>
+      <c r="C338" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D338" t="s">
         <v>139</v>
@@ -19205,8 +19205,8 @@
       <c r="B339">
         <v>2010</v>
       </c>
-      <c r="C339" t="s">
-        <v>542</v>
+      <c r="C339" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D339" t="s">
         <v>139</v>
@@ -19255,8 +19255,8 @@
       <c r="B340">
         <v>2010</v>
       </c>
-      <c r="C340" t="s">
-        <v>542</v>
+      <c r="C340" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D340" t="s">
         <v>139</v>
@@ -19305,8 +19305,8 @@
       <c r="B341">
         <v>2010</v>
       </c>
-      <c r="C341" t="s">
-        <v>542</v>
+      <c r="C341" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D341" t="s">
         <v>139</v>
@@ -19355,8 +19355,8 @@
       <c r="B342">
         <v>2010</v>
       </c>
-      <c r="C342" t="s">
-        <v>542</v>
+      <c r="C342" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D342" t="s">
         <v>139</v>
@@ -19405,8 +19405,8 @@
       <c r="B343">
         <v>2010</v>
       </c>
-      <c r="C343" t="s">
-        <v>542</v>
+      <c r="C343" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D343" t="s">
         <v>96</v>
@@ -19455,8 +19455,8 @@
       <c r="B344">
         <v>2010</v>
       </c>
-      <c r="C344" t="s">
-        <v>542</v>
+      <c r="C344" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D344" t="s">
         <v>96</v>
@@ -19505,8 +19505,8 @@
       <c r="B345">
         <v>2010</v>
       </c>
-      <c r="C345" t="s">
-        <v>542</v>
+      <c r="C345" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D345" t="s">
         <v>96</v>
@@ -19555,8 +19555,8 @@
       <c r="B346">
         <v>2010</v>
       </c>
-      <c r="C346" t="s">
-        <v>542</v>
+      <c r="C346" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D346" t="s">
         <v>96</v>
@@ -19605,8 +19605,8 @@
       <c r="B347">
         <v>2010</v>
       </c>
-      <c r="C347" t="s">
-        <v>542</v>
+      <c r="C347" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D347" t="s">
         <v>96</v>
@@ -19655,8 +19655,8 @@
       <c r="B348">
         <v>2010</v>
       </c>
-      <c r="C348" t="s">
-        <v>542</v>
+      <c r="C348" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D348" t="s">
         <v>96</v>
@@ -19705,8 +19705,8 @@
       <c r="B349">
         <v>2010</v>
       </c>
-      <c r="C349" t="s">
-        <v>542</v>
+      <c r="C349" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D349" t="s">
         <v>96</v>
@@ -19755,8 +19755,8 @@
       <c r="B350">
         <v>2010</v>
       </c>
-      <c r="C350" t="s">
-        <v>542</v>
+      <c r="C350" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D350" t="s">
         <v>96</v>
@@ -19805,8 +19805,8 @@
       <c r="B351">
         <v>2010</v>
       </c>
-      <c r="C351" t="s">
-        <v>542</v>
+      <c r="C351" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D351" t="s">
         <v>96</v>
@@ -19855,8 +19855,8 @@
       <c r="B352">
         <v>2010</v>
       </c>
-      <c r="C352" t="s">
-        <v>542</v>
+      <c r="C352" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D352" t="s">
         <v>96</v>
@@ -19905,8 +19905,8 @@
       <c r="B353">
         <v>2010</v>
       </c>
-      <c r="C353" t="s">
-        <v>542</v>
+      <c r="C353" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D353" t="s">
         <v>96</v>
@@ -19955,8 +19955,8 @@
       <c r="B354">
         <v>2010</v>
       </c>
-      <c r="C354" t="s">
-        <v>542</v>
+      <c r="C354" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D354" t="s">
         <v>96</v>
@@ -20005,8 +20005,8 @@
       <c r="B355">
         <v>2010</v>
       </c>
-      <c r="C355" t="s">
-        <v>542</v>
+      <c r="C355" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D355" t="s">
         <v>96</v>
@@ -20055,8 +20055,8 @@
       <c r="B356">
         <v>2010</v>
       </c>
-      <c r="C356" t="s">
-        <v>542</v>
+      <c r="C356" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D356" t="s">
         <v>96</v>
@@ -20105,8 +20105,8 @@
       <c r="B357">
         <v>2010</v>
       </c>
-      <c r="C357" t="s">
-        <v>542</v>
+      <c r="C357" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D357" t="s">
         <v>96</v>
@@ -20155,8 +20155,8 @@
       <c r="B358">
         <v>2010</v>
       </c>
-      <c r="C358" t="s">
-        <v>542</v>
+      <c r="C358" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D358" t="s">
         <v>96</v>
@@ -20205,8 +20205,8 @@
       <c r="B359">
         <v>2010</v>
       </c>
-      <c r="C359" t="s">
-        <v>542</v>
+      <c r="C359" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D359" t="s">
         <v>96</v>
@@ -20255,8 +20255,8 @@
       <c r="B360">
         <v>2010</v>
       </c>
-      <c r="C360" t="s">
-        <v>542</v>
+      <c r="C360" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D360" t="s">
         <v>96</v>
@@ -20305,8 +20305,8 @@
       <c r="B361">
         <v>2010</v>
       </c>
-      <c r="C361" t="s">
-        <v>542</v>
+      <c r="C361" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D361" t="s">
         <v>96</v>
@@ -20355,8 +20355,8 @@
       <c r="B362">
         <v>2010</v>
       </c>
-      <c r="C362" t="s">
-        <v>542</v>
+      <c r="C362" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D362" t="s">
         <v>96</v>
@@ -20405,8 +20405,8 @@
       <c r="B363">
         <v>2010</v>
       </c>
-      <c r="C363" t="s">
-        <v>542</v>
+      <c r="C363" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D363" t="s">
         <v>139</v>
@@ -20455,8 +20455,8 @@
       <c r="B364">
         <v>2010</v>
       </c>
-      <c r="C364" t="s">
-        <v>542</v>
+      <c r="C364" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D364" t="s">
         <v>139</v>
@@ -20505,8 +20505,8 @@
       <c r="B365">
         <v>2010</v>
       </c>
-      <c r="C365" t="s">
-        <v>542</v>
+      <c r="C365" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D365" t="s">
         <v>139</v>
@@ -20555,8 +20555,8 @@
       <c r="B366">
         <v>2010</v>
       </c>
-      <c r="C366" t="s">
-        <v>542</v>
+      <c r="C366" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D366" t="s">
         <v>96</v>
@@ -20605,8 +20605,8 @@
       <c r="B367">
         <v>2010</v>
       </c>
-      <c r="C367" t="s">
-        <v>542</v>
+      <c r="C367" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D367" t="s">
         <v>96</v>
@@ -20655,8 +20655,8 @@
       <c r="B368">
         <v>2010</v>
       </c>
-      <c r="C368" t="s">
-        <v>542</v>
+      <c r="C368" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D368" t="s">
         <v>96</v>
@@ -20705,8 +20705,8 @@
       <c r="B369">
         <v>2010</v>
       </c>
-      <c r="C369" t="s">
-        <v>542</v>
+      <c r="C369" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D369" t="s">
         <v>96</v>
@@ -20755,8 +20755,8 @@
       <c r="B370">
         <v>2010</v>
       </c>
-      <c r="C370" t="s">
-        <v>542</v>
+      <c r="C370" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D370" t="s">
         <v>96</v>
@@ -20805,8 +20805,8 @@
       <c r="B371">
         <v>2010</v>
       </c>
-      <c r="C371" t="s">
-        <v>542</v>
+      <c r="C371" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D371" t="s">
         <v>96</v>
@@ -20855,8 +20855,8 @@
       <c r="B372">
         <v>2010</v>
       </c>
-      <c r="C372" t="s">
-        <v>542</v>
+      <c r="C372" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D372" t="s">
         <v>96</v>
@@ -20905,8 +20905,8 @@
       <c r="B373">
         <v>2010</v>
       </c>
-      <c r="C373" t="s">
-        <v>542</v>
+      <c r="C373" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D373" t="s">
         <v>96</v>
@@ -20955,8 +20955,8 @@
       <c r="B374">
         <v>2010</v>
       </c>
-      <c r="C374" t="s">
-        <v>542</v>
+      <c r="C374" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D374" t="s">
         <v>96</v>
@@ -21005,8 +21005,8 @@
       <c r="B375">
         <v>2010</v>
       </c>
-      <c r="C375" t="s">
-        <v>542</v>
+      <c r="C375" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D375" t="s">
         <v>96</v>
@@ -21055,8 +21055,8 @@
       <c r="B376">
         <v>2010</v>
       </c>
-      <c r="C376" t="s">
-        <v>542</v>
+      <c r="C376" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D376" t="s">
         <v>96</v>
@@ -21105,8 +21105,8 @@
       <c r="B377">
         <v>2010</v>
       </c>
-      <c r="C377" t="s">
-        <v>542</v>
+      <c r="C377" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D377" t="s">
         <v>96</v>
@@ -21155,8 +21155,8 @@
       <c r="B378">
         <v>2010</v>
       </c>
-      <c r="C378" t="s">
-        <v>542</v>
+      <c r="C378" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D378" t="s">
         <v>139</v>
@@ -21205,8 +21205,8 @@
       <c r="B379">
         <v>2010</v>
       </c>
-      <c r="C379" t="s">
-        <v>542</v>
+      <c r="C379" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D379" t="s">
         <v>139</v>
@@ -21255,8 +21255,8 @@
       <c r="B380">
         <v>2010</v>
       </c>
-      <c r="C380" t="s">
-        <v>542</v>
+      <c r="C380" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D380" t="s">
         <v>139</v>
@@ -21305,8 +21305,8 @@
       <c r="B381">
         <v>2010</v>
       </c>
-      <c r="C381" t="s">
-        <v>542</v>
+      <c r="C381" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D381" t="s">
         <v>139</v>
@@ -21355,8 +21355,8 @@
       <c r="B382">
         <v>2010</v>
       </c>
-      <c r="C382" t="s">
-        <v>542</v>
+      <c r="C382" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D382" t="s">
         <v>139</v>
@@ -21405,8 +21405,8 @@
       <c r="B383">
         <v>2010</v>
       </c>
-      <c r="C383" t="s">
-        <v>542</v>
+      <c r="C383" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D383" t="s">
         <v>139</v>
@@ -21455,8 +21455,8 @@
       <c r="B384">
         <v>2010</v>
       </c>
-      <c r="C384" t="s">
-        <v>542</v>
+      <c r="C384" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="E384">
         <v>47.354024785084292</v>
@@ -21502,8 +21502,8 @@
       <c r="B385">
         <v>2010</v>
       </c>
-      <c r="C385" t="s">
-        <v>542</v>
+      <c r="C385" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D385" t="s">
         <v>139</v>
@@ -21552,8 +21552,8 @@
       <c r="B386">
         <v>2010</v>
       </c>
-      <c r="C386" t="s">
-        <v>542</v>
+      <c r="C386" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D386" t="s">
         <v>139</v>
@@ -21602,8 +21602,8 @@
       <c r="B387">
         <v>2010</v>
       </c>
-      <c r="C387" t="s">
-        <v>542</v>
+      <c r="C387" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D387" t="s">
         <v>139</v>
@@ -21652,8 +21652,8 @@
       <c r="B388">
         <v>2010</v>
       </c>
-      <c r="C388" t="s">
-        <v>542</v>
+      <c r="C388" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D388" t="s">
         <v>139</v>
@@ -21702,8 +21702,8 @@
       <c r="B389">
         <v>2010</v>
       </c>
-      <c r="C389" t="s">
-        <v>542</v>
+      <c r="C389" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D389" t="s">
         <v>139</v>
@@ -21752,8 +21752,8 @@
       <c r="B390">
         <v>2010</v>
       </c>
-      <c r="C390" t="s">
-        <v>542</v>
+      <c r="C390" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D390" t="s">
         <v>139</v>
@@ -21802,14 +21802,14 @@
       <c r="B391">
         <v>2010</v>
       </c>
-      <c r="C391" t="s">
-        <v>542</v>
+      <c r="C391" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="D391" t="s">
         <v>139</v>
       </c>
       <c r="E391">
-        <v>51.590206050437793</v>
+        <v>51.5902060504378</v>
       </c>
       <c r="F391">
         <v>0.27053950610811095</v>
@@ -21852,9 +21852,10 @@
       <c r="B392">
         <v>2006</v>
       </c>
-      <c r="C392" s="3" t="s">
-        <v>550</v>
-      </c>
+      <c r="C392" t="s">
+        <v>542</v>
+      </c>
+      <c r="D392" s="3"/>
       <c r="E392">
         <v>50.215499999999999</v>
       </c>
@@ -21896,8 +21897,8 @@
       <c r="B393">
         <v>2006</v>
       </c>
-      <c r="C393" s="3" t="s">
-        <v>550</v>
+      <c r="C393" t="s">
+        <v>542</v>
       </c>
       <c r="E393">
         <v>53.144500000000001</v>
@@ -21940,8 +21941,8 @@
       <c r="B394">
         <v>2006</v>
       </c>
-      <c r="C394" s="3" t="s">
-        <v>550</v>
+      <c r="C394" t="s">
+        <v>542</v>
       </c>
       <c r="E394">
         <v>52.321399999999997</v>
@@ -21984,8 +21985,8 @@
       <c r="B395">
         <v>2006</v>
       </c>
-      <c r="C395" s="3" t="s">
-        <v>550</v>
+      <c r="C395" t="s">
+        <v>542</v>
       </c>
       <c r="E395">
         <v>52.1509</v>
@@ -22028,8 +22029,8 @@
       <c r="B396">
         <v>2006</v>
       </c>
-      <c r="C396" s="3" t="s">
-        <v>550</v>
+      <c r="C396" t="s">
+        <v>542</v>
       </c>
       <c r="E396">
         <v>50.286900000000003</v>
@@ -22072,8 +22073,8 @@
       <c r="B397">
         <v>2006</v>
       </c>
-      <c r="C397" s="3" t="s">
-        <v>550</v>
+      <c r="C397" t="s">
+        <v>542</v>
       </c>
       <c r="E397">
         <v>50.713700000000003</v>
@@ -22116,8 +22117,8 @@
       <c r="B398">
         <v>2006</v>
       </c>
-      <c r="C398" s="3" t="s">
-        <v>550</v>
+      <c r="C398" t="s">
+        <v>542</v>
       </c>
       <c r="E398">
         <v>52.264400000000002</v>
@@ -22160,8 +22161,8 @@
       <c r="B399">
         <v>2006</v>
       </c>
-      <c r="C399" s="3" t="s">
-        <v>550</v>
+      <c r="C399" t="s">
+        <v>542</v>
       </c>
       <c r="E399">
         <v>51.719200000000001</v>
@@ -22204,8 +22205,8 @@
       <c r="B400">
         <v>2006</v>
       </c>
-      <c r="C400" s="3" t="s">
-        <v>550</v>
+      <c r="C400" t="s">
+        <v>542</v>
       </c>
       <c r="E400">
         <v>51.775300000000001</v>
@@ -22248,8 +22249,8 @@
       <c r="B401">
         <v>2006</v>
       </c>
-      <c r="C401" s="3" t="s">
-        <v>550</v>
+      <c r="C401" t="s">
+        <v>542</v>
       </c>
       <c r="E401">
         <v>51.429099999999998</v>
@@ -22292,8 +22293,8 @@
       <c r="B402">
         <v>2006</v>
       </c>
-      <c r="C402" s="3" t="s">
-        <v>550</v>
+      <c r="C402" t="s">
+        <v>542</v>
       </c>
       <c r="E402">
         <v>51.997500000000002</v>
@@ -22336,8 +22337,8 @@
       <c r="B403">
         <v>2006</v>
       </c>
-      <c r="C403" s="3" t="s">
-        <v>550</v>
+      <c r="C403" t="s">
+        <v>542</v>
       </c>
       <c r="E403">
         <v>51.853000000000002</v>
@@ -22380,8 +22381,8 @@
       <c r="B404">
         <v>2006</v>
       </c>
-      <c r="C404" s="3" t="s">
-        <v>550</v>
+      <c r="C404" t="s">
+        <v>542</v>
       </c>
       <c r="E404">
         <v>52.081499999999998</v>
@@ -22424,8 +22425,8 @@
       <c r="B405">
         <v>2006</v>
       </c>
-      <c r="C405" s="3" t="s">
-        <v>550</v>
+      <c r="C405" t="s">
+        <v>542</v>
       </c>
       <c r="E405">
         <v>50.387599999999999</v>
@@ -22468,8 +22469,8 @@
       <c r="B406">
         <v>2006</v>
       </c>
-      <c r="C406" s="3" t="s">
-        <v>550</v>
+      <c r="C406" t="s">
+        <v>542</v>
       </c>
       <c r="E406">
         <v>51.983800000000002</v>
@@ -22512,8 +22513,8 @@
       <c r="B407">
         <v>2006</v>
       </c>
-      <c r="C407" s="3" t="s">
-        <v>550</v>
+      <c r="C407" t="s">
+        <v>542</v>
       </c>
       <c r="D407" t="s">
         <v>96</v>
@@ -22559,8 +22560,8 @@
       <c r="B408">
         <v>2006</v>
       </c>
-      <c r="C408" s="3" t="s">
-        <v>550</v>
+      <c r="C408" t="s">
+        <v>542</v>
       </c>
       <c r="D408" t="s">
         <v>96</v>
@@ -22606,8 +22607,8 @@
       <c r="B409">
         <v>2006</v>
       </c>
-      <c r="C409" s="3" t="s">
-        <v>550</v>
+      <c r="C409" t="s">
+        <v>542</v>
       </c>
       <c r="E409">
         <v>50.154499999999999</v>
@@ -22650,8 +22651,8 @@
       <c r="B410">
         <v>2006</v>
       </c>
-      <c r="C410" s="3" t="s">
-        <v>550</v>
+      <c r="C410" t="s">
+        <v>542</v>
       </c>
       <c r="E410">
         <v>49.400399999999998</v>
@@ -22694,8 +22695,8 @@
       <c r="B411">
         <v>2006</v>
       </c>
-      <c r="C411" s="3" t="s">
-        <v>550</v>
+      <c r="C411" t="s">
+        <v>542</v>
       </c>
       <c r="E411">
         <v>49.943600000000004</v>
@@ -22738,8 +22739,8 @@
       <c r="B412">
         <v>2006</v>
       </c>
-      <c r="C412" s="3" t="s">
-        <v>550</v>
+      <c r="C412" t="s">
+        <v>542</v>
       </c>
       <c r="E412">
         <v>49.940100000000001</v>
@@ -22782,8 +22783,8 @@
       <c r="B413">
         <v>2006</v>
       </c>
-      <c r="C413" s="3" t="s">
-        <v>550</v>
+      <c r="C413" t="s">
+        <v>542</v>
       </c>
       <c r="E413">
         <v>49.908900000000003</v>
@@ -22826,8 +22827,8 @@
       <c r="B414">
         <v>2006</v>
       </c>
-      <c r="C414" s="3" t="s">
-        <v>550</v>
+      <c r="C414" t="s">
+        <v>542</v>
       </c>
       <c r="E414">
         <v>37.328299999999999</v>
@@ -22870,8 +22871,8 @@
       <c r="B415">
         <v>2006</v>
       </c>
-      <c r="C415" s="3" t="s">
-        <v>550</v>
+      <c r="C415" t="s">
+        <v>542</v>
       </c>
       <c r="E415">
         <v>50.110500000000002</v>
@@ -22914,8 +22915,8 @@
       <c r="B416">
         <v>2006</v>
       </c>
-      <c r="C416" s="3" t="s">
-        <v>550</v>
+      <c r="C416" t="s">
+        <v>542</v>
       </c>
       <c r="D416" t="s">
         <v>96</v>
@@ -22961,8 +22962,8 @@
       <c r="B417">
         <v>2006</v>
       </c>
-      <c r="C417" s="3" t="s">
-        <v>550</v>
+      <c r="C417" t="s">
+        <v>542</v>
       </c>
       <c r="E417">
         <v>50.231400000000001</v>
@@ -23005,8 +23006,8 @@
       <c r="B418">
         <v>2006</v>
       </c>
-      <c r="C418" s="3" t="s">
-        <v>550</v>
+      <c r="C418" t="s">
+        <v>542</v>
       </c>
       <c r="E418">
         <v>50.688099999999999</v>
@@ -23049,8 +23050,8 @@
       <c r="B419">
         <v>2006</v>
       </c>
-      <c r="C419" s="3" t="s">
-        <v>550</v>
+      <c r="C419" t="s">
+        <v>542</v>
       </c>
       <c r="E419">
         <v>50.491900000000001</v>
@@ -23093,8 +23094,8 @@
       <c r="B420">
         <v>2006</v>
       </c>
-      <c r="C420" s="3" t="s">
-        <v>550</v>
+      <c r="C420" t="s">
+        <v>542</v>
       </c>
       <c r="E420">
         <v>50.802100000000003</v>
@@ -23137,8 +23138,8 @@
       <c r="B421">
         <v>2006</v>
       </c>
-      <c r="C421" s="3" t="s">
-        <v>550</v>
+      <c r="C421" t="s">
+        <v>542</v>
       </c>
       <c r="E421">
         <v>50.7361</v>
@@ -23181,8 +23182,8 @@
       <c r="B422">
         <v>2006</v>
       </c>
-      <c r="C422" s="3" t="s">
-        <v>550</v>
+      <c r="C422" t="s">
+        <v>542</v>
       </c>
       <c r="E422">
         <v>50.875900000000001</v>
@@ -23225,8 +23226,8 @@
       <c r="B423">
         <v>2006</v>
       </c>
-      <c r="C423" s="3" t="s">
-        <v>550</v>
+      <c r="C423" t="s">
+        <v>542</v>
       </c>
       <c r="E423">
         <v>50.5473</v>
@@ -23269,8 +23270,8 @@
       <c r="B424">
         <v>2006</v>
       </c>
-      <c r="C424" s="3" t="s">
-        <v>550</v>
+      <c r="C424" t="s">
+        <v>542</v>
       </c>
       <c r="E424">
         <v>51.2224</v>
@@ -23313,8 +23314,8 @@
       <c r="B425">
         <v>2006</v>
       </c>
-      <c r="C425" s="3" t="s">
-        <v>550</v>
+      <c r="C425" t="s">
+        <v>542</v>
       </c>
       <c r="E425">
         <v>47.170299999999997</v>
@@ -23357,8 +23358,8 @@
       <c r="B426">
         <v>2006</v>
       </c>
-      <c r="C426" s="3" t="s">
-        <v>550</v>
+      <c r="C426" t="s">
+        <v>542</v>
       </c>
       <c r="E426">
         <v>50.954300000000003</v>
@@ -23401,8 +23402,8 @@
       <c r="B427">
         <v>2006</v>
       </c>
-      <c r="C427" s="3" t="s">
-        <v>550</v>
+      <c r="C427" t="s">
+        <v>542</v>
       </c>
       <c r="E427">
         <v>50.542400000000001</v>
@@ -23445,8 +23446,8 @@
       <c r="B428">
         <v>2006</v>
       </c>
-      <c r="C428" s="3" t="s">
-        <v>550</v>
+      <c r="C428" t="s">
+        <v>542</v>
       </c>
       <c r="E428">
         <v>46.140500000000003</v>
@@ -23489,8 +23490,8 @@
       <c r="B429">
         <v>2006</v>
       </c>
-      <c r="C429" s="3" t="s">
-        <v>550</v>
+      <c r="C429" t="s">
+        <v>542</v>
       </c>
       <c r="E429">
         <v>51.566000000000003</v>
@@ -23533,8 +23534,8 @@
       <c r="B430">
         <v>2006</v>
       </c>
-      <c r="C430" s="3" t="s">
-        <v>550</v>
+      <c r="C430" t="s">
+        <v>542</v>
       </c>
       <c r="E430">
         <v>50.564700000000002</v>
@@ -23577,8 +23578,8 @@
       <c r="B431">
         <v>2006</v>
       </c>
-      <c r="C431" s="3" t="s">
-        <v>550</v>
+      <c r="C431" t="s">
+        <v>542</v>
       </c>
       <c r="E431">
         <v>22.904800000000002</v>
@@ -23621,8 +23622,8 @@
       <c r="B432">
         <v>2006</v>
       </c>
-      <c r="C432" s="3" t="s">
-        <v>550</v>
+      <c r="C432" t="s">
+        <v>542</v>
       </c>
       <c r="E432">
         <v>51.479599999999998</v>
@@ -23665,8 +23666,8 @@
       <c r="B433">
         <v>2006</v>
       </c>
-      <c r="C433" s="3" t="s">
-        <v>550</v>
+      <c r="C433" t="s">
+        <v>542</v>
       </c>
       <c r="E433">
         <v>51.427300000000002</v>
@@ -23709,8 +23710,8 @@
       <c r="B434">
         <v>2006</v>
       </c>
-      <c r="C434" s="3" t="s">
-        <v>550</v>
+      <c r="C434" t="s">
+        <v>542</v>
       </c>
       <c r="E434">
         <v>50.897300000000001</v>
@@ -23753,8 +23754,8 @@
       <c r="B435">
         <v>2006</v>
       </c>
-      <c r="C435" s="3" t="s">
-        <v>550</v>
+      <c r="C435" t="s">
+        <v>542</v>
       </c>
       <c r="E435">
         <v>51.141500000000001</v>
@@ -23797,8 +23798,8 @@
       <c r="B436">
         <v>2006</v>
       </c>
-      <c r="C436" s="3" t="s">
-        <v>550</v>
+      <c r="C436" t="s">
+        <v>542</v>
       </c>
       <c r="E436">
         <v>51.336100000000002</v>
@@ -23841,8 +23842,8 @@
       <c r="B437">
         <v>2006</v>
       </c>
-      <c r="C437" s="3" t="s">
-        <v>550</v>
+      <c r="C437" t="s">
+        <v>542</v>
       </c>
       <c r="E437">
         <v>51.109099999999998</v>
@@ -23885,8 +23886,8 @@
       <c r="B438">
         <v>2006</v>
       </c>
-      <c r="C438" s="3" t="s">
-        <v>550</v>
+      <c r="C438" t="s">
+        <v>542</v>
       </c>
       <c r="E438">
         <v>51.477499999999999</v>
@@ -23929,8 +23930,8 @@
       <c r="B439">
         <v>2006</v>
       </c>
-      <c r="C439" s="3" t="s">
-        <v>550</v>
+      <c r="C439" t="s">
+        <v>542</v>
       </c>
       <c r="E439">
         <v>51.2316</v>
@@ -23973,8 +23974,8 @@
       <c r="B440">
         <v>2006</v>
       </c>
-      <c r="C440" s="3" t="s">
-        <v>550</v>
+      <c r="C440" t="s">
+        <v>542</v>
       </c>
       <c r="E440">
         <v>51.453499999999998</v>
@@ -24017,8 +24018,8 @@
       <c r="B441">
         <v>2006</v>
       </c>
-      <c r="C441" s="3" t="s">
-        <v>550</v>
+      <c r="C441" t="s">
+        <v>542</v>
       </c>
       <c r="E441">
         <v>51.800699999999999</v>
@@ -24061,8 +24062,8 @@
       <c r="B442">
         <v>2006</v>
       </c>
-      <c r="C442" s="3" t="s">
-        <v>550</v>
+      <c r="C442" t="s">
+        <v>542</v>
       </c>
       <c r="E442">
         <v>50.796799999999998</v>
@@ -24105,8 +24106,8 @@
       <c r="B443">
         <v>2006</v>
       </c>
-      <c r="C443" s="3" t="s">
-        <v>550</v>
+      <c r="C443" t="s">
+        <v>542</v>
       </c>
       <c r="E443">
         <v>51.637700000000002</v>
@@ -24149,8 +24150,8 @@
       <c r="B444">
         <v>2006</v>
       </c>
-      <c r="C444" s="3" t="s">
-        <v>550</v>
+      <c r="C444" t="s">
+        <v>542</v>
       </c>
       <c r="E444">
         <v>51.4377</v>
@@ -24193,8 +24194,8 @@
       <c r="B445">
         <v>2006</v>
       </c>
-      <c r="C445" s="3" t="s">
-        <v>550</v>
+      <c r="C445" t="s">
+        <v>542</v>
       </c>
       <c r="E445">
         <v>51.680399999999999</v>
@@ -24237,8 +24238,8 @@
       <c r="B446">
         <v>2006</v>
       </c>
-      <c r="C446" s="3" t="s">
-        <v>550</v>
+      <c r="C446" t="s">
+        <v>542</v>
       </c>
       <c r="E446">
         <v>50.500500000000002</v>
@@ -24281,8 +24282,8 @@
       <c r="B447">
         <v>2006</v>
       </c>
-      <c r="C447" s="3" t="s">
-        <v>550</v>
+      <c r="C447" t="s">
+        <v>542</v>
       </c>
       <c r="E447">
         <v>51.210299999999997</v>
@@ -24325,8 +24326,8 @@
       <c r="B448">
         <v>2006</v>
       </c>
-      <c r="C448" s="3" t="s">
-        <v>550</v>
+      <c r="C448" t="s">
+        <v>542</v>
       </c>
       <c r="E448">
         <v>50.904800000000002</v>
@@ -24369,8 +24370,8 @@
       <c r="B449">
         <v>2010</v>
       </c>
-      <c r="C449" s="3" t="s">
-        <v>550</v>
+      <c r="C449" t="s">
+        <v>542</v>
       </c>
       <c r="E449">
         <v>52.600099999999998</v>
@@ -24413,8 +24414,8 @@
       <c r="B450">
         <v>2010</v>
       </c>
-      <c r="C450" s="3" t="s">
-        <v>550</v>
+      <c r="C450" t="s">
+        <v>542</v>
       </c>
       <c r="E450">
         <v>52.598500000000001</v>
@@ -24457,8 +24458,8 @@
       <c r="B451">
         <v>2010</v>
       </c>
-      <c r="C451" s="3" t="s">
-        <v>550</v>
+      <c r="C451" t="s">
+        <v>542</v>
       </c>
       <c r="E451">
         <v>52.634</v>
@@ -24501,8 +24502,8 @@
       <c r="B452">
         <v>2010</v>
       </c>
-      <c r="C452" s="3" t="s">
-        <v>550</v>
+      <c r="C452" t="s">
+        <v>542</v>
       </c>
       <c r="E452">
         <v>51.039400000000001</v>
@@ -24545,8 +24546,8 @@
       <c r="B453">
         <v>2010</v>
       </c>
-      <c r="C453" s="3" t="s">
-        <v>550</v>
+      <c r="C453" t="s">
+        <v>542</v>
       </c>
       <c r="E453">
         <v>51.640700000000002</v>
@@ -24589,8 +24590,8 @@
       <c r="B454">
         <v>2010</v>
       </c>
-      <c r="C454" s="3" t="s">
-        <v>550</v>
+      <c r="C454" t="s">
+        <v>542</v>
       </c>
       <c r="E454">
         <v>51.764699999999998</v>
@@ -24633,8 +24634,8 @@
       <c r="B455">
         <v>2010</v>
       </c>
-      <c r="C455" s="3" t="s">
-        <v>550</v>
+      <c r="C455" t="s">
+        <v>542</v>
       </c>
       <c r="E455">
         <v>50.794600000000003</v>
@@ -24677,8 +24678,8 @@
       <c r="B456">
         <v>2010</v>
       </c>
-      <c r="C456" s="3" t="s">
-        <v>550</v>
+      <c r="C456" t="s">
+        <v>542</v>
       </c>
       <c r="E456">
         <v>52.499000000000002</v>
@@ -24721,8 +24722,8 @@
       <c r="B457">
         <v>2010</v>
       </c>
-      <c r="C457" s="3" t="s">
-        <v>550</v>
+      <c r="C457" t="s">
+        <v>542</v>
       </c>
       <c r="E457">
         <v>52.428400000000003</v>
@@ -24765,8 +24766,8 @@
       <c r="B458">
         <v>2010</v>
       </c>
-      <c r="C458" s="3" t="s">
-        <v>550</v>
+      <c r="C458" t="s">
+        <v>542</v>
       </c>
       <c r="E458">
         <v>51.035499999999999</v>
@@ -24809,8 +24810,8 @@
       <c r="B459">
         <v>2010</v>
       </c>
-      <c r="C459" s="3" t="s">
-        <v>550</v>
+      <c r="C459" t="s">
+        <v>542</v>
       </c>
       <c r="E459">
         <v>51.6295</v>
@@ -24853,8 +24854,8 @@
       <c r="B460">
         <v>2010</v>
       </c>
-      <c r="C460" s="3" t="s">
-        <v>550</v>
+      <c r="C460" t="s">
+        <v>542</v>
       </c>
       <c r="E460">
         <v>51.912100000000002</v>
@@ -24897,8 +24898,8 @@
       <c r="B461">
         <v>2010</v>
       </c>
-      <c r="C461" s="3" t="s">
-        <v>550</v>
+      <c r="C461" t="s">
+        <v>542</v>
       </c>
       <c r="E461">
         <v>51.941600000000001</v>
@@ -24941,8 +24942,8 @@
       <c r="B462">
         <v>2010</v>
       </c>
-      <c r="C462" s="3" t="s">
-        <v>550</v>
+      <c r="C462" t="s">
+        <v>542</v>
       </c>
       <c r="E462">
         <v>51.648200000000003</v>
@@ -24985,8 +24986,8 @@
       <c r="B463">
         <v>2010</v>
       </c>
-      <c r="C463" s="3" t="s">
-        <v>550</v>
+      <c r="C463" t="s">
+        <v>542</v>
       </c>
       <c r="E463">
         <v>48.392299999999999</v>
@@ -25029,8 +25030,8 @@
       <c r="B464">
         <v>2010</v>
       </c>
-      <c r="C464" s="3" t="s">
-        <v>550</v>
+      <c r="C464" t="s">
+        <v>542</v>
       </c>
       <c r="E464">
         <v>46.825200000000002</v>
@@ -25073,8 +25074,8 @@
       <c r="B465">
         <v>2010</v>
       </c>
-      <c r="C465" s="3" t="s">
-        <v>550</v>
+      <c r="C465" t="s">
+        <v>542</v>
       </c>
       <c r="E465">
         <v>47.657699999999998</v>
@@ -25117,8 +25118,8 @@
       <c r="B466">
         <v>2010</v>
       </c>
-      <c r="C466" s="3" t="s">
-        <v>550</v>
+      <c r="C466" t="s">
+        <v>542</v>
       </c>
       <c r="E466">
         <v>47.0366</v>
@@ -25161,8 +25162,8 @@
       <c r="B467">
         <v>2010</v>
       </c>
-      <c r="C467" s="3" t="s">
-        <v>550</v>
+      <c r="C467" t="s">
+        <v>542</v>
       </c>
       <c r="E467">
         <v>46.766100000000002</v>
@@ -25205,8 +25206,8 @@
       <c r="B468">
         <v>2010</v>
       </c>
-      <c r="C468" s="3" t="s">
-        <v>550</v>
+      <c r="C468" t="s">
+        <v>542</v>
       </c>
       <c r="E468">
         <v>47.607999999999997</v>
@@ -25249,8 +25250,8 @@
       <c r="B469">
         <v>2010</v>
       </c>
-      <c r="C469" s="3" t="s">
-        <v>550</v>
+      <c r="C469" t="s">
+        <v>542</v>
       </c>
       <c r="E469">
         <v>47.965600000000002</v>
@@ -25293,8 +25294,8 @@
       <c r="B470">
         <v>2010</v>
       </c>
-      <c r="C470" s="3" t="s">
-        <v>550</v>
+      <c r="C470" t="s">
+        <v>542</v>
       </c>
       <c r="E470">
         <v>46.962499999999999</v>
@@ -25337,8 +25338,8 @@
       <c r="B471">
         <v>2010</v>
       </c>
-      <c r="C471" s="3" t="s">
-        <v>550</v>
+      <c r="C471" t="s">
+        <v>542</v>
       </c>
       <c r="E471">
         <v>46.741100000000003</v>
@@ -25381,8 +25382,8 @@
       <c r="B472">
         <v>2010</v>
       </c>
-      <c r="C472" s="3" t="s">
-        <v>550</v>
+      <c r="C472" t="s">
+        <v>542</v>
       </c>
       <c r="E472">
         <v>44.834899999999998</v>
@@ -25425,8 +25426,8 @@
       <c r="B473">
         <v>2010</v>
       </c>
-      <c r="C473" s="3" t="s">
-        <v>550</v>
+      <c r="C473" t="s">
+        <v>542</v>
       </c>
       <c r="E473">
         <v>45.429000000000002</v>
@@ -25469,8 +25470,8 @@
       <c r="B474">
         <v>2010</v>
       </c>
-      <c r="C474" s="3" t="s">
-        <v>550</v>
+      <c r="C474" t="s">
+        <v>542</v>
       </c>
       <c r="E474">
         <v>44.906100000000002</v>
@@ -25513,8 +25514,8 @@
       <c r="B475">
         <v>2010</v>
       </c>
-      <c r="C475" s="3" t="s">
-        <v>550</v>
+      <c r="C475" t="s">
+        <v>542</v>
       </c>
       <c r="E475">
         <v>43.943600000000004</v>
@@ -25557,8 +25558,8 @@
       <c r="B476">
         <v>2010</v>
       </c>
-      <c r="C476" s="3" t="s">
-        <v>550</v>
+      <c r="C476" t="s">
+        <v>542</v>
       </c>
       <c r="E476">
         <v>44.674999999999997</v>
@@ -25601,8 +25602,8 @@
       <c r="B477">
         <v>2010</v>
       </c>
-      <c r="C477" s="3" t="s">
-        <v>550</v>
+      <c r="C477" t="s">
+        <v>542</v>
       </c>
       <c r="E477">
         <v>46.465699999999998</v>
@@ -25645,8 +25646,8 @@
       <c r="B478">
         <v>2010</v>
       </c>
-      <c r="C478" s="3" t="s">
-        <v>550</v>
+      <c r="C478" t="s">
+        <v>542</v>
       </c>
       <c r="E478">
         <v>46.298400000000001</v>
@@ -25689,8 +25690,8 @@
       <c r="B479">
         <v>2010</v>
       </c>
-      <c r="C479" s="3" t="s">
-        <v>550</v>
+      <c r="C479" t="s">
+        <v>542</v>
       </c>
       <c r="E479">
         <v>44.919600000000003</v>
@@ -25733,8 +25734,8 @@
       <c r="B480">
         <v>2010</v>
       </c>
-      <c r="C480" s="3" t="s">
-        <v>550</v>
+      <c r="C480" t="s">
+        <v>542</v>
       </c>
       <c r="E480">
         <v>48.535899999999998</v>
@@ -25777,8 +25778,8 @@
       <c r="B481">
         <v>2010</v>
       </c>
-      <c r="C481" s="3" t="s">
-        <v>550</v>
+      <c r="C481" t="s">
+        <v>542</v>
       </c>
       <c r="E481">
         <v>47.724800000000002</v>
@@ -25821,8 +25822,8 @@
       <c r="B482">
         <v>2010</v>
       </c>
-      <c r="C482" s="3" t="s">
-        <v>550</v>
+      <c r="C482" t="s">
+        <v>542</v>
       </c>
       <c r="E482">
         <v>48.907800000000002</v>
@@ -25865,8 +25866,8 @@
       <c r="B483">
         <v>2010</v>
       </c>
-      <c r="C483" s="3" t="s">
-        <v>550</v>
+      <c r="C483" t="s">
+        <v>542</v>
       </c>
       <c r="E483">
         <v>50.492100000000001</v>
@@ -25909,8 +25910,8 @@
       <c r="B484">
         <v>2010</v>
       </c>
-      <c r="C484" s="3" t="s">
-        <v>550</v>
+      <c r="C484" t="s">
+        <v>542</v>
       </c>
       <c r="E484">
         <v>50.122900000000001</v>
@@ -25953,8 +25954,8 @@
       <c r="B485">
         <v>2010</v>
       </c>
-      <c r="C485" s="3" t="s">
-        <v>550</v>
+      <c r="C485" t="s">
+        <v>542</v>
       </c>
       <c r="E485">
         <v>49.796900000000001</v>
@@ -25997,8 +25998,8 @@
       <c r="B486">
         <v>2010</v>
       </c>
-      <c r="C486" s="3" t="s">
-        <v>550</v>
+      <c r="C486" t="s">
+        <v>542</v>
       </c>
       <c r="E486">
         <v>50.411200000000001</v>
@@ -26041,8 +26042,8 @@
       <c r="B487">
         <v>2010</v>
       </c>
-      <c r="C487" s="3" t="s">
-        <v>550</v>
+      <c r="C487" t="s">
+        <v>542</v>
       </c>
       <c r="E487">
         <v>49.868099999999998</v>
@@ -26085,8 +26086,8 @@
       <c r="B488">
         <v>2010</v>
       </c>
-      <c r="C488" s="3" t="s">
-        <v>550</v>
+      <c r="C488" t="s">
+        <v>542</v>
       </c>
       <c r="E488">
         <v>50.271000000000001</v>
@@ -26129,8 +26130,8 @@
       <c r="B489">
         <v>2010</v>
       </c>
-      <c r="C489" s="3" t="s">
-        <v>550</v>
+      <c r="C489" t="s">
+        <v>542</v>
       </c>
       <c r="E489">
         <v>49.133200000000002</v>
@@ -26173,8 +26174,8 @@
       <c r="B490">
         <v>2010</v>
       </c>
-      <c r="C490" s="3" t="s">
-        <v>550</v>
+      <c r="C490" t="s">
+        <v>542</v>
       </c>
       <c r="E490">
         <v>48.313499999999998</v>
@@ -26217,8 +26218,8 @@
       <c r="B491">
         <v>2010</v>
       </c>
-      <c r="C491" s="3" t="s">
-        <v>550</v>
+      <c r="C491" t="s">
+        <v>542</v>
       </c>
       <c r="E491">
         <v>50.280700000000003</v>
@@ -26261,8 +26262,8 @@
       <c r="B492">
         <v>2010</v>
       </c>
-      <c r="C492" s="3" t="s">
-        <v>550</v>
+      <c r="C492" t="s">
+        <v>542</v>
       </c>
       <c r="E492">
         <v>49.145699999999998</v>
@@ -26305,8 +26306,8 @@
       <c r="B493">
         <v>2010</v>
       </c>
-      <c r="C493" s="3" t="s">
-        <v>550</v>
+      <c r="C493" t="s">
+        <v>542</v>
       </c>
       <c r="E493">
         <v>45.384399999999999</v>
@@ -26349,8 +26350,8 @@
       <c r="B494">
         <v>2010</v>
       </c>
-      <c r="C494" s="3" t="s">
-        <v>550</v>
+      <c r="C494" t="s">
+        <v>542</v>
       </c>
       <c r="E494">
         <v>48.354999999999997</v>
@@ -26393,8 +26394,8 @@
       <c r="B495">
         <v>2010</v>
       </c>
-      <c r="C495" s="3" t="s">
-        <v>550</v>
+      <c r="C495" t="s">
+        <v>542</v>
       </c>
       <c r="E495">
         <v>50.6494</v>
@@ -26437,8 +26438,8 @@
       <c r="B496">
         <v>2010</v>
       </c>
-      <c r="C496" s="3" t="s">
-        <v>550</v>
+      <c r="C496" t="s">
+        <v>542</v>
       </c>
       <c r="E496">
         <v>51.224600000000002</v>
@@ -26481,8 +26482,8 @@
       <c r="B497">
         <v>2010</v>
       </c>
-      <c r="C497" s="3" t="s">
-        <v>550</v>
+      <c r="C497" t="s">
+        <v>542</v>
       </c>
       <c r="E497">
         <v>50.347200000000001</v>
@@ -26525,8 +26526,8 @@
       <c r="B498">
         <v>2010</v>
       </c>
-      <c r="C498" s="3" t="s">
-        <v>550</v>
+      <c r="C498" t="s">
+        <v>542</v>
       </c>
       <c r="E498">
         <v>53.985500000000002</v>
@@ -26569,8 +26570,8 @@
       <c r="B499">
         <v>2010</v>
       </c>
-      <c r="C499" s="3" t="s">
-        <v>550</v>
+      <c r="C499" t="s">
+        <v>542</v>
       </c>
       <c r="E499">
         <v>53.191699999999997</v>
@@ -26613,8 +26614,8 @@
       <c r="B500">
         <v>2010</v>
       </c>
-      <c r="C500" s="3" t="s">
-        <v>550</v>
+      <c r="C500" t="s">
+        <v>542</v>
       </c>
       <c r="E500">
         <v>53.131300000000003</v>
@@ -26657,8 +26658,8 @@
       <c r="B501">
         <v>2010</v>
       </c>
-      <c r="C501" s="3" t="s">
-        <v>550</v>
+      <c r="C501" t="s">
+        <v>542</v>
       </c>
       <c r="E501">
         <v>52.441699999999997</v>
@@ -26701,8 +26702,8 @@
       <c r="B502">
         <v>2010</v>
       </c>
-      <c r="C502" s="3" t="s">
-        <v>550</v>
+      <c r="C502" t="s">
+        <v>542</v>
       </c>
       <c r="E502">
         <v>47.673200000000001</v>
@@ -26745,8 +26746,8 @@
       <c r="B503">
         <v>2010</v>
       </c>
-      <c r="C503" s="3" t="s">
-        <v>550</v>
+      <c r="C503" t="s">
+        <v>542</v>
       </c>
       <c r="E503">
         <v>52.6267</v>
@@ -26789,8 +26790,8 @@
       <c r="B504">
         <v>2010</v>
       </c>
-      <c r="C504" s="3" t="s">
-        <v>550</v>
+      <c r="C504" t="s">
+        <v>542</v>
       </c>
       <c r="E504">
         <v>51.896599999999999</v>
@@ -26833,8 +26834,8 @@
       <c r="B505">
         <v>2010</v>
       </c>
-      <c r="C505" s="3" t="s">
-        <v>550</v>
+      <c r="C505" t="s">
+        <v>542</v>
       </c>
       <c r="E505">
         <v>50.389299999999999</v>
@@ -26877,8 +26878,8 @@
       <c r="B506">
         <v>2010</v>
       </c>
-      <c r="C506" s="3" t="s">
-        <v>550</v>
+      <c r="C506" t="s">
+        <v>542</v>
       </c>
       <c r="E506">
         <v>52.139200000000002</v>
@@ -26921,8 +26922,8 @@
       <c r="B507">
         <v>2010</v>
       </c>
-      <c r="C507" s="3" t="s">
-        <v>550</v>
+      <c r="C507" t="s">
+        <v>542</v>
       </c>
       <c r="E507">
         <v>51.399799999999999</v>
@@ -26965,8 +26966,8 @@
       <c r="B508">
         <v>2010</v>
       </c>
-      <c r="C508" s="3" t="s">
-        <v>550</v>
+      <c r="C508" t="s">
+        <v>542</v>
       </c>
       <c r="E508">
         <v>49.427</v>
@@ -27009,8 +27010,8 @@
       <c r="B509">
         <v>2010</v>
       </c>
-      <c r="C509" s="3" t="s">
-        <v>550</v>
+      <c r="C509" t="s">
+        <v>542</v>
       </c>
       <c r="E509">
         <v>51.782400000000003</v>
@@ -27053,8 +27054,8 @@
       <c r="B510">
         <v>2010</v>
       </c>
-      <c r="C510" s="3" t="s">
-        <v>550</v>
+      <c r="C510" t="s">
+        <v>542</v>
       </c>
       <c r="D510" t="s">
         <v>96</v>
@@ -27100,8 +27101,8 @@
       <c r="B511">
         <v>2010</v>
       </c>
-      <c r="C511" s="3" t="s">
-        <v>550</v>
+      <c r="C511" t="s">
+        <v>542</v>
       </c>
       <c r="E511">
         <v>50.922699999999999</v>
@@ -27144,8 +27145,8 @@
       <c r="B512">
         <v>2010</v>
       </c>
-      <c r="C512" s="3" t="s">
-        <v>550</v>
+      <c r="C512" t="s">
+        <v>542</v>
       </c>
       <c r="E512">
         <v>52.1447</v>
@@ -27188,8 +27189,8 @@
       <c r="B513">
         <v>2010</v>
       </c>
-      <c r="C513" s="3" t="s">
-        <v>550</v>
+      <c r="C513" t="s">
+        <v>542</v>
       </c>
       <c r="E513">
         <v>51.215699999999998</v>
@@ -27232,8 +27233,8 @@
       <c r="B514">
         <v>2010</v>
       </c>
-      <c r="C514" s="3" t="s">
-        <v>550</v>
+      <c r="C514" t="s">
+        <v>542</v>
       </c>
       <c r="E514">
         <v>51.811599999999999</v>
@@ -27276,8 +27277,8 @@
       <c r="B515">
         <v>2010</v>
       </c>
-      <c r="C515" s="3" t="s">
-        <v>550</v>
+      <c r="C515" t="s">
+        <v>542</v>
       </c>
       <c r="E515">
         <v>49.096299999999999</v>
@@ -27320,8 +27321,8 @@
       <c r="B516">
         <v>2010</v>
       </c>
-      <c r="C516" s="3" t="s">
-        <v>550</v>
+      <c r="C516" t="s">
+        <v>542</v>
       </c>
       <c r="D516" t="s">
         <v>96</v>
@@ -27367,8 +27368,8 @@
       <c r="B517">
         <v>2010</v>
       </c>
-      <c r="C517" s="3" t="s">
-        <v>550</v>
+      <c r="C517" t="s">
+        <v>542</v>
       </c>
       <c r="E517">
         <v>51.855899999999998</v>
@@ -27411,8 +27412,8 @@
       <c r="B518">
         <v>2010</v>
       </c>
-      <c r="C518" s="3" t="s">
-        <v>550</v>
+      <c r="C518" t="s">
+        <v>542</v>
       </c>
       <c r="D518" t="s">
         <v>96</v>
@@ -27458,8 +27459,8 @@
       <c r="B519">
         <v>2010</v>
       </c>
-      <c r="C519" s="3" t="s">
-        <v>550</v>
+      <c r="C519" t="s">
+        <v>542</v>
       </c>
       <c r="D519" t="s">
         <v>96</v>
@@ -27505,8 +27506,8 @@
       <c r="B520">
         <v>2010</v>
       </c>
-      <c r="C520" s="3" t="s">
-        <v>550</v>
+      <c r="C520" t="s">
+        <v>542</v>
       </c>
       <c r="E520">
         <v>51.496000000000002</v>
@@ -27549,8 +27550,8 @@
       <c r="B521">
         <v>2010</v>
       </c>
-      <c r="C521" s="3" t="s">
-        <v>550</v>
+      <c r="C521" t="s">
+        <v>542</v>
       </c>
       <c r="E521">
         <v>51.464300000000001</v>
@@ -27593,8 +27594,8 @@
       <c r="B522">
         <v>2010</v>
       </c>
-      <c r="C522" s="3" t="s">
-        <v>550</v>
+      <c r="C522" t="s">
+        <v>542</v>
       </c>
       <c r="E522">
         <v>50.908999999999999</v>
@@ -27637,8 +27638,8 @@
       <c r="B523">
         <v>2010</v>
       </c>
-      <c r="C523" s="3" t="s">
-        <v>550</v>
+      <c r="C523" t="s">
+        <v>542</v>
       </c>
       <c r="E523">
         <v>52.254800000000003</v>
@@ -27681,8 +27682,8 @@
       <c r="B524">
         <v>2010</v>
       </c>
-      <c r="C524" s="3" t="s">
-        <v>550</v>
+      <c r="C524" t="s">
+        <v>542</v>
       </c>
       <c r="E524">
         <v>51.493499999999997</v>
@@ -27725,8 +27726,8 @@
       <c r="B525">
         <v>2010</v>
       </c>
-      <c r="C525" s="3" t="s">
-        <v>550</v>
+      <c r="C525" t="s">
+        <v>542</v>
       </c>
       <c r="E525">
         <v>51.538699999999999</v>
@@ -27769,8 +27770,8 @@
       <c r="B526">
         <v>2010</v>
       </c>
-      <c r="C526" s="3" t="s">
-        <v>550</v>
+      <c r="C526" t="s">
+        <v>542</v>
       </c>
       <c r="D526" t="s">
         <v>96</v>
@@ -27816,8 +27817,8 @@
       <c r="B527">
         <v>2010</v>
       </c>
-      <c r="C527" s="3" t="s">
-        <v>550</v>
+      <c r="C527" t="s">
+        <v>542</v>
       </c>
       <c r="E527">
         <v>51.953299999999999</v>
@@ -27860,8 +27861,8 @@
       <c r="B528">
         <v>2010</v>
       </c>
-      <c r="C528" s="3" t="s">
-        <v>550</v>
+      <c r="C528" t="s">
+        <v>542</v>
       </c>
       <c r="E528">
         <v>51.316299999999998</v>
@@ -27904,8 +27905,8 @@
       <c r="B529">
         <v>2010</v>
       </c>
-      <c r="C529" s="3" t="s">
-        <v>550</v>
+      <c r="C529" t="s">
+        <v>542</v>
       </c>
       <c r="D529" t="s">
         <v>96</v>
@@ -27951,8 +27952,8 @@
       <c r="B530">
         <v>2010</v>
       </c>
-      <c r="C530" s="3" t="s">
-        <v>550</v>
+      <c r="C530" t="s">
+        <v>542</v>
       </c>
       <c r="D530" t="s">
         <v>96</v>
@@ -27998,8 +27999,8 @@
       <c r="B531">
         <v>2010</v>
       </c>
-      <c r="C531" s="3" t="s">
-        <v>550</v>
+      <c r="C531" t="s">
+        <v>542</v>
       </c>
       <c r="E531">
         <v>52.109699999999997</v>
